--- a/src/config/midas_config_values.xlsx
+++ b/src/config/midas_config_values.xlsx
@@ -8,16 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/james/Documents/code/midas-alt/src/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8616FB9E-B90A-2B4A-975D-636AEF2C7295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA311461-FD02-EB4A-A022-F7EF0D34DC66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8320" yWindow="3860" windowWidth="34560" windowHeight="21580" activeTab="1" xr2:uid="{C4C84A31-B2D7-9544-A674-D1C9532EF091}"/>
+    <workbookView xWindow="51200" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="3" xr2:uid="{C4C84A31-B2D7-9544-A674-D1C9532EF091}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="8" r:id="rId1"/>
     <sheet name="Config" sheetId="7" r:id="rId2"/>
     <sheet name="Facilities" sheetId="2" r:id="rId3"/>
-    <sheet name="Systems" sheetId="3" r:id="rId4"/>
+    <sheet name="Installation Locations" sheetId="11" r:id="rId4"/>
+    <sheet name="Systems" sheetId="3" r:id="rId5"/>
   </sheets>
+  <definedNames>
+    <definedName name="afb_excel_1" localSheetId="3">'Installation Locations'!$A$1:$D$211</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -38,8 +42,26 @@
 </workbook>
 </file>
 
+<file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
+<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
+  <connection id="1" xr16:uid="{B57F21D2-81B0-B047-A227-7E57E7C55936}" name="afb_excel" type="6" refreshedVersion="8" background="1" saveData="1">
+    <textPr codePage="65001" sourceFile="/Users/james/Documents/code/midas-alt/output/afb_excel.csv" comma="1">
+      <textFields count="7">
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField/>
+        <textField type="skip"/>
+        <textField type="skip"/>
+      </textFields>
+    </textPr>
+  </connection>
+</connections>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="827">
   <si>
     <t>Key</t>
   </si>
@@ -514,12 +536,2096 @@
     <t>Value distribution of possible age's for both Facilities and Systems used when randomly generating sample data. This is defined (per the provided: "Simulate Date - US Space Template" spreadsheet) in 'segments', where each 'segment' is comprised of a probability and range. The probability is the likelehood a given Facility/System will fall into the correlated age range, and the range defines a bounds for how many years old that segment is. 
 Each segment consists of a single percentage value defined as an integer from 1-100 (ex: 25 = 25%), with a range defined as two integers separated by a hyphen (ex: 10-20). You can define as many segments as needed but the maximum total value of all combined percentages of the segments should be 100 (first values, or key).</t>
   </si>
+  <si>
+    <t>Altus Air Force Base</t>
+  </si>
+  <si>
+    <t>Altus</t>
+  </si>
+  <si>
+    <t>Oklahoma</t>
+  </si>
+  <si>
+    <t>34°39′59″N 099°16′05″W</t>
+  </si>
+  <si>
+    <t>Joint Base Anacostia-Bolling</t>
+  </si>
+  <si>
+    <t>Southwest</t>
+  </si>
+  <si>
+    <t>Washington, D.C.</t>
+  </si>
+  <si>
+    <t>38°50′34″N 077°00′58″W</t>
+  </si>
+  <si>
+    <t>Joint Base Andrews-Naval Air Facility Washington</t>
+  </si>
+  <si>
+    <t>Camp Springs</t>
+  </si>
+  <si>
+    <t>Maryland</t>
+  </si>
+  <si>
+    <t>38°48′39″N 076°52′01″W</t>
+  </si>
+  <si>
+    <t>Arnold Air Force Base</t>
+  </si>
+  <si>
+    <t>near Tullahoma</t>
+  </si>
+  <si>
+    <t>Tennessee</t>
+  </si>
+  <si>
+    <t>35°23′33″N 086°05′09″W</t>
+  </si>
+  <si>
+    <t>Barksdale Air Force Base</t>
+  </si>
+  <si>
+    <t>Bossier City</t>
+  </si>
+  <si>
+    <t>Louisiana</t>
+  </si>
+  <si>
+    <t>32°30′07″N 093°39′46″W</t>
+  </si>
+  <si>
+    <t>Beale Air Force Base</t>
+  </si>
+  <si>
+    <t>Waldo Junction</t>
+  </si>
+  <si>
+    <t>California</t>
+  </si>
+  <si>
+    <t>39°08′10″N 121°26′11″W</t>
+  </si>
+  <si>
+    <t>Cannon Air Force Base</t>
+  </si>
+  <si>
+    <t>Clovis</t>
+  </si>
+  <si>
+    <t>New Mexico</t>
+  </si>
+  <si>
+    <t>34°22′58″N 103°19′20″W</t>
+  </si>
+  <si>
+    <t>Joint Base Charleston</t>
+  </si>
+  <si>
+    <t>Charleston</t>
+  </si>
+  <si>
+    <t>South Carolina</t>
+  </si>
+  <si>
+    <t>32°53′55″N 080°02′26″W</t>
+  </si>
+  <si>
+    <t>Columbus Air Force Base</t>
+  </si>
+  <si>
+    <t>Columbus</t>
+  </si>
+  <si>
+    <t>Mississippi</t>
+  </si>
+  <si>
+    <t>33°38′38″N 088°26′38″W</t>
+  </si>
+  <si>
+    <t>Creech Air Force Base</t>
+  </si>
+  <si>
+    <t>Indian Springs</t>
+  </si>
+  <si>
+    <t>Nevada</t>
+  </si>
+  <si>
+    <t>36°35′14″N 115°40′24″W</t>
+  </si>
+  <si>
+    <t>Davis–Monthan Air Force Base</t>
+  </si>
+  <si>
+    <t>Tucson</t>
+  </si>
+  <si>
+    <t>Arizona</t>
+  </si>
+  <si>
+    <t>32°09′59″N 110°52′59″W</t>
+  </si>
+  <si>
+    <t>Dover Air Force Base</t>
+  </si>
+  <si>
+    <t>Dover</t>
+  </si>
+  <si>
+    <t>Delaware</t>
+  </si>
+  <si>
+    <t>39°07′42″N 075°27′53″W</t>
+  </si>
+  <si>
+    <t>Dyess Air Force Base</t>
+  </si>
+  <si>
+    <t>Abilene</t>
+  </si>
+  <si>
+    <t>Texas</t>
+  </si>
+  <si>
+    <t>32°25′15″N 099°51′17″W</t>
+  </si>
+  <si>
+    <t>Edwards Air Force Base</t>
+  </si>
+  <si>
+    <t>Edwards</t>
+  </si>
+  <si>
+    <t>34°54′20″N 117°53′01″W</t>
+  </si>
+  <si>
+    <t>Eglin Air Force Base</t>
+  </si>
+  <si>
+    <t>Valparaiso</t>
+  </si>
+  <si>
+    <t>Florida</t>
+  </si>
+  <si>
+    <t>30°29′N 086°32′W</t>
+  </si>
+  <si>
+    <t>Ellsworth Air Force Base</t>
+  </si>
+  <si>
+    <t>Box Elder</t>
+  </si>
+  <si>
+    <t>South Dakota</t>
+  </si>
+  <si>
+    <t>44°08′42″N 103°06′13″W</t>
+  </si>
+  <si>
+    <t>Francis E. Warren Air Force Base</t>
+  </si>
+  <si>
+    <t>Cheyenne</t>
+  </si>
+  <si>
+    <t>Wyoming</t>
+  </si>
+  <si>
+    <t>41°07′59″N 104°52′01″W</t>
+  </si>
+  <si>
+    <t>Fairchild Air Force Base</t>
+  </si>
+  <si>
+    <t>Spokane</t>
+  </si>
+  <si>
+    <t>Washington</t>
+  </si>
+  <si>
+    <t>47°36′54″N 117°39′20″W</t>
+  </si>
+  <si>
+    <t>Fort George G. Meade</t>
+  </si>
+  <si>
+    <t>Odenton</t>
+  </si>
+  <si>
+    <t>39°6′25″N 76°44′35″W</t>
+  </si>
+  <si>
+    <t>Gila Bend Air Force Auxiliary Field</t>
+  </si>
+  <si>
+    <t>Gila Bend</t>
+  </si>
+  <si>
+    <t>32°53′15″N 112°43′12″W</t>
+  </si>
+  <si>
+    <t>Goodfellow Air Force Base</t>
+  </si>
+  <si>
+    <t>San Angelo</t>
+  </si>
+  <si>
+    <t>31°25′46″N 100°23′56″W</t>
+  </si>
+  <si>
+    <t>Grand Forks Air Force Base</t>
+  </si>
+  <si>
+    <t>Grand Forks</t>
+  </si>
+  <si>
+    <t>North Dakota</t>
+  </si>
+  <si>
+    <t>47°57′40″N 097°24′04″W</t>
+  </si>
+  <si>
+    <t>Hanscom Air Force Base</t>
+  </si>
+  <si>
+    <t>Lincoln</t>
+  </si>
+  <si>
+    <t>Massachusetts</t>
+  </si>
+  <si>
+    <t>42°28′12″N 071°17′21″W</t>
+  </si>
+  <si>
+    <t>Hill Air Force Base</t>
+  </si>
+  <si>
+    <t>Ogden</t>
+  </si>
+  <si>
+    <t>Utah</t>
+  </si>
+  <si>
+    <t>41°07′26″N 111°58′22″W</t>
+  </si>
+  <si>
+    <t>Homey Airport</t>
+  </si>
+  <si>
+    <t>Groom Lake</t>
+  </si>
+  <si>
+    <t>37°14′0″N 115°48′30″W</t>
+  </si>
+  <si>
+    <t>Holloman Air Force Base</t>
+  </si>
+  <si>
+    <t>Alamogordo</t>
+  </si>
+  <si>
+    <t>32°51′09″N 106°06′23″W</t>
+  </si>
+  <si>
+    <t>Hurlburt Field</t>
+  </si>
+  <si>
+    <t>Mary Esther</t>
+  </si>
+  <si>
+    <t>30°25′40″N 086°41′22″W</t>
+  </si>
+  <si>
+    <t>Keesler Air Force Base</t>
+  </si>
+  <si>
+    <t>Biloxi</t>
+  </si>
+  <si>
+    <t>30°24′41″N 088°55′25″W</t>
+  </si>
+  <si>
+    <t>Kegelman Air Force Auxiliary Field</t>
+  </si>
+  <si>
+    <t>Cherokee</t>
+  </si>
+  <si>
+    <t>36°44′17″N 098°07′34″W</t>
+  </si>
+  <si>
+    <t>Kirtland Air Force Base</t>
+  </si>
+  <si>
+    <t>Albuquerque</t>
+  </si>
+  <si>
+    <t>35°02′25″N 106°36′33″W</t>
+  </si>
+  <si>
+    <t>Joint Base Langley–Eustis</t>
+  </si>
+  <si>
+    <t>Hampton</t>
+  </si>
+  <si>
+    <t>Virginia</t>
+  </si>
+  <si>
+    <t>37°04′58″N 076°21′38″W</t>
+  </si>
+  <si>
+    <t>Laughlin Air Force Base</t>
+  </si>
+  <si>
+    <t>Del Rio</t>
+  </si>
+  <si>
+    <t>29°21′34″N 100°46′41″W</t>
+  </si>
+  <si>
+    <t>Joint Base Lewis-McChord</t>
+  </si>
+  <si>
+    <t>Tacoma</t>
+  </si>
+  <si>
+    <t>47°08′51″N 122°28′46″W</t>
+  </si>
+  <si>
+    <t>Little Rock Air Force Base</t>
+  </si>
+  <si>
+    <t>Jacksonville</t>
+  </si>
+  <si>
+    <t>Arkansas</t>
+  </si>
+  <si>
+    <t>34°55′01″N 092°08′47″W</t>
+  </si>
+  <si>
+    <t>Luke Air Force Base</t>
+  </si>
+  <si>
+    <t>Glendale</t>
+  </si>
+  <si>
+    <t>33°32′06″N 112°22′59″W</t>
+  </si>
+  <si>
+    <t>MacDill Air Force Base</t>
+  </si>
+  <si>
+    <t>Tampa</t>
+  </si>
+  <si>
+    <t>27°50′58″N 082°31′16″W</t>
+  </si>
+  <si>
+    <t>Malmstrom Air Force Base</t>
+  </si>
+  <si>
+    <t>Great Falls</t>
+  </si>
+  <si>
+    <t>Montana</t>
+  </si>
+  <si>
+    <t>47°30′17″N 111°11′14″W</t>
+  </si>
+  <si>
+    <t>Maxwell Air Force Base</t>
+  </si>
+  <si>
+    <t>Montgomery</t>
+  </si>
+  <si>
+    <t>Alabama</t>
+  </si>
+  <si>
+    <t>32°22′45″N 086°21′45″W</t>
+  </si>
+  <si>
+    <t>McConnell Air Force Base</t>
+  </si>
+  <si>
+    <t>Wichita</t>
+  </si>
+  <si>
+    <t>Kansas</t>
+  </si>
+  <si>
+    <t>37°37′23″N 097°16′02″W</t>
+  </si>
+  <si>
+    <t>Joint Base McGuire–Dix–Lakehurst</t>
+  </si>
+  <si>
+    <t>Trenton</t>
+  </si>
+  <si>
+    <t>New Jersey</t>
+  </si>
+  <si>
+    <t>40°01′09″N 074°31′22″W</t>
+  </si>
+  <si>
+    <t>Minot Air Force Base</t>
+  </si>
+  <si>
+    <t>Minot</t>
+  </si>
+  <si>
+    <t>48°24′57″N 101°21′29″W</t>
+  </si>
+  <si>
+    <t>Moody Air Force Base</t>
+  </si>
+  <si>
+    <t>Valdosta</t>
+  </si>
+  <si>
+    <t>Georgia</t>
+  </si>
+  <si>
+    <t>30°58′4″N 83°11′34″W</t>
+  </si>
+  <si>
+    <t>Mountain Home Air Force Base</t>
+  </si>
+  <si>
+    <t>Mountain Home</t>
+  </si>
+  <si>
+    <t>Idaho</t>
+  </si>
+  <si>
+    <t>43°02′37″N 115°52′21″W</t>
+  </si>
+  <si>
+    <t>Nellis Air Force Base</t>
+  </si>
+  <si>
+    <t>Las Vegas</t>
+  </si>
+  <si>
+    <t>36°14′10″N 115°02′03″W</t>
+  </si>
+  <si>
+    <t>North Auxiliary Airfield</t>
+  </si>
+  <si>
+    <t>North</t>
+  </si>
+  <si>
+    <t>33°37′01″N 081°04′59″W</t>
+  </si>
+  <si>
+    <t>Offutt Air Force Base</t>
+  </si>
+  <si>
+    <t>Bellevue</t>
+  </si>
+  <si>
+    <t>Nebraska</t>
+  </si>
+  <si>
+    <t>41°07′10″N 095°54′31″W</t>
+  </si>
+  <si>
+    <t>Pope Field</t>
+  </si>
+  <si>
+    <t>Fayetteville</t>
+  </si>
+  <si>
+    <t>North Carolina</t>
+  </si>
+  <si>
+    <t>35°10′15″N 079°00′52″W</t>
+  </si>
+  <si>
+    <t>Robins Air Force Base</t>
+  </si>
+  <si>
+    <t>Warner Robins</t>
+  </si>
+  <si>
+    <t>32°38′24″N 083°35′30″W</t>
+  </si>
+  <si>
+    <t>Rome Research Site</t>
+  </si>
+  <si>
+    <t>Rome</t>
+  </si>
+  <si>
+    <t>New York</t>
+  </si>
+  <si>
+    <t>43°13′16.9″N 75°24′30.8″W</t>
+  </si>
+  <si>
+    <t>Joint Base San Antonio</t>
+  </si>
+  <si>
+    <t>San Antonio</t>
+  </si>
+  <si>
+    <t>29°26′56″N 098°26′56″W</t>
+  </si>
+  <si>
+    <t>Scott Air Force Base</t>
+  </si>
+  <si>
+    <t>Belleville</t>
+  </si>
+  <si>
+    <t>Illinois</t>
+  </si>
+  <si>
+    <t>38°32′43″N 089°50′07″W</t>
+  </si>
+  <si>
+    <t>Seymour Johnson Air Force Base</t>
+  </si>
+  <si>
+    <t>Goldsboro</t>
+  </si>
+  <si>
+    <t>35°20′22″N 077°57′38″W</t>
+  </si>
+  <si>
+    <t>Shaw Air Force Base</t>
+  </si>
+  <si>
+    <t>Sumter</t>
+  </si>
+  <si>
+    <t>33°58′23″N 080°28′22″W</t>
+  </si>
+  <si>
+    <t>Sheppard Air Force Base</t>
+  </si>
+  <si>
+    <t>Wichita Falls</t>
+  </si>
+  <si>
+    <t>33°59′20″N 098°29′31″W</t>
+  </si>
+  <si>
+    <t>Tinker Air Force Base</t>
+  </si>
+  <si>
+    <t>Oklahoma City</t>
+  </si>
+  <si>
+    <t>35°24′53″N 097°23′12″W</t>
+  </si>
+  <si>
+    <t>Tonopah Test Range Airport</t>
+  </si>
+  <si>
+    <t>Tonopah</t>
+  </si>
+  <si>
+    <t>37°47′41″N 116°46′43″W</t>
+  </si>
+  <si>
+    <t>Travis Air Force Base</t>
+  </si>
+  <si>
+    <t>Fairfield</t>
+  </si>
+  <si>
+    <t>38°15′46″N 121°55′39″W</t>
+  </si>
+  <si>
+    <t>Tyndall Air Force Base</t>
+  </si>
+  <si>
+    <t>Panama City</t>
+  </si>
+  <si>
+    <t>30°4′43″N 85°34′35″W</t>
+  </si>
+  <si>
+    <t>United States Air Force Academy</t>
+  </si>
+  <si>
+    <t>Colorado Springs</t>
+  </si>
+  <si>
+    <t>Colorado</t>
+  </si>
+  <si>
+    <t>38°59′25″N 104°51′30″W</t>
+  </si>
+  <si>
+    <t>Vance Air Force Base</t>
+  </si>
+  <si>
+    <t>Enid</t>
+  </si>
+  <si>
+    <t>36°20′22″N 097°55′02″W</t>
+  </si>
+  <si>
+    <t>Whiteman Air Force Base</t>
+  </si>
+  <si>
+    <t>Knob Noster</t>
+  </si>
+  <si>
+    <t>Missouri</t>
+  </si>
+  <si>
+    <t>38°43′49″N 093°32′53″W</t>
+  </si>
+  <si>
+    <t>Wright-Patterson Air Force Base</t>
+  </si>
+  <si>
+    <t>Dayton</t>
+  </si>
+  <si>
+    <t>Ohio</t>
+  </si>
+  <si>
+    <t>39°49′23″N 084°02′58″W</t>
+  </si>
+  <si>
+    <t>Duke Field</t>
+  </si>
+  <si>
+    <t>Homestead</t>
+  </si>
+  <si>
+    <t>Niagara Falls</t>
+  </si>
+  <si>
+    <t>Pittsburgh</t>
+  </si>
+  <si>
+    <t>Youngstown</t>
+  </si>
+  <si>
+    <t>Fresno</t>
+  </si>
+  <si>
+    <t>San Diego</t>
+  </si>
+  <si>
+    <t>Greeley</t>
+  </si>
+  <si>
+    <t>New Castle</t>
+  </si>
+  <si>
+    <t>Savannah</t>
+  </si>
+  <si>
+    <t>Peoria</t>
+  </si>
+  <si>
+    <t>Fort Wayne</t>
+  </si>
+  <si>
+    <t>Des Moines</t>
+  </si>
+  <si>
+    <t>Fort Dodge</t>
+  </si>
+  <si>
+    <t>Sioux City</t>
+  </si>
+  <si>
+    <t>Bangor</t>
+  </si>
+  <si>
+    <t>South Portland</t>
+  </si>
+  <si>
+    <t>Duluth</t>
+  </si>
+  <si>
+    <t>Gulfport</t>
+  </si>
+  <si>
+    <t>Jackson</t>
+  </si>
+  <si>
+    <t>Reno</t>
+  </si>
+  <si>
+    <t>Charlotte</t>
+  </si>
+  <si>
+    <t>New London</t>
+  </si>
+  <si>
+    <t>Fargo</t>
+  </si>
+  <si>
+    <t>Springfield</t>
+  </si>
+  <si>
+    <t>Toledo</t>
+  </si>
+  <si>
+    <t>Tulsa</t>
+  </si>
+  <si>
+    <t>Portland</t>
+  </si>
+  <si>
+    <t>Camp Rilea</t>
+  </si>
+  <si>
+    <t>Johnstown</t>
+  </si>
+  <si>
+    <t>Memphis</t>
+  </si>
+  <si>
+    <t>Fort Bliss</t>
+  </si>
+  <si>
+    <t>Burlington</t>
+  </si>
+  <si>
+    <t>Louisville</t>
+  </si>
+  <si>
+    <t>Zanesville</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Coordinates</t>
+  </si>
+  <si>
+    <t>Abston Air National Guard Station</t>
+  </si>
+  <si>
+    <t>32°21′22″N 086°20′48″W</t>
+  </si>
+  <si>
+    <t>Atlantic City Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Egg Harbor</t>
+  </si>
+  <si>
+    <t>39°26′53″N 074°34′54″W</t>
+  </si>
+  <si>
+    <t>Bangor Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Maine</t>
+  </si>
+  <si>
+    <t>44°48′51″N 068°49′51″W</t>
+  </si>
+  <si>
+    <t>Barnes Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Westfield</t>
+  </si>
+  <si>
+    <t>42°09′56″N 072°43′14″W</t>
+  </si>
+  <si>
+    <t>Battle Creek Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Michigan</t>
+  </si>
+  <si>
+    <t>42°18′26.2″N 85°15′05.3″W</t>
+  </si>
+  <si>
+    <t>Berry Field Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Nashville</t>
+  </si>
+  <si>
+    <t>36°07′36″N 86°40′55″W</t>
+  </si>
+  <si>
+    <t>Biddle Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Horsham Township</t>
+  </si>
+  <si>
+    <t>Pennsylvania</t>
+  </si>
+  <si>
+    <t>40°11′59″N 075°08′53″W</t>
+  </si>
+  <si>
+    <t>Bradley Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Windsor Locks</t>
+  </si>
+  <si>
+    <t>Connecticut</t>
+  </si>
+  <si>
+    <t>41°56′20″N 72°41′0″W</t>
+  </si>
+  <si>
+    <t>Brunswick Air National Guard Station</t>
+  </si>
+  <si>
+    <t>Dock Junction</t>
+  </si>
+  <si>
+    <t>31°14′51.9″N 81°29′09″W</t>
+  </si>
+  <si>
+    <t>Burlington Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Vermont</t>
+  </si>
+  <si>
+    <t>44°28′22″N 073°08′48″W</t>
+  </si>
+  <si>
+    <t>Camp Murray Air National Guard Station</t>
+  </si>
+  <si>
+    <t>47°7′5″N 122°33′36″W</t>
+  </si>
+  <si>
+    <t>Warrenton</t>
+  </si>
+  <si>
+    <t>Oregon</t>
+  </si>
+  <si>
+    <t>46°7′45″N 123°56′38″W</t>
+  </si>
+  <si>
+    <t>Capital Airport Air National Guard Station</t>
+  </si>
+  <si>
+    <t>39°50′39″N 089°40′41″W</t>
+  </si>
+  <si>
+    <t>Channel Islands Air National Guard Station</t>
+  </si>
+  <si>
+    <t>Oxnard</t>
+  </si>
+  <si>
+    <t>34°06′54″N 119°06′37″W</t>
+  </si>
+  <si>
+    <t>Charlotte Air National Guard Base</t>
+  </si>
+  <si>
+    <t>35°12′58″N 80°55′55″W</t>
+  </si>
+  <si>
+    <t>Dallas Air Guard Station</t>
+  </si>
+  <si>
+    <t>Grand Prairie</t>
+  </si>
+  <si>
+    <t>32°44′24″N 096°58′12″W</t>
+  </si>
+  <si>
+    <t>Des Moines Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Iowa</t>
+  </si>
+  <si>
+    <t>41°32′18″N 093°39′34″W</t>
+  </si>
+  <si>
+    <t>Dobbins Air Reserve Base</t>
+  </si>
+  <si>
+    <t>Marietta</t>
+  </si>
+  <si>
+    <t>33°54′55″N 084°30′59″W</t>
+  </si>
+  <si>
+    <t>Crestview</t>
+  </si>
+  <si>
+    <t>30°39′01″N 086°31′22″W</t>
+  </si>
+  <si>
+    <t>Duluth Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Minnesota</t>
+  </si>
+  <si>
+    <t>46°50′32″N 92°11′37″W</t>
+  </si>
+  <si>
+    <t>Eastern Air Defense Sector</t>
+  </si>
+  <si>
+    <t>43°12′59.8″N 75°24′17.4″W</t>
+  </si>
+  <si>
+    <t>Ebbing Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Fort Smith</t>
+  </si>
+  <si>
+    <t>35°20′12″N 94°22′03″W</t>
+  </si>
+  <si>
+    <t>Ellington Field Joint Reserve Base</t>
+  </si>
+  <si>
+    <t>Houston</t>
+  </si>
+  <si>
+    <t>29°36′26″N 95°09′32″W</t>
+  </si>
+  <si>
+    <t>Fargo Air National Guard Base</t>
+  </si>
+  <si>
+    <t>46°55′14″N 096°48′57″W</t>
+  </si>
+  <si>
+    <t>Forbes Field Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Topeka</t>
+  </si>
+  <si>
+    <t>38°57′04″N 095°39′57″W</t>
+  </si>
+  <si>
+    <t>El Paso</t>
+  </si>
+  <si>
+    <t>31°48′7″N 106°25′29″W</t>
+  </si>
+  <si>
+    <t>Fort Dodge Air National Guard Station</t>
+  </si>
+  <si>
+    <t>42°33′02.5″N 94°10′45.3″W</t>
+  </si>
+  <si>
+    <t>Fort Wayne Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Indiana</t>
+  </si>
+  <si>
+    <t>40°58′42″N 085°11′42″W</t>
+  </si>
+  <si>
+    <t>Naval Air Station Joint Reserve Base Fort Worth</t>
+  </si>
+  <si>
+    <t>Fort Worth</t>
+  </si>
+  <si>
+    <t>32°46′09″N 097°26′30″W</t>
+  </si>
+  <si>
+    <t>Francis S. Gabreski Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Westhampton Beach</t>
+  </si>
+  <si>
+    <t>40°50′13″N 072°38′32″W</t>
+  </si>
+  <si>
+    <t>Fresno Air National Guard Base</t>
+  </si>
+  <si>
+    <t>36°46′34″N 119°43′50″W</t>
+  </si>
+  <si>
+    <t>General Mitchell Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Milwaukee</t>
+  </si>
+  <si>
+    <t>Wisconsin</t>
+  </si>
+  <si>
+    <t>42°56′50″N 087°53′48″W</t>
+  </si>
+  <si>
+    <t>Gowen Field Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Boise</t>
+  </si>
+  <si>
+    <t>43°33′52″N 116°13′22″W</t>
+  </si>
+  <si>
+    <t>Great Falls Air National Guard Base</t>
+  </si>
+  <si>
+    <t>47°28′55.20″N 111°22′14.46″W</t>
+  </si>
+  <si>
+    <t>Greeley Air National Guard Station</t>
+  </si>
+  <si>
+    <t>40°25′25.8″N 104°38′24.6″W</t>
+  </si>
+  <si>
+    <t>Grissom Air Reserve Base</t>
+  </si>
+  <si>
+    <t>Kokomo</t>
+  </si>
+  <si>
+    <t>40°38′53″N 086°09′08″W</t>
+  </si>
+  <si>
+    <t>Goldwater Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Phoenix</t>
+  </si>
+  <si>
+    <t>33°25′36″N 112°00′43″W</t>
+  </si>
+  <si>
+    <t>Gulfport Combat Readiness Training Center</t>
+  </si>
+  <si>
+    <t>30°24′26″N 089°04′12″W</t>
+  </si>
+  <si>
+    <t>Hall Air Guard Station</t>
+  </si>
+  <si>
+    <t>Dothan</t>
+  </si>
+  <si>
+    <t>31°19′46.7″N 85°27′57.2″W</t>
+  </si>
+  <si>
+    <t>Hancock Field Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Syracuse</t>
+  </si>
+  <si>
+    <t>43°06′41″N 076°07′25″W</t>
+  </si>
+  <si>
+    <t>Harrisburg Air Station Middletown</t>
+  </si>
+  <si>
+    <t>Middletown</t>
+  </si>
+  <si>
+    <t>40°11′37″N 076°45′48″W</t>
+  </si>
+  <si>
+    <t>Homestead Air Reserve Base</t>
+  </si>
+  <si>
+    <t>25°29′18″N 080°23′01″W</t>
+  </si>
+  <si>
+    <t>Hulman Field Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Terre Haute</t>
+  </si>
+  <si>
+    <t>39°27′05″N 087°18′27″W</t>
+  </si>
+  <si>
+    <t>Jackson Air National Guard Base</t>
+  </si>
+  <si>
+    <t>32°18′40″N 090°04′33″W</t>
+  </si>
+  <si>
+    <t>Jacksonville Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Jacksonville, Florida</t>
+  </si>
+  <si>
+    <t>30°29′39″N 081°41′16″W</t>
+  </si>
+  <si>
+    <t>Jefferson Barracks Air National Guard Station</t>
+  </si>
+  <si>
+    <t>St Louis</t>
+  </si>
+  <si>
+    <t>38°30′14.3″N 90°16′48.9″W</t>
+  </si>
+  <si>
+    <t>Joe Foss Field Air National Guard Station</t>
+  </si>
+  <si>
+    <t>Sioux Falls</t>
+  </si>
+  <si>
+    <t>43°34′55″N 096°44′31″W</t>
+  </si>
+  <si>
+    <t>Johnstown Air National Guard Station</t>
+  </si>
+  <si>
+    <t>40°19′23.5″N 78°50′15.7″W</t>
+  </si>
+  <si>
+    <t>Key Field Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Meridian</t>
+  </si>
+  <si>
+    <t>32°19′57″N 088°45′07″W</t>
+  </si>
+  <si>
+    <t>Kingsley Field Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Klamath Falls</t>
+  </si>
+  <si>
+    <t>42°09′22″N 121°43′59″W</t>
+  </si>
+  <si>
+    <t>Lincoln Air National Guard Base</t>
+  </si>
+  <si>
+    <t>40°51′04″N 096°45′33″W</t>
+  </si>
+  <si>
+    <t>Louisville Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Kentucky</t>
+  </si>
+  <si>
+    <t>38°10′41″N 85°43′29″W</t>
+  </si>
+  <si>
+    <t>Mansfield Lahm Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Mansfield</t>
+  </si>
+  <si>
+    <t>40°48′49″N 82°31′00″W</t>
+  </si>
+  <si>
+    <t>March Joint Air Reserve Base</t>
+  </si>
+  <si>
+    <t>Riverside</t>
+  </si>
+  <si>
+    <t>33°52′50″N 117°15′34″W</t>
+  </si>
+  <si>
+    <t>McEntire Joint National Guard Base</t>
+  </si>
+  <si>
+    <t>Eastover</t>
+  </si>
+  <si>
+    <t>33°55′15″N 080°48′04″W</t>
+  </si>
+  <si>
+    <t>McGhee Tyson Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Knoxville</t>
+  </si>
+  <si>
+    <t>35°48′39″N 083°59′38″W</t>
+  </si>
+  <si>
+    <t>McLaughlin Air National Guard Base</t>
+  </si>
+  <si>
+    <t>West Virginia</t>
+  </si>
+  <si>
+    <t>38°22′23″N 81°35′35″W</t>
+  </si>
+  <si>
+    <t>Memphis Air National Guard Base</t>
+  </si>
+  <si>
+    <t>35°02′33″N 089°58′36″W</t>
+  </si>
+  <si>
+    <t>Minneapolis-Saint Paul Joint Air Reserve Station</t>
+  </si>
+  <si>
+    <t>Minneapolis – Saint Paul</t>
+  </si>
+  <si>
+    <t>44°52′54″N 093°14′01″W</t>
+  </si>
+  <si>
+    <t>Moffett Federal Airfield</t>
+  </si>
+  <si>
+    <t>Mountain View</t>
+  </si>
+  <si>
+    <t>37°24′54″N 122°02′54″W</t>
+  </si>
+  <si>
+    <t>Montgomery Air National Guard Base</t>
+  </si>
+  <si>
+    <t>32°18′16″N 086°24′01″W</t>
+  </si>
+  <si>
+    <t>Morris Air National Guard Base</t>
+  </si>
+  <si>
+    <t>32°06′55″N 110°55′50″W</t>
+  </si>
+  <si>
+    <t>New Castle Air National Guard Base</t>
+  </si>
+  <si>
+    <t>39°41′07″N 075°35′57″W</t>
+  </si>
+  <si>
+    <t>New London Air National Guard Base</t>
+  </si>
+  <si>
+    <t>35°25′06.9″N 80°08′30″W</t>
+  </si>
+  <si>
+    <t>Naval Air Station Joint Reserve Base New Orleans</t>
+  </si>
+  <si>
+    <t>Belle Chasse</t>
+  </si>
+  <si>
+    <t>29°49′31″N 090°02′06″W</t>
+  </si>
+  <si>
+    <t>Niagara Falls Air Reserve Station</t>
+  </si>
+  <si>
+    <t>43°06′48″N 078°56′51″W</t>
+  </si>
+  <si>
+    <t>North Highlands Air National Guard Station</t>
+  </si>
+  <si>
+    <t>Sacramento, California</t>
+  </si>
+  <si>
+    <t>38°38′24″N 121°24′09″W</t>
+  </si>
+  <si>
+    <t>North Smithfield Air National Guard Station</t>
+  </si>
+  <si>
+    <t>North Smithfield</t>
+  </si>
+  <si>
+    <t>Rhode Island</t>
+  </si>
+  <si>
+    <t>41°58′13″N 71°34′32.4″W</t>
+  </si>
+  <si>
+    <t>Otis Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Mashpee</t>
+  </si>
+  <si>
+    <t>41°39′31″N 070°31′17″W</t>
+  </si>
+  <si>
+    <t>Pease Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Portsmouth</t>
+  </si>
+  <si>
+    <t>New Hampshire</t>
+  </si>
+  <si>
+    <t>43°04′41″N 070°49′24″W</t>
+  </si>
+  <si>
+    <t>Peoria Air National Guard Base</t>
+  </si>
+  <si>
+    <t>40°39′38″N 089°41′44″W</t>
+  </si>
+  <si>
+    <t>Peterson Space Force Base</t>
+  </si>
+  <si>
+    <t>38°49′25″N 104°41′42″W</t>
+  </si>
+  <si>
+    <t>Pittsburgh International Airport Air Reserve Station</t>
+  </si>
+  <si>
+    <t>40°29′40.49″N 080°12′55.71″W</t>
+  </si>
+  <si>
+    <t>Portland Air National Guard Base</t>
+  </si>
+  <si>
+    <t>45°34′56″N 122°35′23″W</t>
+  </si>
+  <si>
+    <t>Quonset Point Air National Guard Station</t>
+  </si>
+  <si>
+    <t>North Kingstown</t>
+  </si>
+  <si>
+    <t>41°35′50″N 071°24′44″W</t>
+  </si>
+  <si>
+    <t>Reno Air National Guard Base</t>
+  </si>
+  <si>
+    <t>39°29′57″N 119°46′05″W</t>
+  </si>
+  <si>
+    <t>Rickenbacker Air National Guard Base</t>
+  </si>
+  <si>
+    <t>39°48′49″N 082°56′48″W</t>
+  </si>
+  <si>
+    <t>Roland R. Wright Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Salt Lake City</t>
+  </si>
+  <si>
+    <t>40°47′18″N 111°58′40″W</t>
+  </si>
+  <si>
+    <t>Rosecrans Air National Guard Base</t>
+  </si>
+  <si>
+    <t>St. Joseph</t>
+  </si>
+  <si>
+    <t>39°46′19″N 94°54′34.94″W</t>
+  </si>
+  <si>
+    <t>San Diego Air National Guard Station</t>
+  </si>
+  <si>
+    <t>32°50′10″N 117°9′38″W</t>
+  </si>
+  <si>
+    <t>Savannah Air National Guard Base</t>
+  </si>
+  <si>
+    <t>32°07′39″N 081°12′7″W</t>
+  </si>
+  <si>
+    <t>Schriever Space Force Base</t>
+  </si>
+  <si>
+    <t>38°48′12″N 104°31′32″W</t>
+  </si>
+  <si>
+    <t>Selfridge Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Mount Clemens</t>
+  </si>
+  <si>
+    <t>42°36′30″N 082°50′08″W</t>
+  </si>
+  <si>
+    <t>Sepulveda Air National Guard Station</t>
+  </si>
+  <si>
+    <t>Van Nuys</t>
+  </si>
+  <si>
+    <t>34°11′09.4″N 118°28′48″W</t>
+  </si>
+  <si>
+    <t>Shepherd Field Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Martinsburg</t>
+  </si>
+  <si>
+    <t>39°24′07″N 77°59′04″W</t>
+  </si>
+  <si>
+    <t>Sioux City Air National Guard Base</t>
+  </si>
+  <si>
+    <t>42°23′54″N 096°22′19″W</t>
+  </si>
+  <si>
+    <t>South Portland Air National Guard Station</t>
+  </si>
+  <si>
+    <t>43°38′00.9″N 70°18′58.7″W</t>
+  </si>
+  <si>
+    <t>Springfield Air National Guard Base</t>
+  </si>
+  <si>
+    <t>39°50′25″N 083°50′25″W</t>
+  </si>
+  <si>
+    <t>Stewart Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Newburgh</t>
+  </si>
+  <si>
+    <t>41°30′15″N 74°06′17″W</t>
+  </si>
+  <si>
+    <t>Stratton Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Schenectady</t>
+  </si>
+  <si>
+    <t>42°51′09″N 073°55′21″W</t>
+  </si>
+  <si>
+    <t>Sumpter Smith Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Birmingham</t>
+  </si>
+  <si>
+    <t>33°33′50″N 086°45′08″W</t>
+  </si>
+  <si>
+    <t>Toledo Air National Guard Base</t>
+  </si>
+  <si>
+    <t>41°35′12.5″N 83°48′28.2″W</t>
+  </si>
+  <si>
+    <t>Truax Field Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Madison</t>
+  </si>
+  <si>
+    <t>43°08′23″N 089°20′15″W</t>
+  </si>
+  <si>
+    <t>Tulsa Air National Guard Base</t>
+  </si>
+  <si>
+    <t>36°11′54″N 095°53′17″W</t>
+  </si>
+  <si>
+    <t>Volk Field Air National Guard Base</t>
+  </si>
+  <si>
+    <t>New Lisbon</t>
+  </si>
+  <si>
+    <t>43°56′11″N 090°15′35″W</t>
+  </si>
+  <si>
+    <t>Volunteer Air National Guard Station</t>
+  </si>
+  <si>
+    <t>Chattanooga</t>
+  </si>
+  <si>
+    <t>35°4′24.91″N 85°9′48.6″W</t>
+  </si>
+  <si>
+    <t>Warfield Air National Guard Base</t>
+  </si>
+  <si>
+    <t>Middle River</t>
+  </si>
+  <si>
+    <t>39°19′32.38″N 76°24′49.55″W</t>
+  </si>
+  <si>
+    <t>Westover Air Reserve Base</t>
+  </si>
+  <si>
+    <t>Chicopee</t>
+  </si>
+  <si>
+    <t>42°11′38″N 072°32′05″W</t>
+  </si>
+  <si>
+    <t>Will Rogers Air National Guard Base</t>
+  </si>
+  <si>
+    <t>35°23′35″N 097°36′03″W</t>
+  </si>
+  <si>
+    <t>Wyoming Air National Guard Base</t>
+  </si>
+  <si>
+    <t>41°09′41″N 104°49′10″W</t>
+  </si>
+  <si>
+    <t>Youngstown Air Reserve Station</t>
+  </si>
+  <si>
+    <t>41°15′38.64″N 80°40′44.74″W</t>
+  </si>
+  <si>
+    <t>Zanesville Air National Guard Base</t>
+  </si>
+  <si>
+    <t>39°56′47.6″N 81°53′58.1″W</t>
+  </si>
+  <si>
+    <t>Guantanamo Bay</t>
+  </si>
+  <si>
+    <t>Guantanamo Bay Naval Base</t>
+  </si>
+  <si>
+    <t>19°54′0″N 75°9′0″W</t>
+  </si>
+  <si>
+    <t>Hato International Airport</t>
+  </si>
+  <si>
+    <t>12°11′20″N 068°57′35″W</t>
+  </si>
+  <si>
+    <t>Muñiz Air National Guard Base</t>
+  </si>
+  <si>
+    <t>18°26′22″N 066°00′07″W</t>
+  </si>
+  <si>
+    <t>Punta Borinquen Radar Station</t>
+  </si>
+  <si>
+    <t>18°29′6″N 67°8′56″W</t>
+  </si>
+  <si>
+    <t>Punta Salinas Air National Guard Station</t>
+  </si>
+  <si>
+    <t>18°22′30″N 066°15′42″W</t>
+  </si>
+  <si>
+    <t>Queen Beatrix International Airport</t>
+  </si>
+  <si>
+    <t>12°30′05″N 70°00′55″W</t>
+  </si>
+  <si>
+    <t>Soto Cano Air Base</t>
+  </si>
+  <si>
+    <t>14°22′57″N 087°37′16″W</t>
+  </si>
+  <si>
+    <t>St Croix Air National Guard Station</t>
+  </si>
+  <si>
+    <t>17°42′24.2″N 64°48′01.9″W</t>
+  </si>
+  <si>
+    <t>Ämari Air Base</t>
+  </si>
+  <si>
+    <t>59°15′44″N 024°13′07″E</t>
+  </si>
+  <si>
+    <t>Aviano Air Base</t>
+  </si>
+  <si>
+    <t>46°01′53″N 012°35′49″E</t>
+  </si>
+  <si>
+    <t>Büchel Air Base</t>
+  </si>
+  <si>
+    <t>50°10′35″N 007°03′28″E</t>
+  </si>
+  <si>
+    <t>Camp Darby</t>
+  </si>
+  <si>
+    <t>43°38′0″N 10°19′0″E</t>
+  </si>
+  <si>
+    <t>Camp Lemonnier</t>
+  </si>
+  <si>
+    <t>11°32′37″N 43°8′55″E</t>
+  </si>
+  <si>
+    <t>Camp Simba</t>
+  </si>
+  <si>
+    <t>2°09′56.8″S 40°53′40.1″E</t>
+  </si>
+  <si>
+    <t>Câmpia Turzii (71st Air Base)</t>
+  </si>
+  <si>
+    <t>46°30′12″N 023°53′07″E</t>
+  </si>
+  <si>
+    <t>Chabelley Airfield</t>
+  </si>
+  <si>
+    <t>11°31′N 43°04′E</t>
+  </si>
+  <si>
+    <t>Chièvres Air Base</t>
+  </si>
+  <si>
+    <t>50°35′9.58″N 003°50′37.47″E</t>
+  </si>
+  <si>
+    <t>Einsiedlerhof Air Station</t>
+  </si>
+  <si>
+    <t>49°25′42.7″N 7°3′15.5″E</t>
+  </si>
+  <si>
+    <t>Ghedi Air Base</t>
+  </si>
+  <si>
+    <t>45°25′52.57″N 10°16′48.40″E</t>
+  </si>
+  <si>
+    <t>Incirlik Air Base</t>
+  </si>
+  <si>
+    <t>37°00′07″N 035°25′33″E</t>
+  </si>
+  <si>
+    <t>Izmir Air Station</t>
+  </si>
+  <si>
+    <t>38°27′27″N 027°10′13″E</t>
+  </si>
+  <si>
+    <t>Kleine Brogel Air Base</t>
+  </si>
+  <si>
+    <t>51°10′10.5″N 005°28′19″E</t>
+  </si>
+  <si>
+    <t>Lajes Field</t>
+  </si>
+  <si>
+    <t>38°45′42″N 027°05′26″W</t>
+  </si>
+  <si>
+    <t>Łask Air Base</t>
+  </si>
+  <si>
+    <t>51°33′5.76″N 19°10′44.76″E</t>
+  </si>
+  <si>
+    <t>Morón Air Base</t>
+  </si>
+  <si>
+    <t>37°10′29″N 5°36′57″W</t>
+  </si>
+  <si>
+    <t>NATO Air Base Geilenkirchen</t>
+  </si>
+  <si>
+    <t>50°57′39″N 6°2′33″E</t>
+  </si>
+  <si>
+    <t>RAF Akrotiri</t>
+  </si>
+  <si>
+    <t>34°35′0″N 32°59′0″E</t>
+  </si>
+  <si>
+    <t>RAF Alconbury</t>
+  </si>
+  <si>
+    <t>52°22′15.27″N 000°13′36.94″W</t>
+  </si>
+  <si>
+    <t>RAF Barford St John</t>
+  </si>
+  <si>
+    <t>52°0′13″N 1°21′36″W</t>
+  </si>
+  <si>
+    <t>RAF Croughton</t>
+  </si>
+  <si>
+    <t>51°59′15″N 1°11′10″W</t>
+  </si>
+  <si>
+    <t>RAF Fairford</t>
+  </si>
+  <si>
+    <t>51°40′56″N 1°47′24″W</t>
+  </si>
+  <si>
+    <t>RAF Feltwell</t>
+  </si>
+  <si>
+    <t>52°28′46″N 0°31′9″E</t>
+  </si>
+  <si>
+    <t>RAF Lakenheath</t>
+  </si>
+  <si>
+    <t>52°24′30″N 000°33′24″E</t>
+  </si>
+  <si>
+    <t>RAF Menwith Hill</t>
+  </si>
+  <si>
+    <t>54°0′28.35″N 1°41′22.2″W</t>
+  </si>
+  <si>
+    <t>RAF Mildenhall</t>
+  </si>
+  <si>
+    <t>52°21′54″N 000°28′51″E</t>
+  </si>
+  <si>
+    <t>RAF Molesworth</t>
+  </si>
+  <si>
+    <t>52°22′46″N 0°24′18″W</t>
+  </si>
+  <si>
+    <t>RAF Welford</t>
+  </si>
+  <si>
+    <t>51°28′6″N 1°24′13″W</t>
+  </si>
+  <si>
+    <t>Ramstein Air Base</t>
+  </si>
+  <si>
+    <t>49°26′38.10″N 007°36′08.13″E</t>
+  </si>
+  <si>
+    <t>Spangdahlem Air Base</t>
+  </si>
+  <si>
+    <t>49°58′33″N 006°41′50″E</t>
+  </si>
+  <si>
+    <t>Stavanger</t>
+  </si>
+  <si>
+    <t>58°54′27″N 5°43′18″E</t>
+  </si>
+  <si>
+    <t>Volkel Air Base</t>
+  </si>
+  <si>
+    <t>51°39′26″N 5°41′27″E</t>
+  </si>
+  <si>
+    <t>Abdullah Al Mubarak Air Base (Cargo City)</t>
+  </si>
+  <si>
+    <t>29°13′36″N 047°58′48″E</t>
+  </si>
+  <si>
+    <t>Al Dhafra Air Base</t>
+  </si>
+  <si>
+    <t>24°14′53″N 054°32′51″E</t>
+  </si>
+  <si>
+    <t>Al Udeid Air Base</t>
+  </si>
+  <si>
+    <t>25°07′02″N 051°18′53″E</t>
+  </si>
+  <si>
+    <t>Muwaffaq Salti Air Base</t>
+  </si>
+  <si>
+    <t>31°50′03″N 036°47′14″E</t>
+  </si>
+  <si>
+    <t>Prince Sultan Air Base</t>
+  </si>
+  <si>
+    <t>24°03′19″N 047°33′49″E</t>
+  </si>
+  <si>
+    <t>Cuba</t>
+  </si>
+  <si>
+    <t>Puerto Rico</t>
+  </si>
+  <si>
+    <t>Aruba</t>
+  </si>
+  <si>
+    <t>Honduras</t>
+  </si>
+  <si>
+    <t>United States Virgin Islands</t>
+  </si>
+  <si>
+    <t>Estonia</t>
+  </si>
+  <si>
+    <t>Turkey</t>
+  </si>
+  <si>
+    <t>Italy</t>
+  </si>
+  <si>
+    <t>Germany</t>
+  </si>
+  <si>
+    <t>Djibouti</t>
+  </si>
+  <si>
+    <t>Kenya</t>
+  </si>
+  <si>
+    <t>Romania</t>
+  </si>
+  <si>
+    <t>Belgium</t>
+  </si>
+  <si>
+    <t>Azores</t>
+  </si>
+  <si>
+    <t>Poland</t>
+  </si>
+  <si>
+    <t>Spain</t>
+  </si>
+  <si>
+    <t>Sovereign Base Areas of Akrotiri and Dhekelia</t>
+  </si>
+  <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
+    <t>Norway</t>
+  </si>
+  <si>
+    <t>Netherlands</t>
+  </si>
+  <si>
+    <t>Kuwait</t>
+  </si>
+  <si>
+    <t>United Arab Emirates</t>
+  </si>
+  <si>
+    <t>Qatar</t>
+  </si>
+  <si>
+    <t>Jordan</t>
+  </si>
+  <si>
+    <t>Saudi Arabia</t>
+  </si>
+  <si>
+    <t>Curaçao</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Willemstad</t>
+  </si>
+  <si>
+    <t>Carolina</t>
+  </si>
+  <si>
+    <t>Aguadilla</t>
+  </si>
+  <si>
+    <t>Toa Alta</t>
+  </si>
+  <si>
+    <t>Oranjestad</t>
+  </si>
+  <si>
+    <t>Comayagua</t>
+  </si>
+  <si>
+    <t>Frederiksted Southeast</t>
+  </si>
+  <si>
+    <t>Aviano</t>
+  </si>
+  <si>
+    <t>Alflen</t>
+  </si>
+  <si>
+    <t>Pisa</t>
+  </si>
+  <si>
+    <t>Ambouli</t>
+  </si>
+  <si>
+    <t>Jipe</t>
+  </si>
+  <si>
+    <t>Călărași-Gară</t>
+  </si>
+  <si>
+    <t>Chabelley</t>
+  </si>
+  <si>
+    <t>Brugelette</t>
+  </si>
+  <si>
+    <t>Marpingen</t>
+  </si>
+  <si>
+    <t>Ghedi</t>
+  </si>
+  <si>
+    <t>Sarıçam</t>
+  </si>
+  <si>
+    <t>Bayraklı</t>
+  </si>
+  <si>
+    <t>Peer</t>
+  </si>
+  <si>
+    <t>Lajes</t>
+  </si>
+  <si>
+    <t>Mauryca</t>
+  </si>
+  <si>
+    <t>Los Molares</t>
+  </si>
+  <si>
+    <t>Geilenkirchen</t>
+  </si>
+  <si>
+    <t>Akrotiri</t>
+  </si>
+  <si>
+    <t>Huntingdon</t>
+  </si>
+  <si>
+    <t>Banbury</t>
+  </si>
+  <si>
+    <t>Brackley</t>
+  </si>
+  <si>
+    <t>Fairford</t>
+  </si>
+  <si>
+    <t>Thetford</t>
+  </si>
+  <si>
+    <t>Brandon</t>
+  </si>
+  <si>
+    <t>Harrogate</t>
+  </si>
+  <si>
+    <t>Bury Saint Edmunds</t>
+  </si>
+  <si>
+    <t>Newbury</t>
+  </si>
+  <si>
+    <t>Ramstein-Miesenbach</t>
+  </si>
+  <si>
+    <t>Spangdahlem</t>
+  </si>
+  <si>
+    <t>Volkel</t>
+  </si>
+  <si>
+    <t>Al-Dajeej</t>
+  </si>
+  <si>
+    <t>Abu Dhabi</t>
+  </si>
+  <si>
+    <t>Abū Nakẖlah</t>
+  </si>
+  <si>
+    <t>Azraq</t>
+  </si>
+  <si>
+    <t>Al-Kharj</t>
+  </si>
+  <si>
+    <r>
+      <t>Äm</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ari </t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -641,6 +2747,24 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <u/>
+      <sz val="18"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -703,7 +2827,7 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -786,6 +2910,10 @@
     <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="4" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="49" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="20% - Accent1" xfId="2" builtinId="30"/>
@@ -811,6 +2939,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="afb_excel_1" connectionId="1" xr16:uid="{4D6878E2-C1CF-2B46-B224-2C31EBB1CD5B}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="1" applyPatternFormats="1" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1931,6 +4063,3355 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{063F91C9-FF91-F443-A3C8-B989B963D99A}">
+  <dimension ref="A1:F211"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="48" style="35" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.1640625" style="35" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.83203125" style="35" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31" style="35" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.33203125" style="35" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="48" style="35" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="10.83203125" style="35"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="24" x14ac:dyDescent="0.3">
+      <c r="A1" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="36" t="s">
+        <v>392</v>
+      </c>
+      <c r="C1" s="36" t="s">
+        <v>783</v>
+      </c>
+      <c r="D1" s="36" t="s">
+        <v>393</v>
+      </c>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="B2" s="34" t="s">
+        <v>137</v>
+      </c>
+      <c r="C2" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="34" t="s">
+        <v>140</v>
+      </c>
+      <c r="B3" s="34" t="s">
+        <v>141</v>
+      </c>
+      <c r="C3" s="34" t="s">
+        <v>142</v>
+      </c>
+      <c r="D3" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="B4" s="34" t="s">
+        <v>145</v>
+      </c>
+      <c r="C4" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="D4" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="E4" s="34"/>
+      <c r="F4" s="34"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="D5" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="E5" s="34"/>
+      <c r="F5" s="34"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>153</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>157</v>
+      </c>
+      <c r="C7" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="D7" s="34" t="s">
+        <v>159</v>
+      </c>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="34" t="s">
+        <v>160</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>161</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>162</v>
+      </c>
+      <c r="D8" s="34" t="s">
+        <v>163</v>
+      </c>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="34" t="s">
+        <v>164</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>165</v>
+      </c>
+      <c r="C9" s="34" t="s">
+        <v>166</v>
+      </c>
+      <c r="D9" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="B10" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="C10" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="D10" s="34" t="s">
+        <v>171</v>
+      </c>
+      <c r="E10" s="34"/>
+      <c r="F10" s="34"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="B11" s="34" t="s">
+        <v>173</v>
+      </c>
+      <c r="C11" s="34" t="s">
+        <v>174</v>
+      </c>
+      <c r="D11" s="34" t="s">
+        <v>175</v>
+      </c>
+      <c r="E11" s="34"/>
+      <c r="F11" s="34"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>177</v>
+      </c>
+      <c r="C12" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="D12" s="34" t="s">
+        <v>179</v>
+      </c>
+      <c r="E12" s="34"/>
+      <c r="F12" s="34"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="34" t="s">
+        <v>180</v>
+      </c>
+      <c r="B13" s="34" t="s">
+        <v>181</v>
+      </c>
+      <c r="C13" s="34" t="s">
+        <v>182</v>
+      </c>
+      <c r="D13" s="34" t="s">
+        <v>183</v>
+      </c>
+      <c r="E13" s="34"/>
+      <c r="F13" s="34"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="34" t="s">
+        <v>184</v>
+      </c>
+      <c r="B14" s="34" t="s">
+        <v>185</v>
+      </c>
+      <c r="C14" s="34" t="s">
+        <v>186</v>
+      </c>
+      <c r="D14" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="34" t="s">
+        <v>188</v>
+      </c>
+      <c r="B15" s="34" t="s">
+        <v>189</v>
+      </c>
+      <c r="C15" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="D15" s="34" t="s">
+        <v>190</v>
+      </c>
+      <c r="E15" s="34"/>
+      <c r="F15" s="34"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="34" t="s">
+        <v>191</v>
+      </c>
+      <c r="B16" s="34" t="s">
+        <v>192</v>
+      </c>
+      <c r="C16" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="D16" s="34" t="s">
+        <v>194</v>
+      </c>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="34" t="s">
+        <v>195</v>
+      </c>
+      <c r="B17" s="34" t="s">
+        <v>196</v>
+      </c>
+      <c r="C17" s="34" t="s">
+        <v>197</v>
+      </c>
+      <c r="D17" s="34" t="s">
+        <v>198</v>
+      </c>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="34" t="s">
+        <v>199</v>
+      </c>
+      <c r="B18" s="34" t="s">
+        <v>200</v>
+      </c>
+      <c r="C18" s="34" t="s">
+        <v>201</v>
+      </c>
+      <c r="D18" s="34" t="s">
+        <v>202</v>
+      </c>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="34" t="s">
+        <v>203</v>
+      </c>
+      <c r="B19" s="34" t="s">
+        <v>204</v>
+      </c>
+      <c r="C19" s="34" t="s">
+        <v>205</v>
+      </c>
+      <c r="D19" s="34" t="s">
+        <v>206</v>
+      </c>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="34" t="s">
+        <v>207</v>
+      </c>
+      <c r="B20" s="34" t="s">
+        <v>208</v>
+      </c>
+      <c r="C20" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="D20" s="34" t="s">
+        <v>209</v>
+      </c>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="34" t="s">
+        <v>210</v>
+      </c>
+      <c r="B21" s="34" t="s">
+        <v>211</v>
+      </c>
+      <c r="C21" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="D21" s="34" t="s">
+        <v>212</v>
+      </c>
+      <c r="E21" s="34"/>
+      <c r="F21" s="34"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="34" t="s">
+        <v>213</v>
+      </c>
+      <c r="B22" s="34" t="s">
+        <v>214</v>
+      </c>
+      <c r="C22" s="34" t="s">
+        <v>186</v>
+      </c>
+      <c r="D22" s="34" t="s">
+        <v>215</v>
+      </c>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="34" t="s">
+        <v>216</v>
+      </c>
+      <c r="B23" s="34" t="s">
+        <v>217</v>
+      </c>
+      <c r="C23" s="34" t="s">
+        <v>218</v>
+      </c>
+      <c r="D23" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="B24" s="34" t="s">
+        <v>221</v>
+      </c>
+      <c r="C24" s="34" t="s">
+        <v>222</v>
+      </c>
+      <c r="D24" s="34" t="s">
+        <v>223</v>
+      </c>
+      <c r="E24" s="34"/>
+      <c r="F24" s="34"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="34" t="s">
+        <v>224</v>
+      </c>
+      <c r="B25" s="34" t="s">
+        <v>225</v>
+      </c>
+      <c r="C25" s="34" t="s">
+        <v>226</v>
+      </c>
+      <c r="D25" s="34" t="s">
+        <v>227</v>
+      </c>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="34" t="s">
+        <v>228</v>
+      </c>
+      <c r="B26" s="34" t="s">
+        <v>229</v>
+      </c>
+      <c r="C26" s="34" t="s">
+        <v>174</v>
+      </c>
+      <c r="D26" s="34" t="s">
+        <v>230</v>
+      </c>
+      <c r="E26" s="34"/>
+      <c r="F26" s="34"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="34" t="s">
+        <v>231</v>
+      </c>
+      <c r="B27" s="34" t="s">
+        <v>232</v>
+      </c>
+      <c r="C27" s="34" t="s">
+        <v>162</v>
+      </c>
+      <c r="D27" s="34" t="s">
+        <v>233</v>
+      </c>
+      <c r="E27" s="34"/>
+      <c r="F27" s="34"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="34" t="s">
+        <v>234</v>
+      </c>
+      <c r="B28" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="C28" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="D28" s="34" t="s">
+        <v>236</v>
+      </c>
+      <c r="E28" s="34"/>
+      <c r="F28" s="34"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="34" t="s">
+        <v>237</v>
+      </c>
+      <c r="B29" s="34" t="s">
+        <v>238</v>
+      </c>
+      <c r="C29" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="D29" s="34" t="s">
+        <v>239</v>
+      </c>
+      <c r="E29" s="34"/>
+      <c r="F29" s="34"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="34" t="s">
+        <v>240</v>
+      </c>
+      <c r="B30" s="34" t="s">
+        <v>241</v>
+      </c>
+      <c r="C30" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="D30" s="34" t="s">
+        <v>242</v>
+      </c>
+      <c r="E30" s="34"/>
+      <c r="F30" s="34"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="34" t="s">
+        <v>243</v>
+      </c>
+      <c r="B31" s="34" t="s">
+        <v>244</v>
+      </c>
+      <c r="C31" s="34" t="s">
+        <v>162</v>
+      </c>
+      <c r="D31" s="34" t="s">
+        <v>245</v>
+      </c>
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="34" t="s">
+        <v>246</v>
+      </c>
+      <c r="B32" s="34" t="s">
+        <v>247</v>
+      </c>
+      <c r="C32" s="34" t="s">
+        <v>248</v>
+      </c>
+      <c r="D32" s="34" t="s">
+        <v>249</v>
+      </c>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="34" t="s">
+        <v>250</v>
+      </c>
+      <c r="B33" s="34" t="s">
+        <v>251</v>
+      </c>
+      <c r="C33" s="34" t="s">
+        <v>186</v>
+      </c>
+      <c r="D33" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="34" t="s">
+        <v>253</v>
+      </c>
+      <c r="B34" s="34" t="s">
+        <v>254</v>
+      </c>
+      <c r="C34" s="34" t="s">
+        <v>205</v>
+      </c>
+      <c r="D34" s="34" t="s">
+        <v>255</v>
+      </c>
+      <c r="E34" s="34"/>
+      <c r="F34" s="34"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="34" t="s">
+        <v>256</v>
+      </c>
+      <c r="B35" s="34" t="s">
+        <v>257</v>
+      </c>
+      <c r="C35" s="34" t="s">
+        <v>258</v>
+      </c>
+      <c r="D35" s="34" t="s">
+        <v>259</v>
+      </c>
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="34" t="s">
+        <v>260</v>
+      </c>
+      <c r="B36" s="34" t="s">
+        <v>261</v>
+      </c>
+      <c r="C36" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="D36" s="34" t="s">
+        <v>262</v>
+      </c>
+      <c r="E36" s="34"/>
+      <c r="F36" s="34"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="34" t="s">
+        <v>263</v>
+      </c>
+      <c r="B37" s="34" t="s">
+        <v>264</v>
+      </c>
+      <c r="C37" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="D37" s="34" t="s">
+        <v>265</v>
+      </c>
+      <c r="E37" s="34"/>
+      <c r="F37" s="34"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="34" t="s">
+        <v>266</v>
+      </c>
+      <c r="B38" s="34" t="s">
+        <v>267</v>
+      </c>
+      <c r="C38" s="34" t="s">
+        <v>268</v>
+      </c>
+      <c r="D38" s="34" t="s">
+        <v>269</v>
+      </c>
+      <c r="E38" s="34"/>
+      <c r="F38" s="34"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="B39" s="34" t="s">
+        <v>271</v>
+      </c>
+      <c r="C39" s="34" t="s">
+        <v>272</v>
+      </c>
+      <c r="D39" s="34" t="s">
+        <v>273</v>
+      </c>
+      <c r="E39" s="34"/>
+      <c r="F39" s="34"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="34" t="s">
+        <v>274</v>
+      </c>
+      <c r="B40" s="34" t="s">
+        <v>275</v>
+      </c>
+      <c r="C40" s="34" t="s">
+        <v>276</v>
+      </c>
+      <c r="D40" s="34" t="s">
+        <v>277</v>
+      </c>
+      <c r="E40" s="34"/>
+      <c r="F40" s="34"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="34" t="s">
+        <v>278</v>
+      </c>
+      <c r="B41" s="34" t="s">
+        <v>279</v>
+      </c>
+      <c r="C41" s="34" t="s">
+        <v>280</v>
+      </c>
+      <c r="D41" s="34" t="s">
+        <v>281</v>
+      </c>
+      <c r="E41" s="34"/>
+      <c r="F41" s="34"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="34" t="s">
+        <v>282</v>
+      </c>
+      <c r="B42" s="34" t="s">
+        <v>283</v>
+      </c>
+      <c r="C42" s="34" t="s">
+        <v>218</v>
+      </c>
+      <c r="D42" s="34" t="s">
+        <v>284</v>
+      </c>
+      <c r="E42" s="34"/>
+      <c r="F42" s="34"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="34" t="s">
+        <v>285</v>
+      </c>
+      <c r="B43" s="34" t="s">
+        <v>286</v>
+      </c>
+      <c r="C43" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="D43" s="34" t="s">
+        <v>288</v>
+      </c>
+      <c r="E43" s="34"/>
+      <c r="F43" s="34"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="34" t="s">
+        <v>289</v>
+      </c>
+      <c r="B44" s="34" t="s">
+        <v>290</v>
+      </c>
+      <c r="C44" s="34" t="s">
+        <v>291</v>
+      </c>
+      <c r="D44" s="34" t="s">
+        <v>292</v>
+      </c>
+      <c r="E44" s="34"/>
+      <c r="F44" s="34"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="34" t="s">
+        <v>293</v>
+      </c>
+      <c r="B45" s="34" t="s">
+        <v>294</v>
+      </c>
+      <c r="C45" s="34" t="s">
+        <v>174</v>
+      </c>
+      <c r="D45" s="34" t="s">
+        <v>295</v>
+      </c>
+      <c r="E45" s="34"/>
+      <c r="F45" s="34"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="34" t="s">
+        <v>296</v>
+      </c>
+      <c r="B46" s="34" t="s">
+        <v>297</v>
+      </c>
+      <c r="C46" s="34" t="s">
+        <v>166</v>
+      </c>
+      <c r="D46" s="34" t="s">
+        <v>298</v>
+      </c>
+      <c r="E46" s="34"/>
+      <c r="F46" s="34"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="34" t="s">
+        <v>299</v>
+      </c>
+      <c r="B47" s="34" t="s">
+        <v>300</v>
+      </c>
+      <c r="C47" s="34" t="s">
+        <v>301</v>
+      </c>
+      <c r="D47" s="34" t="s">
+        <v>302</v>
+      </c>
+      <c r="E47" s="34"/>
+      <c r="F47" s="34"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="34" t="s">
+        <v>303</v>
+      </c>
+      <c r="B48" s="34" t="s">
+        <v>304</v>
+      </c>
+      <c r="C48" s="34" t="s">
+        <v>305</v>
+      </c>
+      <c r="D48" s="34" t="s">
+        <v>306</v>
+      </c>
+      <c r="E48" s="34"/>
+      <c r="F48" s="34"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="34" t="s">
+        <v>307</v>
+      </c>
+      <c r="B49" s="34" t="s">
+        <v>308</v>
+      </c>
+      <c r="C49" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="D49" s="34" t="s">
+        <v>309</v>
+      </c>
+      <c r="E49" s="34"/>
+      <c r="F49" s="34"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="34" t="s">
+        <v>310</v>
+      </c>
+      <c r="B50" s="34" t="s">
+        <v>311</v>
+      </c>
+      <c r="C50" s="34" t="s">
+        <v>312</v>
+      </c>
+      <c r="D50" s="34" t="s">
+        <v>313</v>
+      </c>
+      <c r="E50" s="34"/>
+      <c r="F50" s="34"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="34" t="s">
+        <v>314</v>
+      </c>
+      <c r="B51" s="34" t="s">
+        <v>315</v>
+      </c>
+      <c r="C51" s="34" t="s">
+        <v>186</v>
+      </c>
+      <c r="D51" s="34" t="s">
+        <v>316</v>
+      </c>
+      <c r="E51" s="34"/>
+      <c r="F51" s="34"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="34" t="s">
+        <v>317</v>
+      </c>
+      <c r="B52" s="34" t="s">
+        <v>318</v>
+      </c>
+      <c r="C52" s="34" t="s">
+        <v>319</v>
+      </c>
+      <c r="D52" s="34" t="s">
+        <v>320</v>
+      </c>
+      <c r="E52" s="34"/>
+      <c r="F52" s="34"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="34" t="s">
+        <v>321</v>
+      </c>
+      <c r="B53" s="34" t="s">
+        <v>322</v>
+      </c>
+      <c r="C53" s="34" t="s">
+        <v>305</v>
+      </c>
+      <c r="D53" s="34" t="s">
+        <v>323</v>
+      </c>
+      <c r="E53" s="34"/>
+      <c r="F53" s="34"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="34" t="s">
+        <v>324</v>
+      </c>
+      <c r="B54" s="34" t="s">
+        <v>325</v>
+      </c>
+      <c r="C54" s="34" t="s">
+        <v>166</v>
+      </c>
+      <c r="D54" s="34" t="s">
+        <v>326</v>
+      </c>
+      <c r="E54" s="34"/>
+      <c r="F54" s="34"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="34" t="s">
+        <v>327</v>
+      </c>
+      <c r="B55" s="34" t="s">
+        <v>328</v>
+      </c>
+      <c r="C55" s="34" t="s">
+        <v>186</v>
+      </c>
+      <c r="D55" s="34" t="s">
+        <v>329</v>
+      </c>
+      <c r="E55" s="34"/>
+      <c r="F55" s="34"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="34" t="s">
+        <v>330</v>
+      </c>
+      <c r="B56" s="34" t="s">
+        <v>331</v>
+      </c>
+      <c r="C56" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="D56" s="34" t="s">
+        <v>332</v>
+      </c>
+      <c r="E56" s="34"/>
+      <c r="F56" s="34"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="34" t="s">
+        <v>333</v>
+      </c>
+      <c r="B57" s="34" t="s">
+        <v>334</v>
+      </c>
+      <c r="C57" s="34" t="s">
+        <v>174</v>
+      </c>
+      <c r="D57" s="34" t="s">
+        <v>335</v>
+      </c>
+      <c r="E57" s="34"/>
+      <c r="F57" s="34"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="34" t="s">
+        <v>336</v>
+      </c>
+      <c r="B58" s="34" t="s">
+        <v>337</v>
+      </c>
+      <c r="C58" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="D58" s="34" t="s">
+        <v>338</v>
+      </c>
+      <c r="E58" s="34"/>
+      <c r="F58" s="34"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="34" t="s">
+        <v>339</v>
+      </c>
+      <c r="B59" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="C59" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="D59" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="E59" s="34"/>
+      <c r="F59" s="34"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="34" t="s">
+        <v>342</v>
+      </c>
+      <c r="B60" s="34" t="s">
+        <v>343</v>
+      </c>
+      <c r="C60" s="34" t="s">
+        <v>344</v>
+      </c>
+      <c r="D60" s="34" t="s">
+        <v>345</v>
+      </c>
+      <c r="E60" s="34"/>
+      <c r="F60" s="34"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="34" t="s">
+        <v>346</v>
+      </c>
+      <c r="B61" s="34" t="s">
+        <v>347</v>
+      </c>
+      <c r="C61" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="D61" s="34" t="s">
+        <v>348</v>
+      </c>
+      <c r="E61" s="34"/>
+      <c r="F61" s="34"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="34" t="s">
+        <v>349</v>
+      </c>
+      <c r="B62" s="34" t="s">
+        <v>350</v>
+      </c>
+      <c r="C62" s="34" t="s">
+        <v>351</v>
+      </c>
+      <c r="D62" s="34" t="s">
+        <v>352</v>
+      </c>
+      <c r="E62" s="34"/>
+      <c r="F62" s="34"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="34" t="s">
+        <v>353</v>
+      </c>
+      <c r="B63" s="34" t="s">
+        <v>354</v>
+      </c>
+      <c r="C63" s="34" t="s">
+        <v>355</v>
+      </c>
+      <c r="D63" s="34" t="s">
+        <v>356</v>
+      </c>
+      <c r="E63" s="34"/>
+      <c r="F63" s="34"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="34" t="s">
+        <v>394</v>
+      </c>
+      <c r="B64" s="34" t="s">
+        <v>271</v>
+      </c>
+      <c r="C64" s="34" t="s">
+        <v>272</v>
+      </c>
+      <c r="D64" s="34" t="s">
+        <v>395</v>
+      </c>
+      <c r="E64" s="34"/>
+      <c r="F64" s="34"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="34" t="s">
+        <v>396</v>
+      </c>
+      <c r="B65" s="34" t="s">
+        <v>397</v>
+      </c>
+      <c r="C65" s="34" t="s">
+        <v>280</v>
+      </c>
+      <c r="D65" s="34" t="s">
+        <v>398</v>
+      </c>
+      <c r="E65" s="34"/>
+      <c r="F65" s="34"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="34" t="s">
+        <v>399</v>
+      </c>
+      <c r="B66" s="34" t="s">
+        <v>372</v>
+      </c>
+      <c r="C66" s="34" t="s">
+        <v>400</v>
+      </c>
+      <c r="D66" s="34" t="s">
+        <v>401</v>
+      </c>
+      <c r="E66" s="34"/>
+      <c r="F66" s="34"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="34" t="s">
+        <v>402</v>
+      </c>
+      <c r="B67" s="34" t="s">
+        <v>403</v>
+      </c>
+      <c r="C67" s="34" t="s">
+        <v>222</v>
+      </c>
+      <c r="D67" s="34" t="s">
+        <v>404</v>
+      </c>
+      <c r="E67" s="34"/>
+      <c r="F67" s="34"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="34" t="s">
+        <v>405</v>
+      </c>
+      <c r="B68" s="34" t="s">
+        <v>381</v>
+      </c>
+      <c r="C68" s="34" t="s">
+        <v>406</v>
+      </c>
+      <c r="D68" s="34" t="s">
+        <v>407</v>
+      </c>
+      <c r="E68" s="34"/>
+      <c r="F68" s="34"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="34" t="s">
+        <v>408</v>
+      </c>
+      <c r="B69" s="34" t="s">
+        <v>409</v>
+      </c>
+      <c r="C69" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="D69" s="34" t="s">
+        <v>410</v>
+      </c>
+      <c r="E69" s="34"/>
+      <c r="F69" s="34"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="34" t="s">
+        <v>411</v>
+      </c>
+      <c r="B70" s="34" t="s">
+        <v>412</v>
+      </c>
+      <c r="C70" s="34" t="s">
+        <v>413</v>
+      </c>
+      <c r="D70" s="34" t="s">
+        <v>414</v>
+      </c>
+      <c r="E70" s="34"/>
+      <c r="F70" s="34"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="34" t="s">
+        <v>415</v>
+      </c>
+      <c r="B71" s="34" t="s">
+        <v>416</v>
+      </c>
+      <c r="C71" s="34" t="s">
+        <v>417</v>
+      </c>
+      <c r="D71" s="34" t="s">
+        <v>418</v>
+      </c>
+      <c r="E71" s="34"/>
+      <c r="F71" s="34"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="34" t="s">
+        <v>419</v>
+      </c>
+      <c r="B72" s="34" t="s">
+        <v>420</v>
+      </c>
+      <c r="C72" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="D72" s="34" t="s">
+        <v>421</v>
+      </c>
+      <c r="E72" s="34"/>
+      <c r="F72" s="34"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="34" t="s">
+        <v>422</v>
+      </c>
+      <c r="B73" s="34" t="s">
+        <v>389</v>
+      </c>
+      <c r="C73" s="34" t="s">
+        <v>423</v>
+      </c>
+      <c r="D73" s="34" t="s">
+        <v>424</v>
+      </c>
+      <c r="E73" s="34"/>
+      <c r="F73" s="34"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="34" t="s">
+        <v>425</v>
+      </c>
+      <c r="B74" s="34" t="s">
+        <v>254</v>
+      </c>
+      <c r="C74" s="34" t="s">
+        <v>205</v>
+      </c>
+      <c r="D74" s="34" t="s">
+        <v>426</v>
+      </c>
+      <c r="E74" s="34"/>
+      <c r="F74" s="34"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="34" t="s">
+        <v>385</v>
+      </c>
+      <c r="B75" s="34" t="s">
+        <v>427</v>
+      </c>
+      <c r="C75" s="34" t="s">
+        <v>428</v>
+      </c>
+      <c r="D75" s="34" t="s">
+        <v>429</v>
+      </c>
+      <c r="E75" s="34"/>
+      <c r="F75" s="34"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="34" t="s">
+        <v>430</v>
+      </c>
+      <c r="B76" s="34" t="s">
+        <v>381</v>
+      </c>
+      <c r="C76" s="34" t="s">
+        <v>319</v>
+      </c>
+      <c r="D76" s="34" t="s">
+        <v>431</v>
+      </c>
+      <c r="E76" s="34"/>
+      <c r="F76" s="34"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="34" t="s">
+        <v>432</v>
+      </c>
+      <c r="B77" s="34" t="s">
+        <v>433</v>
+      </c>
+      <c r="C77" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="D77" s="34" t="s">
+        <v>434</v>
+      </c>
+      <c r="E77" s="34"/>
+      <c r="F77" s="34"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="34" t="s">
+        <v>435</v>
+      </c>
+      <c r="B78" s="34" t="s">
+        <v>378</v>
+      </c>
+      <c r="C78" s="34" t="s">
+        <v>305</v>
+      </c>
+      <c r="D78" s="34" t="s">
+        <v>436</v>
+      </c>
+      <c r="E78" s="34"/>
+      <c r="F78" s="34"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="34" t="s">
+        <v>437</v>
+      </c>
+      <c r="B79" s="34" t="s">
+        <v>438</v>
+      </c>
+      <c r="C79" s="34" t="s">
+        <v>186</v>
+      </c>
+      <c r="D79" s="34" t="s">
+        <v>439</v>
+      </c>
+      <c r="E79" s="34"/>
+      <c r="F79" s="34"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="34" t="s">
+        <v>440</v>
+      </c>
+      <c r="B80" s="34" t="s">
+        <v>369</v>
+      </c>
+      <c r="C80" s="34" t="s">
+        <v>441</v>
+      </c>
+      <c r="D80" s="34" t="s">
+        <v>442</v>
+      </c>
+      <c r="E80" s="34"/>
+      <c r="F80" s="34"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="34" t="s">
+        <v>443</v>
+      </c>
+      <c r="B81" s="34" t="s">
+        <v>444</v>
+      </c>
+      <c r="C81" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="D81" s="34" t="s">
+        <v>445</v>
+      </c>
+      <c r="E81" s="34"/>
+      <c r="F81" s="34"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="34" t="s">
+        <v>357</v>
+      </c>
+      <c r="B82" s="34" t="s">
+        <v>446</v>
+      </c>
+      <c r="C82" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="D82" s="34" t="s">
+        <v>447</v>
+      </c>
+      <c r="E82" s="34"/>
+      <c r="F82" s="34"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="34" t="s">
+        <v>448</v>
+      </c>
+      <c r="B83" s="34" t="s">
+        <v>374</v>
+      </c>
+      <c r="C83" s="34" t="s">
+        <v>449</v>
+      </c>
+      <c r="D83" s="34" t="s">
+        <v>450</v>
+      </c>
+      <c r="E83" s="34"/>
+      <c r="F83" s="34"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A84" s="34" t="s">
+        <v>451</v>
+      </c>
+      <c r="B84" s="34" t="s">
+        <v>311</v>
+      </c>
+      <c r="C84" s="34" t="s">
+        <v>312</v>
+      </c>
+      <c r="D84" s="34" t="s">
+        <v>452</v>
+      </c>
+      <c r="E84" s="34"/>
+      <c r="F84" s="34"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A85" s="34" t="s">
+        <v>453</v>
+      </c>
+      <c r="B85" s="34" t="s">
+        <v>454</v>
+      </c>
+      <c r="C85" s="34" t="s">
+        <v>258</v>
+      </c>
+      <c r="D85" s="34" t="s">
+        <v>455</v>
+      </c>
+      <c r="E85" s="34"/>
+      <c r="F85" s="34"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A86" s="34" t="s">
+        <v>456</v>
+      </c>
+      <c r="B86" s="34" t="s">
+        <v>457</v>
+      </c>
+      <c r="C86" s="34" t="s">
+        <v>186</v>
+      </c>
+      <c r="D86" s="34" t="s">
+        <v>458</v>
+      </c>
+      <c r="E86" s="34"/>
+      <c r="F86" s="34"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A87" s="34" t="s">
+        <v>459</v>
+      </c>
+      <c r="B87" s="34" t="s">
+        <v>380</v>
+      </c>
+      <c r="C87" s="34" t="s">
+        <v>218</v>
+      </c>
+      <c r="D87" s="34" t="s">
+        <v>460</v>
+      </c>
+      <c r="E87" s="34"/>
+      <c r="F87" s="34"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A88" s="34" t="s">
+        <v>461</v>
+      </c>
+      <c r="B88" s="34" t="s">
+        <v>462</v>
+      </c>
+      <c r="C88" s="34" t="s">
+        <v>276</v>
+      </c>
+      <c r="D88" s="34" t="s">
+        <v>463</v>
+      </c>
+      <c r="E88" s="34"/>
+      <c r="F88" s="34"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A89" s="34" t="s">
+        <v>388</v>
+      </c>
+      <c r="B89" s="34" t="s">
+        <v>464</v>
+      </c>
+      <c r="C89" s="34" t="s">
+        <v>186</v>
+      </c>
+      <c r="D89" s="34" t="s">
+        <v>465</v>
+      </c>
+      <c r="E89" s="34"/>
+      <c r="F89" s="34"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A90" s="34" t="s">
+        <v>466</v>
+      </c>
+      <c r="B90" s="34" t="s">
+        <v>370</v>
+      </c>
+      <c r="C90" s="34" t="s">
+        <v>441</v>
+      </c>
+      <c r="D90" s="34" t="s">
+        <v>467</v>
+      </c>
+      <c r="E90" s="34"/>
+      <c r="F90" s="34"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A91" s="34" t="s">
+        <v>468</v>
+      </c>
+      <c r="B91" s="34" t="s">
+        <v>368</v>
+      </c>
+      <c r="C91" s="34" t="s">
+        <v>469</v>
+      </c>
+      <c r="D91" s="34" t="s">
+        <v>470</v>
+      </c>
+      <c r="E91" s="34"/>
+      <c r="F91" s="34"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A92" s="34" t="s">
+        <v>471</v>
+      </c>
+      <c r="B92" s="34" t="s">
+        <v>472</v>
+      </c>
+      <c r="C92" s="34" t="s">
+        <v>186</v>
+      </c>
+      <c r="D92" s="34" t="s">
+        <v>473</v>
+      </c>
+      <c r="E92" s="34"/>
+      <c r="F92" s="34"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A93" s="34" t="s">
+        <v>474</v>
+      </c>
+      <c r="B93" s="34" t="s">
+        <v>475</v>
+      </c>
+      <c r="C93" s="34" t="s">
+        <v>312</v>
+      </c>
+      <c r="D93" s="34" t="s">
+        <v>476</v>
+      </c>
+      <c r="E93" s="34"/>
+      <c r="F93" s="34"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A94" s="34" t="s">
+        <v>477</v>
+      </c>
+      <c r="B94" s="34" t="s">
+        <v>362</v>
+      </c>
+      <c r="C94" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="D94" s="34" t="s">
+        <v>478</v>
+      </c>
+      <c r="E94" s="34"/>
+      <c r="F94" s="34"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A95" s="34" t="s">
+        <v>479</v>
+      </c>
+      <c r="B95" s="34" t="s">
+        <v>480</v>
+      </c>
+      <c r="C95" s="34" t="s">
+        <v>481</v>
+      </c>
+      <c r="D95" s="34" t="s">
+        <v>482</v>
+      </c>
+      <c r="E95" s="34"/>
+      <c r="F95" s="34"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A96" s="34" t="s">
+        <v>483</v>
+      </c>
+      <c r="B96" s="34" t="s">
+        <v>484</v>
+      </c>
+      <c r="C96" s="34" t="s">
+        <v>291</v>
+      </c>
+      <c r="D96" s="34" t="s">
+        <v>485</v>
+      </c>
+      <c r="E96" s="34"/>
+      <c r="F96" s="34"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A97" s="34" t="s">
+        <v>486</v>
+      </c>
+      <c r="B97" s="34" t="s">
+        <v>267</v>
+      </c>
+      <c r="C97" s="34" t="s">
+        <v>268</v>
+      </c>
+      <c r="D97" s="34" t="s">
+        <v>487</v>
+      </c>
+      <c r="E97" s="34"/>
+      <c r="F97" s="34"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A98" s="34" t="s">
+        <v>488</v>
+      </c>
+      <c r="B98" s="34" t="s">
+        <v>364</v>
+      </c>
+      <c r="C98" s="34" t="s">
+        <v>344</v>
+      </c>
+      <c r="D98" s="34" t="s">
+        <v>489</v>
+      </c>
+      <c r="E98" s="34"/>
+      <c r="F98" s="34"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A99" s="34" t="s">
+        <v>490</v>
+      </c>
+      <c r="B99" s="34" t="s">
+        <v>491</v>
+      </c>
+      <c r="C99" s="34" t="s">
+        <v>469</v>
+      </c>
+      <c r="D99" s="34" t="s">
+        <v>492</v>
+      </c>
+      <c r="E99" s="34"/>
+      <c r="F99" s="34"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A100" s="34" t="s">
+        <v>493</v>
+      </c>
+      <c r="B100" s="34" t="s">
+        <v>494</v>
+      </c>
+      <c r="C100" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="D100" s="34" t="s">
+        <v>495</v>
+      </c>
+      <c r="E100" s="34"/>
+      <c r="F100" s="34"/>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A101" s="34" t="s">
+        <v>496</v>
+      </c>
+      <c r="B101" s="34" t="s">
+        <v>375</v>
+      </c>
+      <c r="C101" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="D101" s="34" t="s">
+        <v>497</v>
+      </c>
+      <c r="E101" s="34"/>
+      <c r="F101" s="34"/>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A102" s="34" t="s">
+        <v>498</v>
+      </c>
+      <c r="B102" s="34" t="s">
+        <v>499</v>
+      </c>
+      <c r="C102" s="34" t="s">
+        <v>272</v>
+      </c>
+      <c r="D102" s="34" t="s">
+        <v>500</v>
+      </c>
+      <c r="E102" s="34"/>
+      <c r="F102" s="34"/>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A103" s="34" t="s">
+        <v>501</v>
+      </c>
+      <c r="B103" s="34" t="s">
+        <v>502</v>
+      </c>
+      <c r="C103" s="34" t="s">
+        <v>312</v>
+      </c>
+      <c r="D103" s="34" t="s">
+        <v>503</v>
+      </c>
+      <c r="E103" s="34"/>
+      <c r="F103" s="34"/>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A104" s="34" t="s">
+        <v>504</v>
+      </c>
+      <c r="B104" s="34" t="s">
+        <v>505</v>
+      </c>
+      <c r="C104" s="34" t="s">
+        <v>413</v>
+      </c>
+      <c r="D104" s="34" t="s">
+        <v>506</v>
+      </c>
+      <c r="E104" s="34"/>
+      <c r="F104" s="34"/>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A105" s="34" t="s">
+        <v>507</v>
+      </c>
+      <c r="B105" s="34" t="s">
+        <v>358</v>
+      </c>
+      <c r="C105" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="D105" s="34" t="s">
+        <v>508</v>
+      </c>
+      <c r="E105" s="34"/>
+      <c r="F105" s="34"/>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A106" s="34" t="s">
+        <v>509</v>
+      </c>
+      <c r="B106" s="34" t="s">
+        <v>510</v>
+      </c>
+      <c r="C106" s="34" t="s">
+        <v>469</v>
+      </c>
+      <c r="D106" s="34" t="s">
+        <v>511</v>
+      </c>
+      <c r="E106" s="34"/>
+      <c r="F106" s="34"/>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A107" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="B107" s="34" t="s">
+        <v>376</v>
+      </c>
+      <c r="C107" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="D107" s="34" t="s">
+        <v>513</v>
+      </c>
+      <c r="E107" s="34"/>
+      <c r="F107" s="34"/>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A108" s="34" t="s">
+        <v>514</v>
+      </c>
+      <c r="B108" s="34" t="s">
+        <v>515</v>
+      </c>
+      <c r="C108" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="D108" s="34" t="s">
+        <v>516</v>
+      </c>
+      <c r="E108" s="34"/>
+      <c r="F108" s="34"/>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A109" s="34" t="s">
+        <v>517</v>
+      </c>
+      <c r="B109" s="34" t="s">
+        <v>518</v>
+      </c>
+      <c r="C109" s="34" t="s">
+        <v>351</v>
+      </c>
+      <c r="D109" s="34" t="s">
+        <v>519</v>
+      </c>
+      <c r="E109" s="34"/>
+      <c r="F109" s="34"/>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A110" s="34" t="s">
+        <v>520</v>
+      </c>
+      <c r="B110" s="34" t="s">
+        <v>521</v>
+      </c>
+      <c r="C110" s="34" t="s">
+        <v>197</v>
+      </c>
+      <c r="D110" s="34" t="s">
+        <v>522</v>
+      </c>
+      <c r="E110" s="34"/>
+      <c r="F110" s="34"/>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A111" s="34" t="s">
+        <v>523</v>
+      </c>
+      <c r="B111" s="34" t="s">
+        <v>386</v>
+      </c>
+      <c r="C111" s="34" t="s">
+        <v>413</v>
+      </c>
+      <c r="D111" s="34" t="s">
+        <v>524</v>
+      </c>
+      <c r="E111" s="34"/>
+      <c r="F111" s="34"/>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A112" s="34" t="s">
+        <v>525</v>
+      </c>
+      <c r="B112" s="34" t="s">
+        <v>526</v>
+      </c>
+      <c r="C112" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="D112" s="34" t="s">
+        <v>527</v>
+      </c>
+      <c r="E112" s="34"/>
+      <c r="F112" s="34"/>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A113" s="34" t="s">
+        <v>528</v>
+      </c>
+      <c r="B113" s="34" t="s">
+        <v>529</v>
+      </c>
+      <c r="C113" s="34" t="s">
+        <v>428</v>
+      </c>
+      <c r="D113" s="34" t="s">
+        <v>530</v>
+      </c>
+      <c r="E113" s="34"/>
+      <c r="F113" s="34"/>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A114" s="34" t="s">
+        <v>531</v>
+      </c>
+      <c r="B114" s="34" t="s">
+        <v>221</v>
+      </c>
+      <c r="C114" s="34" t="s">
+        <v>301</v>
+      </c>
+      <c r="D114" s="34" t="s">
+        <v>532</v>
+      </c>
+      <c r="E114" s="34"/>
+      <c r="F114" s="34"/>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A115" s="34" t="s">
+        <v>533</v>
+      </c>
+      <c r="B115" s="34" t="s">
+        <v>390</v>
+      </c>
+      <c r="C115" s="34" t="s">
+        <v>534</v>
+      </c>
+      <c r="D115" s="34" t="s">
+        <v>535</v>
+      </c>
+      <c r="E115" s="34"/>
+      <c r="F115" s="34"/>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="34" t="s">
+        <v>536</v>
+      </c>
+      <c r="B116" s="34" t="s">
+        <v>537</v>
+      </c>
+      <c r="C116" s="34" t="s">
+        <v>355</v>
+      </c>
+      <c r="D116" s="34" t="s">
+        <v>538</v>
+      </c>
+      <c r="E116" s="34"/>
+      <c r="F116" s="34"/>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A117" s="34" t="s">
+        <v>539</v>
+      </c>
+      <c r="B117" s="34" t="s">
+        <v>540</v>
+      </c>
+      <c r="C117" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="D117" s="34" t="s">
+        <v>541</v>
+      </c>
+      <c r="E117" s="34"/>
+      <c r="F117" s="34"/>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A118" s="34" t="s">
+        <v>542</v>
+      </c>
+      <c r="B118" s="34" t="s">
+        <v>543</v>
+      </c>
+      <c r="C118" s="34" t="s">
+        <v>166</v>
+      </c>
+      <c r="D118" s="34" t="s">
+        <v>544</v>
+      </c>
+      <c r="E118" s="34"/>
+      <c r="F118" s="34"/>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A119" s="34" t="s">
+        <v>545</v>
+      </c>
+      <c r="B119" s="34" t="s">
+        <v>546</v>
+      </c>
+      <c r="C119" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="D119" s="34" t="s">
+        <v>547</v>
+      </c>
+      <c r="E119" s="34"/>
+      <c r="F119" s="34"/>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A120" s="34" t="s">
+        <v>548</v>
+      </c>
+      <c r="B120" s="34" t="s">
+        <v>165</v>
+      </c>
+      <c r="C120" s="34" t="s">
+        <v>549</v>
+      </c>
+      <c r="D120" s="34" t="s">
+        <v>550</v>
+      </c>
+      <c r="E120" s="34"/>
+      <c r="F120" s="34"/>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A121" s="34" t="s">
+        <v>551</v>
+      </c>
+      <c r="B121" s="34" t="s">
+        <v>387</v>
+      </c>
+      <c r="C121" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="D121" s="34" t="s">
+        <v>552</v>
+      </c>
+      <c r="E121" s="34"/>
+      <c r="F121" s="34"/>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A122" s="34" t="s">
+        <v>553</v>
+      </c>
+      <c r="B122" s="34" t="s">
+        <v>554</v>
+      </c>
+      <c r="C122" s="34" t="s">
+        <v>449</v>
+      </c>
+      <c r="D122" s="34" t="s">
+        <v>555</v>
+      </c>
+      <c r="E122" s="34"/>
+      <c r="F122" s="34"/>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A123" s="34" t="s">
+        <v>556</v>
+      </c>
+      <c r="B123" s="34" t="s">
+        <v>557</v>
+      </c>
+      <c r="C123" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="D123" s="34" t="s">
+        <v>558</v>
+      </c>
+      <c r="E123" s="34"/>
+      <c r="F123" s="34"/>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A124" s="34" t="s">
+        <v>559</v>
+      </c>
+      <c r="B124" s="34" t="s">
+        <v>271</v>
+      </c>
+      <c r="C124" s="34" t="s">
+        <v>272</v>
+      </c>
+      <c r="D124" s="34" t="s">
+        <v>560</v>
+      </c>
+      <c r="E124" s="34"/>
+      <c r="F124" s="34"/>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A125" s="34" t="s">
+        <v>561</v>
+      </c>
+      <c r="B125" s="34" t="s">
+        <v>177</v>
+      </c>
+      <c r="C125" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="D125" s="34" t="s">
+        <v>562</v>
+      </c>
+      <c r="E125" s="34"/>
+      <c r="F125" s="34"/>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A126" s="34" t="s">
+        <v>563</v>
+      </c>
+      <c r="B126" s="34" t="s">
+        <v>365</v>
+      </c>
+      <c r="C126" s="34" t="s">
+        <v>182</v>
+      </c>
+      <c r="D126" s="34" t="s">
+        <v>564</v>
+      </c>
+      <c r="E126" s="34"/>
+      <c r="F126" s="34"/>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A127" s="34" t="s">
+        <v>565</v>
+      </c>
+      <c r="B127" s="34" t="s">
+        <v>379</v>
+      </c>
+      <c r="C127" s="34" t="s">
+        <v>305</v>
+      </c>
+      <c r="D127" s="34" t="s">
+        <v>566</v>
+      </c>
+      <c r="E127" s="34"/>
+      <c r="F127" s="34"/>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A128" s="34" t="s">
+        <v>567</v>
+      </c>
+      <c r="B128" s="34" t="s">
+        <v>568</v>
+      </c>
+      <c r="C128" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="D128" s="34" t="s">
+        <v>569</v>
+      </c>
+      <c r="E128" s="34"/>
+      <c r="F128" s="34"/>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A129" s="34" t="s">
+        <v>570</v>
+      </c>
+      <c r="B129" s="34" t="s">
+        <v>359</v>
+      </c>
+      <c r="C129" s="34" t="s">
+        <v>312</v>
+      </c>
+      <c r="D129" s="34" t="s">
+        <v>571</v>
+      </c>
+      <c r="E129" s="34"/>
+      <c r="F129" s="34"/>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A130" s="34" t="s">
+        <v>572</v>
+      </c>
+      <c r="B130" s="34" t="s">
+        <v>573</v>
+      </c>
+      <c r="C130" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="D130" s="34" t="s">
+        <v>574</v>
+      </c>
+      <c r="E130" s="34"/>
+      <c r="F130" s="34"/>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A131" s="34" t="s">
+        <v>575</v>
+      </c>
+      <c r="B131" s="34" t="s">
+        <v>576</v>
+      </c>
+      <c r="C131" s="34" t="s">
+        <v>577</v>
+      </c>
+      <c r="D131" s="34" t="s">
+        <v>578</v>
+      </c>
+      <c r="E131" s="34"/>
+      <c r="F131" s="34"/>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A132" s="34" t="s">
+        <v>579</v>
+      </c>
+      <c r="B132" s="34" t="s">
+        <v>580</v>
+      </c>
+      <c r="C132" s="34" t="s">
+        <v>222</v>
+      </c>
+      <c r="D132" s="34" t="s">
+        <v>581</v>
+      </c>
+      <c r="E132" s="34"/>
+      <c r="F132" s="34"/>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A133" s="34" t="s">
+        <v>582</v>
+      </c>
+      <c r="B133" s="34" t="s">
+        <v>583</v>
+      </c>
+      <c r="C133" s="34" t="s">
+        <v>584</v>
+      </c>
+      <c r="D133" s="34" t="s">
+        <v>585</v>
+      </c>
+      <c r="E133" s="34"/>
+      <c r="F133" s="34"/>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A134" s="34" t="s">
+        <v>586</v>
+      </c>
+      <c r="B134" s="34" t="s">
+        <v>367</v>
+      </c>
+      <c r="C134" s="34" t="s">
+        <v>319</v>
+      </c>
+      <c r="D134" s="34" t="s">
+        <v>587</v>
+      </c>
+      <c r="E134" s="34"/>
+      <c r="F134" s="34"/>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A135" s="34" t="s">
+        <v>588</v>
+      </c>
+      <c r="B135" s="34" t="s">
+        <v>343</v>
+      </c>
+      <c r="C135" s="34" t="s">
+        <v>344</v>
+      </c>
+      <c r="D135" s="34" t="s">
+        <v>589</v>
+      </c>
+      <c r="E135" s="34"/>
+      <c r="F135" s="34"/>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A136" s="34" t="s">
+        <v>590</v>
+      </c>
+      <c r="B136" s="34" t="s">
+        <v>360</v>
+      </c>
+      <c r="C136" s="34" t="s">
+        <v>413</v>
+      </c>
+      <c r="D136" s="34" t="s">
+        <v>591</v>
+      </c>
+      <c r="E136" s="34"/>
+      <c r="F136" s="34"/>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A137" s="34" t="s">
+        <v>592</v>
+      </c>
+      <c r="B137" s="34" t="s">
+        <v>384</v>
+      </c>
+      <c r="C137" s="34" t="s">
+        <v>428</v>
+      </c>
+      <c r="D137" s="34" t="s">
+        <v>593</v>
+      </c>
+      <c r="E137" s="34"/>
+      <c r="F137" s="34"/>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A138" s="34" t="s">
+        <v>594</v>
+      </c>
+      <c r="B138" s="34" t="s">
+        <v>595</v>
+      </c>
+      <c r="C138" s="34" t="s">
+        <v>577</v>
+      </c>
+      <c r="D138" s="34" t="s">
+        <v>596</v>
+      </c>
+      <c r="E138" s="34"/>
+      <c r="F138" s="34"/>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A139" s="34" t="s">
+        <v>597</v>
+      </c>
+      <c r="B139" s="34" t="s">
+        <v>377</v>
+      </c>
+      <c r="C139" s="34" t="s">
+        <v>174</v>
+      </c>
+      <c r="D139" s="34" t="s">
+        <v>598</v>
+      </c>
+      <c r="E139" s="34"/>
+      <c r="F139" s="34"/>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A140" s="34" t="s">
+        <v>599</v>
+      </c>
+      <c r="B140" s="34" t="s">
+        <v>169</v>
+      </c>
+      <c r="C140" s="34" t="s">
+        <v>355</v>
+      </c>
+      <c r="D140" s="34" t="s">
+        <v>600</v>
+      </c>
+      <c r="E140" s="34"/>
+      <c r="F140" s="34"/>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A141" s="34" t="s">
+        <v>601</v>
+      </c>
+      <c r="B141" s="34" t="s">
+        <v>602</v>
+      </c>
+      <c r="C141" s="34" t="s">
+        <v>226</v>
+      </c>
+      <c r="D141" s="34" t="s">
+        <v>603</v>
+      </c>
+      <c r="E141" s="34"/>
+      <c r="F141" s="34"/>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A142" s="34" t="s">
+        <v>604</v>
+      </c>
+      <c r="B142" s="34" t="s">
+        <v>605</v>
+      </c>
+      <c r="C142" s="34" t="s">
+        <v>351</v>
+      </c>
+      <c r="D142" s="34" t="s">
+        <v>606</v>
+      </c>
+      <c r="E142" s="34"/>
+      <c r="F142" s="34"/>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A143" s="34" t="s">
+        <v>607</v>
+      </c>
+      <c r="B143" s="34" t="s">
+        <v>363</v>
+      </c>
+      <c r="C143" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="D143" s="34" t="s">
+        <v>608</v>
+      </c>
+      <c r="E143" s="34"/>
+      <c r="F143" s="34"/>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A144" s="34" t="s">
+        <v>609</v>
+      </c>
+      <c r="B144" s="34" t="s">
+        <v>366</v>
+      </c>
+      <c r="C144" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="D144" s="34" t="s">
+        <v>610</v>
+      </c>
+      <c r="E144" s="34"/>
+      <c r="F144" s="34"/>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A145" s="34" t="s">
+        <v>611</v>
+      </c>
+      <c r="B145" s="34" t="s">
+        <v>343</v>
+      </c>
+      <c r="C145" s="34" t="s">
+        <v>344</v>
+      </c>
+      <c r="D145" s="34" t="s">
+        <v>612</v>
+      </c>
+      <c r="E145" s="34"/>
+      <c r="F145" s="34"/>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A146" s="34" t="s">
+        <v>613</v>
+      </c>
+      <c r="B146" s="34" t="s">
+        <v>614</v>
+      </c>
+      <c r="C146" s="34" t="s">
+        <v>406</v>
+      </c>
+      <c r="D146" s="34" t="s">
+        <v>615</v>
+      </c>
+      <c r="E146" s="34"/>
+      <c r="F146" s="34"/>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A147" s="34" t="s">
+        <v>616</v>
+      </c>
+      <c r="B147" s="34" t="s">
+        <v>617</v>
+      </c>
+      <c r="C147" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="D147" s="34" t="s">
+        <v>618</v>
+      </c>
+      <c r="E147" s="34"/>
+      <c r="F147" s="34"/>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A148" s="34" t="s">
+        <v>619</v>
+      </c>
+      <c r="B148" s="34" t="s">
+        <v>620</v>
+      </c>
+      <c r="C148" s="34" t="s">
+        <v>549</v>
+      </c>
+      <c r="D148" s="34" t="s">
+        <v>621</v>
+      </c>
+      <c r="E148" s="34"/>
+      <c r="F148" s="34"/>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A149" s="34" t="s">
+        <v>622</v>
+      </c>
+      <c r="B149" s="34" t="s">
+        <v>371</v>
+      </c>
+      <c r="C149" s="34" t="s">
+        <v>441</v>
+      </c>
+      <c r="D149" s="34" t="s">
+        <v>623</v>
+      </c>
+      <c r="E149" s="34"/>
+      <c r="F149" s="34"/>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A150" s="34" t="s">
+        <v>624</v>
+      </c>
+      <c r="B150" s="34" t="s">
+        <v>373</v>
+      </c>
+      <c r="C150" s="34" t="s">
+        <v>400</v>
+      </c>
+      <c r="D150" s="34" t="s">
+        <v>625</v>
+      </c>
+      <c r="E150" s="34"/>
+      <c r="F150" s="34"/>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A151" s="34" t="s">
+        <v>626</v>
+      </c>
+      <c r="B151" s="34" t="s">
+        <v>381</v>
+      </c>
+      <c r="C151" s="34" t="s">
+        <v>355</v>
+      </c>
+      <c r="D151" s="34" t="s">
+        <v>627</v>
+      </c>
+      <c r="E151" s="34"/>
+      <c r="F151" s="34"/>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A152" s="34" t="s">
+        <v>628</v>
+      </c>
+      <c r="B152" s="34" t="s">
+        <v>629</v>
+      </c>
+      <c r="C152" s="34" t="s">
+        <v>312</v>
+      </c>
+      <c r="D152" s="34" t="s">
+        <v>630</v>
+      </c>
+      <c r="E152" s="34"/>
+      <c r="F152" s="34"/>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A153" s="34" t="s">
+        <v>631</v>
+      </c>
+      <c r="B153" s="34" t="s">
+        <v>632</v>
+      </c>
+      <c r="C153" s="34" t="s">
+        <v>312</v>
+      </c>
+      <c r="D153" s="34" t="s">
+        <v>633</v>
+      </c>
+      <c r="E153" s="34"/>
+      <c r="F153" s="34"/>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A154" s="34" t="s">
+        <v>634</v>
+      </c>
+      <c r="B154" s="34" t="s">
+        <v>635</v>
+      </c>
+      <c r="C154" s="34" t="s">
+        <v>272</v>
+      </c>
+      <c r="D154" s="34" t="s">
+        <v>636</v>
+      </c>
+      <c r="E154" s="34"/>
+      <c r="F154" s="34"/>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A155" s="34" t="s">
+        <v>637</v>
+      </c>
+      <c r="B155" s="34" t="s">
+        <v>382</v>
+      </c>
+      <c r="C155" s="34" t="s">
+        <v>355</v>
+      </c>
+      <c r="D155" s="34" t="s">
+        <v>638</v>
+      </c>
+      <c r="E155" s="34"/>
+      <c r="F155" s="34"/>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A156" s="34" t="s">
+        <v>639</v>
+      </c>
+      <c r="B156" s="34" t="s">
+        <v>640</v>
+      </c>
+      <c r="C156" s="34" t="s">
+        <v>481</v>
+      </c>
+      <c r="D156" s="34" t="s">
+        <v>641</v>
+      </c>
+      <c r="E156" s="34"/>
+      <c r="F156" s="34"/>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A157" s="34" t="s">
+        <v>642</v>
+      </c>
+      <c r="B157" s="34" t="s">
+        <v>383</v>
+      </c>
+      <c r="C157" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="D157" s="34" t="s">
+        <v>643</v>
+      </c>
+      <c r="E157" s="34"/>
+      <c r="F157" s="34"/>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A158" s="34" t="s">
+        <v>644</v>
+      </c>
+      <c r="B158" s="34" t="s">
+        <v>645</v>
+      </c>
+      <c r="C158" s="34" t="s">
+        <v>481</v>
+      </c>
+      <c r="D158" s="34" t="s">
+        <v>646</v>
+      </c>
+      <c r="E158" s="34"/>
+      <c r="F158" s="34"/>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A159" s="34" t="s">
+        <v>647</v>
+      </c>
+      <c r="B159" s="34" t="s">
+        <v>648</v>
+      </c>
+      <c r="C159" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="D159" s="34" t="s">
+        <v>649</v>
+      </c>
+      <c r="E159" s="34"/>
+      <c r="F159" s="34"/>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A160" s="34" t="s">
+        <v>650</v>
+      </c>
+      <c r="B160" s="34" t="s">
+        <v>651</v>
+      </c>
+      <c r="C160" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="D160" s="34" t="s">
+        <v>652</v>
+      </c>
+      <c r="E160" s="34"/>
+      <c r="F160" s="34"/>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A161" s="34" t="s">
+        <v>653</v>
+      </c>
+      <c r="B161" s="34" t="s">
+        <v>654</v>
+      </c>
+      <c r="C161" s="34" t="s">
+        <v>222</v>
+      </c>
+      <c r="D161" s="34" t="s">
+        <v>655</v>
+      </c>
+      <c r="E161" s="34"/>
+      <c r="F161" s="34"/>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A162" s="34" t="s">
+        <v>656</v>
+      </c>
+      <c r="B162" s="34" t="s">
+        <v>331</v>
+      </c>
+      <c r="C162" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="D162" s="34" t="s">
+        <v>657</v>
+      </c>
+      <c r="E162" s="34"/>
+      <c r="F162" s="34"/>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A163" s="34" t="s">
+        <v>658</v>
+      </c>
+      <c r="B163" s="34" t="s">
+        <v>200</v>
+      </c>
+      <c r="C163" s="34" t="s">
+        <v>201</v>
+      </c>
+      <c r="D163" s="34" t="s">
+        <v>659</v>
+      </c>
+      <c r="E163" s="34"/>
+      <c r="F163" s="34"/>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A164" s="34" t="s">
+        <v>660</v>
+      </c>
+      <c r="B164" s="34" t="s">
+        <v>361</v>
+      </c>
+      <c r="C164" s="34" t="s">
+        <v>355</v>
+      </c>
+      <c r="D164" s="34" t="s">
+        <v>661</v>
+      </c>
+      <c r="E164" s="34"/>
+      <c r="F164" s="34"/>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A165" s="34" t="s">
+        <v>662</v>
+      </c>
+      <c r="B165" s="34" t="s">
+        <v>391</v>
+      </c>
+      <c r="C165" s="34" t="s">
+        <v>355</v>
+      </c>
+      <c r="D165" s="34" t="s">
+        <v>663</v>
+      </c>
+      <c r="E165" s="34"/>
+      <c r="F165" s="34"/>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A166" s="34" t="s">
+        <v>665</v>
+      </c>
+      <c r="B166" s="34" t="s">
+        <v>664</v>
+      </c>
+      <c r="C166" s="34" t="s">
+        <v>757</v>
+      </c>
+      <c r="D166" s="34" t="s">
+        <v>666</v>
+      </c>
+      <c r="F166" s="34"/>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A167" s="34" t="s">
+        <v>667</v>
+      </c>
+      <c r="B167" s="34" t="s">
+        <v>784</v>
+      </c>
+      <c r="C167" s="34" t="s">
+        <v>782</v>
+      </c>
+      <c r="D167" s="34" t="s">
+        <v>668</v>
+      </c>
+      <c r="F167" s="34"/>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A168" s="34" t="s">
+        <v>669</v>
+      </c>
+      <c r="B168" s="34" t="s">
+        <v>785</v>
+      </c>
+      <c r="C168" s="34" t="s">
+        <v>758</v>
+      </c>
+      <c r="D168" s="34" t="s">
+        <v>670</v>
+      </c>
+      <c r="F168" s="34"/>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A169" s="34" t="s">
+        <v>671</v>
+      </c>
+      <c r="B169" s="34" t="s">
+        <v>786</v>
+      </c>
+      <c r="C169" s="34" t="s">
+        <v>758</v>
+      </c>
+      <c r="D169" s="34" t="s">
+        <v>672</v>
+      </c>
+      <c r="F169" s="34"/>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A170" s="34" t="s">
+        <v>673</v>
+      </c>
+      <c r="B170" s="34" t="s">
+        <v>787</v>
+      </c>
+      <c r="C170" s="34" t="s">
+        <v>758</v>
+      </c>
+      <c r="D170" s="34" t="s">
+        <v>674</v>
+      </c>
+      <c r="F170" s="34"/>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A171" s="34" t="s">
+        <v>675</v>
+      </c>
+      <c r="B171" s="34" t="s">
+        <v>788</v>
+      </c>
+      <c r="C171" s="34" t="s">
+        <v>759</v>
+      </c>
+      <c r="D171" s="34" t="s">
+        <v>676</v>
+      </c>
+      <c r="F171" s="34"/>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A172" s="34" t="s">
+        <v>677</v>
+      </c>
+      <c r="B172" s="34" t="s">
+        <v>789</v>
+      </c>
+      <c r="C172" s="34" t="s">
+        <v>760</v>
+      </c>
+      <c r="D172" s="34" t="s">
+        <v>678</v>
+      </c>
+      <c r="F172" s="34"/>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A173" s="34" t="s">
+        <v>679</v>
+      </c>
+      <c r="B173" s="34" t="s">
+        <v>790</v>
+      </c>
+      <c r="C173" s="34" t="s">
+        <v>761</v>
+      </c>
+      <c r="D173" s="34" t="s">
+        <v>680</v>
+      </c>
+      <c r="F173" s="34"/>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A174" s="34" t="s">
+        <v>681</v>
+      </c>
+      <c r="B174" s="37" t="s">
+        <v>826</v>
+      </c>
+      <c r="C174" s="34" t="s">
+        <v>762</v>
+      </c>
+      <c r="D174" s="34" t="s">
+        <v>682</v>
+      </c>
+      <c r="F174" s="34"/>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A175" s="34" t="s">
+        <v>683</v>
+      </c>
+      <c r="B175" s="34" t="s">
+        <v>791</v>
+      </c>
+      <c r="C175" s="34" t="s">
+        <v>764</v>
+      </c>
+      <c r="D175" s="34" t="s">
+        <v>684</v>
+      </c>
+      <c r="F175" s="34"/>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A176" s="34" t="s">
+        <v>685</v>
+      </c>
+      <c r="B176" s="34" t="s">
+        <v>792</v>
+      </c>
+      <c r="C176" s="34" t="s">
+        <v>765</v>
+      </c>
+      <c r="D176" s="34" t="s">
+        <v>686</v>
+      </c>
+      <c r="F176" s="34"/>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A177" s="34" t="s">
+        <v>687</v>
+      </c>
+      <c r="B177" s="34" t="s">
+        <v>793</v>
+      </c>
+      <c r="C177" s="34" t="s">
+        <v>764</v>
+      </c>
+      <c r="D177" s="34" t="s">
+        <v>688</v>
+      </c>
+      <c r="F177" s="34"/>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A178" s="34" t="s">
+        <v>689</v>
+      </c>
+      <c r="B178" s="34" t="s">
+        <v>794</v>
+      </c>
+      <c r="C178" s="34" t="s">
+        <v>766</v>
+      </c>
+      <c r="D178" s="34" t="s">
+        <v>690</v>
+      </c>
+      <c r="F178" s="34"/>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A179" s="34" t="s">
+        <v>691</v>
+      </c>
+      <c r="B179" s="34" t="s">
+        <v>795</v>
+      </c>
+      <c r="C179" s="34" t="s">
+        <v>767</v>
+      </c>
+      <c r="D179" s="34" t="s">
+        <v>692</v>
+      </c>
+      <c r="F179" s="34"/>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A180" s="34" t="s">
+        <v>693</v>
+      </c>
+      <c r="B180" s="37" t="s">
+        <v>796</v>
+      </c>
+      <c r="C180" s="34" t="s">
+        <v>768</v>
+      </c>
+      <c r="D180" s="34" t="s">
+        <v>694</v>
+      </c>
+      <c r="F180" s="34"/>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A181" s="34" t="s">
+        <v>695</v>
+      </c>
+      <c r="B181" s="37" t="s">
+        <v>797</v>
+      </c>
+      <c r="C181" s="34" t="s">
+        <v>766</v>
+      </c>
+      <c r="D181" s="34" t="s">
+        <v>696</v>
+      </c>
+      <c r="F181" s="34"/>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A182" s="34" t="s">
+        <v>697</v>
+      </c>
+      <c r="B182" s="37" t="s">
+        <v>798</v>
+      </c>
+      <c r="C182" s="34" t="s">
+        <v>769</v>
+      </c>
+      <c r="D182" s="34" t="s">
+        <v>698</v>
+      </c>
+      <c r="F182" s="34"/>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A183" s="34" t="s">
+        <v>699</v>
+      </c>
+      <c r="B183" s="37" t="s">
+        <v>799</v>
+      </c>
+      <c r="C183" s="34" t="s">
+        <v>765</v>
+      </c>
+      <c r="D183" s="34" t="s">
+        <v>700</v>
+      </c>
+      <c r="F183" s="34"/>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A184" s="34" t="s">
+        <v>701</v>
+      </c>
+      <c r="B184" s="37" t="s">
+        <v>800</v>
+      </c>
+      <c r="C184" s="34" t="s">
+        <v>764</v>
+      </c>
+      <c r="D184" s="34" t="s">
+        <v>702</v>
+      </c>
+      <c r="F184" s="34"/>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A185" s="34" t="s">
+        <v>703</v>
+      </c>
+      <c r="B185" s="37" t="s">
+        <v>801</v>
+      </c>
+      <c r="C185" s="34" t="s">
+        <v>763</v>
+      </c>
+      <c r="D185" s="34" t="s">
+        <v>704</v>
+      </c>
+      <c r="F185" s="34"/>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A186" s="34" t="s">
+        <v>705</v>
+      </c>
+      <c r="B186" s="37" t="s">
+        <v>802</v>
+      </c>
+      <c r="C186" s="34" t="s">
+        <v>763</v>
+      </c>
+      <c r="D186" s="34" t="s">
+        <v>706</v>
+      </c>
+      <c r="F186" s="34"/>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A187" s="34" t="s">
+        <v>707</v>
+      </c>
+      <c r="B187" s="37" t="s">
+        <v>803</v>
+      </c>
+      <c r="C187" s="34" t="s">
+        <v>769</v>
+      </c>
+      <c r="D187" s="34" t="s">
+        <v>708</v>
+      </c>
+      <c r="F187" s="34"/>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A188" s="34" t="s">
+        <v>709</v>
+      </c>
+      <c r="B188" s="37" t="s">
+        <v>804</v>
+      </c>
+      <c r="C188" s="34" t="s">
+        <v>770</v>
+      </c>
+      <c r="D188" s="34" t="s">
+        <v>710</v>
+      </c>
+      <c r="F188" s="34"/>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A189" s="34" t="s">
+        <v>711</v>
+      </c>
+      <c r="B189" s="37" t="s">
+        <v>805</v>
+      </c>
+      <c r="C189" s="34" t="s">
+        <v>771</v>
+      </c>
+      <c r="D189" s="34" t="s">
+        <v>712</v>
+      </c>
+      <c r="F189" s="34"/>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A190" s="34" t="s">
+        <v>713</v>
+      </c>
+      <c r="B190" s="37" t="s">
+        <v>806</v>
+      </c>
+      <c r="C190" s="34" t="s">
+        <v>772</v>
+      </c>
+      <c r="D190" s="34" t="s">
+        <v>714</v>
+      </c>
+      <c r="F190" s="34"/>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A191" s="34" t="s">
+        <v>715</v>
+      </c>
+      <c r="B191" s="37" t="s">
+        <v>807</v>
+      </c>
+      <c r="C191" s="34" t="s">
+        <v>765</v>
+      </c>
+      <c r="D191" s="34" t="s">
+        <v>716</v>
+      </c>
+      <c r="F191" s="34"/>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A192" s="34" t="s">
+        <v>717</v>
+      </c>
+      <c r="B192" s="37" t="s">
+        <v>808</v>
+      </c>
+      <c r="C192" s="34" t="s">
+        <v>773</v>
+      </c>
+      <c r="D192" s="34" t="s">
+        <v>718</v>
+      </c>
+      <c r="F192" s="34"/>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A193" s="34" t="s">
+        <v>719</v>
+      </c>
+      <c r="B193" s="37" t="s">
+        <v>809</v>
+      </c>
+      <c r="C193" s="34" t="s">
+        <v>774</v>
+      </c>
+      <c r="D193" s="34" t="s">
+        <v>720</v>
+      </c>
+      <c r="F193" s="34"/>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A194" s="34" t="s">
+        <v>721</v>
+      </c>
+      <c r="B194" s="34" t="s">
+        <v>810</v>
+      </c>
+      <c r="C194" s="34" t="s">
+        <v>774</v>
+      </c>
+      <c r="D194" s="34" t="s">
+        <v>722</v>
+      </c>
+      <c r="F194" s="34"/>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A195" s="34" t="s">
+        <v>723</v>
+      </c>
+      <c r="B195" s="34" t="s">
+        <v>811</v>
+      </c>
+      <c r="C195" s="34" t="s">
+        <v>774</v>
+      </c>
+      <c r="D195" s="34" t="s">
+        <v>724</v>
+      </c>
+      <c r="F195" s="34"/>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A196" s="34" t="s">
+        <v>725</v>
+      </c>
+      <c r="B196" s="37" t="s">
+        <v>812</v>
+      </c>
+      <c r="C196" s="34" t="s">
+        <v>774</v>
+      </c>
+      <c r="D196" s="34" t="s">
+        <v>726</v>
+      </c>
+      <c r="F196" s="34"/>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A197" s="34" t="s">
+        <v>727</v>
+      </c>
+      <c r="B197" s="37" t="s">
+        <v>813</v>
+      </c>
+      <c r="C197" s="34" t="s">
+        <v>774</v>
+      </c>
+      <c r="D197" s="34" t="s">
+        <v>728</v>
+      </c>
+      <c r="F197" s="34"/>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A198" s="34" t="s">
+        <v>729</v>
+      </c>
+      <c r="B198" s="37" t="s">
+        <v>814</v>
+      </c>
+      <c r="C198" s="34" t="s">
+        <v>774</v>
+      </c>
+      <c r="D198" s="34" t="s">
+        <v>730</v>
+      </c>
+      <c r="F198" s="34"/>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A199" s="34" t="s">
+        <v>731</v>
+      </c>
+      <c r="B199" s="37" t="s">
+        <v>815</v>
+      </c>
+      <c r="C199" s="34" t="s">
+        <v>774</v>
+      </c>
+      <c r="D199" s="34" t="s">
+        <v>732</v>
+      </c>
+      <c r="F199" s="34"/>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A200" s="34" t="s">
+        <v>733</v>
+      </c>
+      <c r="B200" s="37" t="s">
+        <v>816</v>
+      </c>
+      <c r="C200" s="34" t="s">
+        <v>774</v>
+      </c>
+      <c r="D200" s="34" t="s">
+        <v>734</v>
+      </c>
+      <c r="F200" s="34"/>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A201" s="34" t="s">
+        <v>735</v>
+      </c>
+      <c r="B201" s="37" t="s">
+        <v>809</v>
+      </c>
+      <c r="C201" s="34" t="s">
+        <v>774</v>
+      </c>
+      <c r="D201" s="34" t="s">
+        <v>736</v>
+      </c>
+      <c r="F201" s="34"/>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A202" s="34" t="s">
+        <v>737</v>
+      </c>
+      <c r="B202" s="37" t="s">
+        <v>817</v>
+      </c>
+      <c r="C202" s="34" t="s">
+        <v>774</v>
+      </c>
+      <c r="D202" s="34" t="s">
+        <v>738</v>
+      </c>
+      <c r="F202" s="34"/>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A203" s="34" t="s">
+        <v>739</v>
+      </c>
+      <c r="B203" s="37" t="s">
+        <v>818</v>
+      </c>
+      <c r="C203" s="34" t="s">
+        <v>765</v>
+      </c>
+      <c r="D203" s="34" t="s">
+        <v>740</v>
+      </c>
+      <c r="F203" s="34"/>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A204" s="34" t="s">
+        <v>741</v>
+      </c>
+      <c r="B204" s="37" t="s">
+        <v>819</v>
+      </c>
+      <c r="C204" s="34" t="s">
+        <v>765</v>
+      </c>
+      <c r="D204" s="34" t="s">
+        <v>742</v>
+      </c>
+      <c r="F204" s="34"/>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A205" s="34" t="s">
+        <v>743</v>
+      </c>
+      <c r="B205" s="37" t="s">
+        <v>743</v>
+      </c>
+      <c r="C205" s="34" t="s">
+        <v>775</v>
+      </c>
+      <c r="D205" s="34" t="s">
+        <v>744</v>
+      </c>
+      <c r="F205" s="34"/>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A206" s="34" t="s">
+        <v>745</v>
+      </c>
+      <c r="B206" s="37" t="s">
+        <v>820</v>
+      </c>
+      <c r="C206" s="34" t="s">
+        <v>776</v>
+      </c>
+      <c r="D206" s="34" t="s">
+        <v>746</v>
+      </c>
+      <c r="F206" s="34"/>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A207" s="34" t="s">
+        <v>747</v>
+      </c>
+      <c r="B207" s="37" t="s">
+        <v>821</v>
+      </c>
+      <c r="C207" s="34" t="s">
+        <v>777</v>
+      </c>
+      <c r="D207" s="34" t="s">
+        <v>748</v>
+      </c>
+      <c r="F207" s="34"/>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A208" s="34" t="s">
+        <v>749</v>
+      </c>
+      <c r="B208" s="37" t="s">
+        <v>822</v>
+      </c>
+      <c r="C208" s="34" t="s">
+        <v>778</v>
+      </c>
+      <c r="D208" s="34" t="s">
+        <v>750</v>
+      </c>
+      <c r="F208" s="34"/>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A209" s="34" t="s">
+        <v>751</v>
+      </c>
+      <c r="B209" s="37" t="s">
+        <v>823</v>
+      </c>
+      <c r="C209" s="34" t="s">
+        <v>779</v>
+      </c>
+      <c r="D209" s="34" t="s">
+        <v>752</v>
+      </c>
+      <c r="F209" s="34"/>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A210" s="34" t="s">
+        <v>753</v>
+      </c>
+      <c r="B210" s="37" t="s">
+        <v>824</v>
+      </c>
+      <c r="C210" s="34" t="s">
+        <v>780</v>
+      </c>
+      <c r="D210" s="34" t="s">
+        <v>754</v>
+      </c>
+      <c r="F210" s="34"/>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A211" s="34" t="s">
+        <v>755</v>
+      </c>
+      <c r="B211" s="34" t="s">
+        <v>825</v>
+      </c>
+      <c r="C211" s="34" t="s">
+        <v>781</v>
+      </c>
+      <c r="D211" s="34" t="s">
+        <v>756</v>
+      </c>
+      <c r="F211" s="34"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDFE1FA3-35F7-4749-A361-DD7391F594E3}">
   <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="22" x14ac:dyDescent="0.3"/>

--- a/src/config/midas_config_values.xlsx
+++ b/src/config/midas_config_values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/james/Documents/code/midas-alt/src/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA311461-FD02-EB4A-A022-F7EF0D34DC66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36BBED24-F22E-E440-98D6-A2F0550DFEA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51200" yWindow="500" windowWidth="38400" windowHeight="21100" activeTab="3" xr2:uid="{C4C84A31-B2D7-9544-A674-D1C9532EF091}"/>
+    <workbookView xWindow="51200" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{C4C84A31-B2D7-9544-A674-D1C9532EF091}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="8" r:id="rId1"/>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1013" uniqueCount="827">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="829">
   <si>
     <t>Key</t>
   </si>
@@ -70,12 +70,6 @@
   </si>
   <si>
     <t>Facility Keys</t>
-  </si>
-  <si>
-    <t>Facilities</t>
-  </si>
-  <si>
-    <t>Systems</t>
   </si>
   <si>
     <t>Description</t>
@@ -2619,6 +2613,18 @@
       </rPr>
       <t>ari </t>
     </r>
+  </si>
+  <si>
+    <t>Installation Locations:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contains a pre-defined subset of the Installation Locations which can be used when creating data inside of MIDAS. The default list was pulled from: https://en.wikipedia.org/wiki/List_of_United_States_Air_Force_installations </t>
+  </si>
+  <si>
+    <t>Systems:</t>
+  </si>
+  <si>
+    <t>Facilities:</t>
   </si>
 </sst>
 </file>
@@ -3262,11 +3268,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D2BE7E4-AE03-BF44-AB43-76DD35D2623F}">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="24" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.5" style="2" customWidth="1"/>
-    <col min="2" max="2" width="94.1640625" style="9" customWidth="1"/>
+    <col min="2" max="2" width="126.33203125" style="9" customWidth="1"/>
     <col min="3" max="3" width="107.6640625" style="9" customWidth="1"/>
     <col min="4" max="4" width="13.1640625" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.1640625" style="2" bestFit="1" customWidth="1"/>
@@ -3276,49 +3282,59 @@
     <row r="1" spans="1:5" ht="73" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="17"/>
       <c r="B1" s="17" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C1" s="18" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="25" x14ac:dyDescent="0.3">
       <c r="A2" s="17"/>
       <c r="B2" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2" s="19" t="s">
         <v>104</v>
       </c>
-      <c r="C2" s="19" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="275" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:5" ht="200" x14ac:dyDescent="0.3">
       <c r="B3" s="9" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D3" s="16"/>
       <c r="E3" s="16"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C4" s="16" t="s">
-        <v>3</v>
+        <v>828</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="100" x14ac:dyDescent="0.3">
       <c r="C5" s="9" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="C6" s="16" t="s">
-        <v>4</v>
+        <v>827</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="100" x14ac:dyDescent="0.3">
       <c r="C7" s="9" t="s">
-        <v>102</v>
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="25" x14ac:dyDescent="0.3">
+      <c r="C8" s="18" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="75" x14ac:dyDescent="0.3">
+      <c r="C9" s="9" t="s">
+        <v>826</v>
       </c>
     </row>
   </sheetData>
@@ -3340,21 +3356,21 @@
   <sheetData>
     <row r="1" spans="1:4" ht="34" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="25" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B1" s="26" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C1" s="27" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D1" s="28" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="29" customFormat="1" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="29" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="B2" s="30"/>
       <c r="C2" s="32"/>
@@ -3362,63 +3378,63 @@
     </row>
     <row r="3" spans="1:4" ht="76" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="100" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="C4" s="22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="50" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C5" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="51" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C6" s="22" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="1:4" s="29" customFormat="1" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="29" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B7" s="30"/>
       <c r="C7" s="31"/>
@@ -3426,74 +3442,74 @@
     </row>
     <row r="8" spans="1:4" ht="101" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C8" s="22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="D8" s="22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C9" s="22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D9" s="22" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="50" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C10" s="22" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D10" s="22" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="50" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C11" s="22" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D11" s="22" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="76" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C12" s="22" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D12" s="22" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="1:4" s="29" customFormat="1" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="29" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B13" s="30"/>
       <c r="C13" s="31"/>
@@ -3501,135 +3517,135 @@
     </row>
     <row r="14" spans="1:4" ht="251" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B14" s="14" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D14" s="23" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="250" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C15" s="24" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D15" s="24" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="176" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C16" s="24" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D16" s="24" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:4" s="29" customFormat="1" ht="18" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="29" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="B17" s="30"/>
       <c r="C17" s="32"/>
     </row>
     <row r="18" spans="1:4" ht="101" thickTop="1" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="100" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="100" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B20" s="12" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="125" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="B21" s="12" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="125" x14ac:dyDescent="0.3">
       <c r="A22" s="11" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="125" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -3655,13 +3671,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E1" s="10"/>
     </row>
@@ -3670,7 +3686,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C2" s="4">
         <v>60</v>
@@ -3684,7 +3700,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C3" s="4">
         <v>30</v>
@@ -3698,7 +3714,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C4" s="4">
         <v>60</v>
@@ -3712,7 +3728,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C5" s="4">
         <v>60</v>
@@ -3726,7 +3742,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C6" s="4">
         <v>30</v>
@@ -3740,7 +3756,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C7" s="4">
         <v>50</v>
@@ -3754,7 +3770,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C8" s="4">
         <v>40</v>
@@ -3768,7 +3784,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C9" s="4">
         <v>30</v>
@@ -3782,7 +3798,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C10" s="4">
         <v>30</v>
@@ -3796,7 +3812,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C11" s="4">
         <v>40</v>
@@ -3810,7 +3826,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C12" s="4">
         <v>40</v>
@@ -3824,7 +3840,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C13" s="4">
         <v>20</v>
@@ -3838,7 +3854,7 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C14" s="4">
         <v>50</v>
@@ -3852,7 +3868,7 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C15" s="4">
         <v>50</v>
@@ -3866,7 +3882,7 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C16" s="4">
         <v>50</v>
@@ -3880,7 +3896,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C17" s="4">
         <v>30</v>
@@ -3894,7 +3910,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C18" s="4">
         <v>30</v>
@@ -3908,7 +3924,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C19" s="4">
         <v>60</v>
@@ -3922,7 +3938,7 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C20" s="4">
         <v>40</v>
@@ -3936,7 +3952,7 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C21" s="4">
         <v>40</v>
@@ -3950,7 +3966,7 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C22" s="4">
         <v>30</v>
@@ -3964,7 +3980,7 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C23" s="4">
         <v>30</v>
@@ -3978,7 +3994,7 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C24" s="4">
         <v>30</v>
@@ -3992,7 +4008,7 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C25" s="4">
         <v>50</v>
@@ -4006,7 +4022,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C26" s="4">
         <v>30</v>
@@ -4020,7 +4036,7 @@
         <v>26</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C27" s="4">
         <v>30</v>
@@ -4034,7 +4050,7 @@
         <v>27</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C28" s="4">
         <v>30</v>
@@ -4048,7 +4064,7 @@
         <v>28</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C29" s="4">
         <v>60</v>
@@ -4078,3331 +4094,3331 @@
   <sheetData>
     <row r="1" spans="1:6" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="36" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B1" s="36" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C1" s="36" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="D1" s="36" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E1" s="34"/>
       <c r="F1" s="34"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="34" t="s">
+        <v>134</v>
+      </c>
+      <c r="B2" s="34" t="s">
+        <v>135</v>
+      </c>
+      <c r="C2" s="34" t="s">
         <v>136</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="D2" s="34" t="s">
         <v>137</v>
-      </c>
-      <c r="C2" s="34" t="s">
-        <v>138</v>
-      </c>
-      <c r="D2" s="34" t="s">
-        <v>139</v>
       </c>
       <c r="E2" s="34"/>
       <c r="F2" s="34"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="34" t="s">
+        <v>138</v>
+      </c>
+      <c r="B3" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="C3" s="34" t="s">
         <v>140</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="D3" s="34" t="s">
         <v>141</v>
-      </c>
-      <c r="C3" s="34" t="s">
-        <v>142</v>
-      </c>
-      <c r="D3" s="34" t="s">
-        <v>143</v>
       </c>
       <c r="E3" s="34"/>
       <c r="F3" s="34"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="34" t="s">
+        <v>142</v>
+      </c>
+      <c r="B4" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="C4" s="34" t="s">
         <v>144</v>
       </c>
-      <c r="B4" s="34" t="s">
+      <c r="D4" s="34" t="s">
         <v>145</v>
-      </c>
-      <c r="C4" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="D4" s="34" t="s">
-        <v>147</v>
       </c>
       <c r="E4" s="34"/>
       <c r="F4" s="34"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="B5" s="34" t="s">
+        <v>147</v>
+      </c>
+      <c r="C5" s="34" t="s">
         <v>148</v>
       </c>
-      <c r="B5" s="34" t="s">
+      <c r="D5" s="34" t="s">
         <v>149</v>
-      </c>
-      <c r="C5" s="34" t="s">
-        <v>150</v>
-      </c>
-      <c r="D5" s="34" t="s">
-        <v>151</v>
       </c>
       <c r="E5" s="34"/>
       <c r="F5" s="34"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="C6" s="34" t="s">
         <v>152</v>
       </c>
-      <c r="B6" s="34" t="s">
+      <c r="D6" s="34" t="s">
         <v>153</v>
-      </c>
-      <c r="C6" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="D6" s="34" t="s">
-        <v>155</v>
       </c>
       <c r="E6" s="34"/>
       <c r="F6" s="34"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="34" t="s">
+        <v>154</v>
+      </c>
+      <c r="B7" s="34" t="s">
+        <v>155</v>
+      </c>
+      <c r="C7" s="34" t="s">
         <v>156</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="D7" s="34" t="s">
         <v>157</v>
-      </c>
-      <c r="C7" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="D7" s="34" t="s">
-        <v>159</v>
       </c>
       <c r="E7" s="34"/>
       <c r="F7" s="34"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="34" t="s">
+        <v>158</v>
+      </c>
+      <c r="B8" s="34" t="s">
+        <v>159</v>
+      </c>
+      <c r="C8" s="34" t="s">
         <v>160</v>
       </c>
-      <c r="B8" s="34" t="s">
+      <c r="D8" s="34" t="s">
         <v>161</v>
-      </c>
-      <c r="C8" s="34" t="s">
-        <v>162</v>
-      </c>
-      <c r="D8" s="34" t="s">
-        <v>163</v>
       </c>
       <c r="E8" s="34"/>
       <c r="F8" s="34"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="34" t="s">
+        <v>162</v>
+      </c>
+      <c r="B9" s="34" t="s">
+        <v>163</v>
+      </c>
+      <c r="C9" s="34" t="s">
         <v>164</v>
       </c>
-      <c r="B9" s="34" t="s">
+      <c r="D9" s="34" t="s">
         <v>165</v>
-      </c>
-      <c r="C9" s="34" t="s">
-        <v>166</v>
-      </c>
-      <c r="D9" s="34" t="s">
-        <v>167</v>
       </c>
       <c r="E9" s="34"/>
       <c r="F9" s="34"/>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="34" t="s">
+        <v>166</v>
+      </c>
+      <c r="B10" s="34" t="s">
+        <v>167</v>
+      </c>
+      <c r="C10" s="34" t="s">
         <v>168</v>
       </c>
-      <c r="B10" s="34" t="s">
+      <c r="D10" s="34" t="s">
         <v>169</v>
-      </c>
-      <c r="C10" s="34" t="s">
-        <v>170</v>
-      </c>
-      <c r="D10" s="34" t="s">
-        <v>171</v>
       </c>
       <c r="E10" s="34"/>
       <c r="F10" s="34"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
+        <v>170</v>
+      </c>
+      <c r="B11" s="34" t="s">
+        <v>171</v>
+      </c>
+      <c r="C11" s="34" t="s">
         <v>172</v>
       </c>
-      <c r="B11" s="34" t="s">
+      <c r="D11" s="34" t="s">
         <v>173</v>
-      </c>
-      <c r="C11" s="34" t="s">
-        <v>174</v>
-      </c>
-      <c r="D11" s="34" t="s">
-        <v>175</v>
       </c>
       <c r="E11" s="34"/>
       <c r="F11" s="34"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="34" t="s">
+        <v>174</v>
+      </c>
+      <c r="B12" s="34" t="s">
+        <v>175</v>
+      </c>
+      <c r="C12" s="34" t="s">
         <v>176</v>
       </c>
-      <c r="B12" s="34" t="s">
+      <c r="D12" s="34" t="s">
         <v>177</v>
-      </c>
-      <c r="C12" s="34" t="s">
-        <v>178</v>
-      </c>
-      <c r="D12" s="34" t="s">
-        <v>179</v>
       </c>
       <c r="E12" s="34"/>
       <c r="F12" s="34"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="34" t="s">
+        <v>178</v>
+      </c>
+      <c r="B13" s="34" t="s">
+        <v>179</v>
+      </c>
+      <c r="C13" s="34" t="s">
         <v>180</v>
       </c>
-      <c r="B13" s="34" t="s">
+      <c r="D13" s="34" t="s">
         <v>181</v>
-      </c>
-      <c r="C13" s="34" t="s">
-        <v>182</v>
-      </c>
-      <c r="D13" s="34" t="s">
-        <v>183</v>
       </c>
       <c r="E13" s="34"/>
       <c r="F13" s="34"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="34" t="s">
+        <v>182</v>
+      </c>
+      <c r="B14" s="34" t="s">
+        <v>183</v>
+      </c>
+      <c r="C14" s="34" t="s">
         <v>184</v>
       </c>
-      <c r="B14" s="34" t="s">
+      <c r="D14" s="34" t="s">
         <v>185</v>
-      </c>
-      <c r="C14" s="34" t="s">
-        <v>186</v>
-      </c>
-      <c r="D14" s="34" t="s">
-        <v>187</v>
       </c>
       <c r="E14" s="34"/>
       <c r="F14" s="34"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="34" t="s">
+        <v>186</v>
+      </c>
+      <c r="B15" s="34" t="s">
+        <v>187</v>
+      </c>
+      <c r="C15" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="D15" s="34" t="s">
         <v>188</v>
-      </c>
-      <c r="B15" s="34" t="s">
-        <v>189</v>
-      </c>
-      <c r="C15" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="D15" s="34" t="s">
-        <v>190</v>
       </c>
       <c r="E15" s="34"/>
       <c r="F15" s="34"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="34" t="s">
+        <v>189</v>
+      </c>
+      <c r="B16" s="34" t="s">
+        <v>190</v>
+      </c>
+      <c r="C16" s="34" t="s">
         <v>191</v>
       </c>
-      <c r="B16" s="34" t="s">
+      <c r="D16" s="34" t="s">
         <v>192</v>
-      </c>
-      <c r="C16" s="34" t="s">
-        <v>193</v>
-      </c>
-      <c r="D16" s="34" t="s">
-        <v>194</v>
       </c>
       <c r="E16" s="34"/>
       <c r="F16" s="34"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="34" t="s">
+        <v>193</v>
+      </c>
+      <c r="B17" s="34" t="s">
+        <v>194</v>
+      </c>
+      <c r="C17" s="34" t="s">
         <v>195</v>
       </c>
-      <c r="B17" s="34" t="s">
+      <c r="D17" s="34" t="s">
         <v>196</v>
-      </c>
-      <c r="C17" s="34" t="s">
-        <v>197</v>
-      </c>
-      <c r="D17" s="34" t="s">
-        <v>198</v>
       </c>
       <c r="E17" s="34"/>
       <c r="F17" s="34"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="34" t="s">
+        <v>197</v>
+      </c>
+      <c r="B18" s="34" t="s">
+        <v>198</v>
+      </c>
+      <c r="C18" s="34" t="s">
         <v>199</v>
       </c>
-      <c r="B18" s="34" t="s">
+      <c r="D18" s="34" t="s">
         <v>200</v>
-      </c>
-      <c r="C18" s="34" t="s">
-        <v>201</v>
-      </c>
-      <c r="D18" s="34" t="s">
-        <v>202</v>
       </c>
       <c r="E18" s="34"/>
       <c r="F18" s="34"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="34" t="s">
+        <v>201</v>
+      </c>
+      <c r="B19" s="34" t="s">
+        <v>202</v>
+      </c>
+      <c r="C19" s="34" t="s">
         <v>203</v>
       </c>
-      <c r="B19" s="34" t="s">
+      <c r="D19" s="34" t="s">
         <v>204</v>
-      </c>
-      <c r="C19" s="34" t="s">
-        <v>205</v>
-      </c>
-      <c r="D19" s="34" t="s">
-        <v>206</v>
       </c>
       <c r="E19" s="34"/>
       <c r="F19" s="34"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
+        <v>205</v>
+      </c>
+      <c r="B20" s="34" t="s">
+        <v>206</v>
+      </c>
+      <c r="C20" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="D20" s="34" t="s">
         <v>207</v>
-      </c>
-      <c r="B20" s="34" t="s">
-        <v>208</v>
-      </c>
-      <c r="C20" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="D20" s="34" t="s">
-        <v>209</v>
       </c>
       <c r="E20" s="34"/>
       <c r="F20" s="34"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="34" t="s">
+        <v>208</v>
+      </c>
+      <c r="B21" s="34" t="s">
+        <v>209</v>
+      </c>
+      <c r="C21" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="D21" s="34" t="s">
         <v>210</v>
-      </c>
-      <c r="B21" s="34" t="s">
-        <v>211</v>
-      </c>
-      <c r="C21" s="34" t="s">
-        <v>178</v>
-      </c>
-      <c r="D21" s="34" t="s">
-        <v>212</v>
       </c>
       <c r="E21" s="34"/>
       <c r="F21" s="34"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="34" t="s">
+        <v>211</v>
+      </c>
+      <c r="B22" s="34" t="s">
+        <v>212</v>
+      </c>
+      <c r="C22" s="34" t="s">
+        <v>184</v>
+      </c>
+      <c r="D22" s="34" t="s">
         <v>213</v>
-      </c>
-      <c r="B22" s="34" t="s">
-        <v>214</v>
-      </c>
-      <c r="C22" s="34" t="s">
-        <v>186</v>
-      </c>
-      <c r="D22" s="34" t="s">
-        <v>215</v>
       </c>
       <c r="E22" s="34"/>
       <c r="F22" s="34"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="34" t="s">
+        <v>214</v>
+      </c>
+      <c r="B23" s="34" t="s">
+        <v>215</v>
+      </c>
+      <c r="C23" s="34" t="s">
         <v>216</v>
       </c>
-      <c r="B23" s="34" t="s">
+      <c r="D23" s="34" t="s">
         <v>217</v>
-      </c>
-      <c r="C23" s="34" t="s">
-        <v>218</v>
-      </c>
-      <c r="D23" s="34" t="s">
-        <v>219</v>
       </c>
       <c r="E23" s="34"/>
       <c r="F23" s="34"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="34" t="s">
+        <v>218</v>
+      </c>
+      <c r="B24" s="34" t="s">
+        <v>219</v>
+      </c>
+      <c r="C24" s="34" t="s">
         <v>220</v>
       </c>
-      <c r="B24" s="34" t="s">
+      <c r="D24" s="34" t="s">
         <v>221</v>
-      </c>
-      <c r="C24" s="34" t="s">
-        <v>222</v>
-      </c>
-      <c r="D24" s="34" t="s">
-        <v>223</v>
       </c>
       <c r="E24" s="34"/>
       <c r="F24" s="34"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="34" t="s">
+        <v>222</v>
+      </c>
+      <c r="B25" s="34" t="s">
+        <v>223</v>
+      </c>
+      <c r="C25" s="34" t="s">
         <v>224</v>
       </c>
-      <c r="B25" s="34" t="s">
+      <c r="D25" s="34" t="s">
         <v>225</v>
-      </c>
-      <c r="C25" s="34" t="s">
-        <v>226</v>
-      </c>
-      <c r="D25" s="34" t="s">
-        <v>227</v>
       </c>
       <c r="E25" s="34"/>
       <c r="F25" s="34"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="34" t="s">
+        <v>226</v>
+      </c>
+      <c r="B26" s="34" t="s">
+        <v>227</v>
+      </c>
+      <c r="C26" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="D26" s="34" t="s">
         <v>228</v>
-      </c>
-      <c r="B26" s="34" t="s">
-        <v>229</v>
-      </c>
-      <c r="C26" s="34" t="s">
-        <v>174</v>
-      </c>
-      <c r="D26" s="34" t="s">
-        <v>230</v>
       </c>
       <c r="E26" s="34"/>
       <c r="F26" s="34"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="34" t="s">
+        <v>229</v>
+      </c>
+      <c r="B27" s="34" t="s">
+        <v>230</v>
+      </c>
+      <c r="C27" s="34" t="s">
+        <v>160</v>
+      </c>
+      <c r="D27" s="34" t="s">
         <v>231</v>
-      </c>
-      <c r="B27" s="34" t="s">
-        <v>232</v>
-      </c>
-      <c r="C27" s="34" t="s">
-        <v>162</v>
-      </c>
-      <c r="D27" s="34" t="s">
-        <v>233</v>
       </c>
       <c r="E27" s="34"/>
       <c r="F27" s="34"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="34" t="s">
+        <v>232</v>
+      </c>
+      <c r="B28" s="34" t="s">
+        <v>233</v>
+      </c>
+      <c r="C28" s="34" t="s">
+        <v>191</v>
+      </c>
+      <c r="D28" s="34" t="s">
         <v>234</v>
-      </c>
-      <c r="B28" s="34" t="s">
-        <v>235</v>
-      </c>
-      <c r="C28" s="34" t="s">
-        <v>193</v>
-      </c>
-      <c r="D28" s="34" t="s">
-        <v>236</v>
       </c>
       <c r="E28" s="34"/>
       <c r="F28" s="34"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="34" t="s">
+        <v>235</v>
+      </c>
+      <c r="B29" s="34" t="s">
+        <v>236</v>
+      </c>
+      <c r="C29" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="D29" s="34" t="s">
         <v>237</v>
-      </c>
-      <c r="B29" s="34" t="s">
-        <v>238</v>
-      </c>
-      <c r="C29" s="34" t="s">
-        <v>170</v>
-      </c>
-      <c r="D29" s="34" t="s">
-        <v>239</v>
       </c>
       <c r="E29" s="34"/>
       <c r="F29" s="34"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="34" t="s">
+        <v>238</v>
+      </c>
+      <c r="B30" s="34" t="s">
+        <v>239</v>
+      </c>
+      <c r="C30" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="D30" s="34" t="s">
         <v>240</v>
-      </c>
-      <c r="B30" s="34" t="s">
-        <v>241</v>
-      </c>
-      <c r="C30" s="34" t="s">
-        <v>138</v>
-      </c>
-      <c r="D30" s="34" t="s">
-        <v>242</v>
       </c>
       <c r="E30" s="34"/>
       <c r="F30" s="34"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="34" t="s">
+        <v>241</v>
+      </c>
+      <c r="B31" s="34" t="s">
+        <v>242</v>
+      </c>
+      <c r="C31" s="34" t="s">
+        <v>160</v>
+      </c>
+      <c r="D31" s="34" t="s">
         <v>243</v>
-      </c>
-      <c r="B31" s="34" t="s">
-        <v>244</v>
-      </c>
-      <c r="C31" s="34" t="s">
-        <v>162</v>
-      </c>
-      <c r="D31" s="34" t="s">
-        <v>245</v>
       </c>
       <c r="E31" s="34"/>
       <c r="F31" s="34"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="34" t="s">
+        <v>244</v>
+      </c>
+      <c r="B32" s="34" t="s">
+        <v>245</v>
+      </c>
+      <c r="C32" s="34" t="s">
         <v>246</v>
       </c>
-      <c r="B32" s="34" t="s">
+      <c r="D32" s="34" t="s">
         <v>247</v>
-      </c>
-      <c r="C32" s="34" t="s">
-        <v>248</v>
-      </c>
-      <c r="D32" s="34" t="s">
-        <v>249</v>
       </c>
       <c r="E32" s="34"/>
       <c r="F32" s="34"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="34" t="s">
+        <v>248</v>
+      </c>
+      <c r="B33" s="34" t="s">
+        <v>249</v>
+      </c>
+      <c r="C33" s="34" t="s">
+        <v>184</v>
+      </c>
+      <c r="D33" s="34" t="s">
         <v>250</v>
-      </c>
-      <c r="B33" s="34" t="s">
-        <v>251</v>
-      </c>
-      <c r="C33" s="34" t="s">
-        <v>186</v>
-      </c>
-      <c r="D33" s="34" t="s">
-        <v>252</v>
       </c>
       <c r="E33" s="34"/>
       <c r="F33" s="34"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="34" t="s">
+        <v>251</v>
+      </c>
+      <c r="B34" s="34" t="s">
+        <v>252</v>
+      </c>
+      <c r="C34" s="34" t="s">
+        <v>203</v>
+      </c>
+      <c r="D34" s="34" t="s">
         <v>253</v>
-      </c>
-      <c r="B34" s="34" t="s">
-        <v>254</v>
-      </c>
-      <c r="C34" s="34" t="s">
-        <v>205</v>
-      </c>
-      <c r="D34" s="34" t="s">
-        <v>255</v>
       </c>
       <c r="E34" s="34"/>
       <c r="F34" s="34"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="34" t="s">
+        <v>254</v>
+      </c>
+      <c r="B35" s="34" t="s">
+        <v>255</v>
+      </c>
+      <c r="C35" s="34" t="s">
         <v>256</v>
       </c>
-      <c r="B35" s="34" t="s">
+      <c r="D35" s="34" t="s">
         <v>257</v>
-      </c>
-      <c r="C35" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="D35" s="34" t="s">
-        <v>259</v>
       </c>
       <c r="E35" s="34"/>
       <c r="F35" s="34"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="34" t="s">
+        <v>258</v>
+      </c>
+      <c r="B36" s="34" t="s">
+        <v>259</v>
+      </c>
+      <c r="C36" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="D36" s="34" t="s">
         <v>260</v>
-      </c>
-      <c r="B36" s="34" t="s">
-        <v>261</v>
-      </c>
-      <c r="C36" s="34" t="s">
-        <v>178</v>
-      </c>
-      <c r="D36" s="34" t="s">
-        <v>262</v>
       </c>
       <c r="E36" s="34"/>
       <c r="F36" s="34"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="34" t="s">
+        <v>261</v>
+      </c>
+      <c r="B37" s="34" t="s">
+        <v>262</v>
+      </c>
+      <c r="C37" s="34" t="s">
+        <v>191</v>
+      </c>
+      <c r="D37" s="34" t="s">
         <v>263</v>
-      </c>
-      <c r="B37" s="34" t="s">
-        <v>264</v>
-      </c>
-      <c r="C37" s="34" t="s">
-        <v>193</v>
-      </c>
-      <c r="D37" s="34" t="s">
-        <v>265</v>
       </c>
       <c r="E37" s="34"/>
       <c r="F37" s="34"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="34" t="s">
+        <v>264</v>
+      </c>
+      <c r="B38" s="34" t="s">
+        <v>265</v>
+      </c>
+      <c r="C38" s="34" t="s">
         <v>266</v>
       </c>
-      <c r="B38" s="34" t="s">
+      <c r="D38" s="34" t="s">
         <v>267</v>
-      </c>
-      <c r="C38" s="34" t="s">
-        <v>268</v>
-      </c>
-      <c r="D38" s="34" t="s">
-        <v>269</v>
       </c>
       <c r="E38" s="34"/>
       <c r="F38" s="34"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="34" t="s">
+        <v>268</v>
+      </c>
+      <c r="B39" s="34" t="s">
+        <v>269</v>
+      </c>
+      <c r="C39" s="34" t="s">
         <v>270</v>
       </c>
-      <c r="B39" s="34" t="s">
+      <c r="D39" s="34" t="s">
         <v>271</v>
-      </c>
-      <c r="C39" s="34" t="s">
-        <v>272</v>
-      </c>
-      <c r="D39" s="34" t="s">
-        <v>273</v>
       </c>
       <c r="E39" s="34"/>
       <c r="F39" s="34"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="34" t="s">
+        <v>272</v>
+      </c>
+      <c r="B40" s="34" t="s">
+        <v>273</v>
+      </c>
+      <c r="C40" s="34" t="s">
         <v>274</v>
       </c>
-      <c r="B40" s="34" t="s">
+      <c r="D40" s="34" t="s">
         <v>275</v>
-      </c>
-      <c r="C40" s="34" t="s">
-        <v>276</v>
-      </c>
-      <c r="D40" s="34" t="s">
-        <v>277</v>
       </c>
       <c r="E40" s="34"/>
       <c r="F40" s="34"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="34" t="s">
+        <v>276</v>
+      </c>
+      <c r="B41" s="34" t="s">
+        <v>277</v>
+      </c>
+      <c r="C41" s="34" t="s">
         <v>278</v>
       </c>
-      <c r="B41" s="34" t="s">
+      <c r="D41" s="34" t="s">
         <v>279</v>
-      </c>
-      <c r="C41" s="34" t="s">
-        <v>280</v>
-      </c>
-      <c r="D41" s="34" t="s">
-        <v>281</v>
       </c>
       <c r="E41" s="34"/>
       <c r="F41" s="34"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="34" t="s">
+        <v>280</v>
+      </c>
+      <c r="B42" s="34" t="s">
+        <v>281</v>
+      </c>
+      <c r="C42" s="34" t="s">
+        <v>216</v>
+      </c>
+      <c r="D42" s="34" t="s">
         <v>282</v>
-      </c>
-      <c r="B42" s="34" t="s">
-        <v>283</v>
-      </c>
-      <c r="C42" s="34" t="s">
-        <v>218</v>
-      </c>
-      <c r="D42" s="34" t="s">
-        <v>284</v>
       </c>
       <c r="E42" s="34"/>
       <c r="F42" s="34"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="34" t="s">
+        <v>283</v>
+      </c>
+      <c r="B43" s="34" t="s">
+        <v>284</v>
+      </c>
+      <c r="C43" s="34" t="s">
         <v>285</v>
       </c>
-      <c r="B43" s="34" t="s">
+      <c r="D43" s="34" t="s">
         <v>286</v>
-      </c>
-      <c r="C43" s="34" t="s">
-        <v>287</v>
-      </c>
-      <c r="D43" s="34" t="s">
-        <v>288</v>
       </c>
       <c r="E43" s="34"/>
       <c r="F43" s="34"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="34" t="s">
+        <v>287</v>
+      </c>
+      <c r="B44" s="34" t="s">
+        <v>288</v>
+      </c>
+      <c r="C44" s="34" t="s">
         <v>289</v>
       </c>
-      <c r="B44" s="34" t="s">
+      <c r="D44" s="34" t="s">
         <v>290</v>
-      </c>
-      <c r="C44" s="34" t="s">
-        <v>291</v>
-      </c>
-      <c r="D44" s="34" t="s">
-        <v>292</v>
       </c>
       <c r="E44" s="34"/>
       <c r="F44" s="34"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="34" t="s">
+        <v>291</v>
+      </c>
+      <c r="B45" s="34" t="s">
+        <v>292</v>
+      </c>
+      <c r="C45" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="D45" s="34" t="s">
         <v>293</v>
-      </c>
-      <c r="B45" s="34" t="s">
-        <v>294</v>
-      </c>
-      <c r="C45" s="34" t="s">
-        <v>174</v>
-      </c>
-      <c r="D45" s="34" t="s">
-        <v>295</v>
       </c>
       <c r="E45" s="34"/>
       <c r="F45" s="34"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="34" t="s">
+        <v>294</v>
+      </c>
+      <c r="B46" s="34" t="s">
+        <v>295</v>
+      </c>
+      <c r="C46" s="34" t="s">
+        <v>164</v>
+      </c>
+      <c r="D46" s="34" t="s">
         <v>296</v>
-      </c>
-      <c r="B46" s="34" t="s">
-        <v>297</v>
-      </c>
-      <c r="C46" s="34" t="s">
-        <v>166</v>
-      </c>
-      <c r="D46" s="34" t="s">
-        <v>298</v>
       </c>
       <c r="E46" s="34"/>
       <c r="F46" s="34"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="34" t="s">
+        <v>297</v>
+      </c>
+      <c r="B47" s="34" t="s">
+        <v>298</v>
+      </c>
+      <c r="C47" s="34" t="s">
         <v>299</v>
       </c>
-      <c r="B47" s="34" t="s">
+      <c r="D47" s="34" t="s">
         <v>300</v>
-      </c>
-      <c r="C47" s="34" t="s">
-        <v>301</v>
-      </c>
-      <c r="D47" s="34" t="s">
-        <v>302</v>
       </c>
       <c r="E47" s="34"/>
       <c r="F47" s="34"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="34" t="s">
+        <v>301</v>
+      </c>
+      <c r="B48" s="34" t="s">
+        <v>302</v>
+      </c>
+      <c r="C48" s="34" t="s">
         <v>303</v>
       </c>
-      <c r="B48" s="34" t="s">
+      <c r="D48" s="34" t="s">
         <v>304</v>
-      </c>
-      <c r="C48" s="34" t="s">
-        <v>305</v>
-      </c>
-      <c r="D48" s="34" t="s">
-        <v>306</v>
       </c>
       <c r="E48" s="34"/>
       <c r="F48" s="34"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="34" t="s">
+        <v>305</v>
+      </c>
+      <c r="B49" s="34" t="s">
+        <v>306</v>
+      </c>
+      <c r="C49" s="34" t="s">
+        <v>285</v>
+      </c>
+      <c r="D49" s="34" t="s">
         <v>307</v>
-      </c>
-      <c r="B49" s="34" t="s">
-        <v>308</v>
-      </c>
-      <c r="C49" s="34" t="s">
-        <v>287</v>
-      </c>
-      <c r="D49" s="34" t="s">
-        <v>309</v>
       </c>
       <c r="E49" s="34"/>
       <c r="F49" s="34"/>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="34" t="s">
+        <v>308</v>
+      </c>
+      <c r="B50" s="34" t="s">
+        <v>309</v>
+      </c>
+      <c r="C50" s="34" t="s">
         <v>310</v>
       </c>
-      <c r="B50" s="34" t="s">
+      <c r="D50" s="34" t="s">
         <v>311</v>
-      </c>
-      <c r="C50" s="34" t="s">
-        <v>312</v>
-      </c>
-      <c r="D50" s="34" t="s">
-        <v>313</v>
       </c>
       <c r="E50" s="34"/>
       <c r="F50" s="34"/>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="34" t="s">
+        <v>312</v>
+      </c>
+      <c r="B51" s="34" t="s">
+        <v>313</v>
+      </c>
+      <c r="C51" s="34" t="s">
+        <v>184</v>
+      </c>
+      <c r="D51" s="34" t="s">
         <v>314</v>
-      </c>
-      <c r="B51" s="34" t="s">
-        <v>315</v>
-      </c>
-      <c r="C51" s="34" t="s">
-        <v>186</v>
-      </c>
-      <c r="D51" s="34" t="s">
-        <v>316</v>
       </c>
       <c r="E51" s="34"/>
       <c r="F51" s="34"/>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="34" t="s">
+        <v>315</v>
+      </c>
+      <c r="B52" s="34" t="s">
+        <v>316</v>
+      </c>
+      <c r="C52" s="34" t="s">
         <v>317</v>
       </c>
-      <c r="B52" s="34" t="s">
+      <c r="D52" s="34" t="s">
         <v>318</v>
-      </c>
-      <c r="C52" s="34" t="s">
-        <v>319</v>
-      </c>
-      <c r="D52" s="34" t="s">
-        <v>320</v>
       </c>
       <c r="E52" s="34"/>
       <c r="F52" s="34"/>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="34" t="s">
+        <v>319</v>
+      </c>
+      <c r="B53" s="34" t="s">
+        <v>320</v>
+      </c>
+      <c r="C53" s="34" t="s">
+        <v>303</v>
+      </c>
+      <c r="D53" s="34" t="s">
         <v>321</v>
-      </c>
-      <c r="B53" s="34" t="s">
-        <v>322</v>
-      </c>
-      <c r="C53" s="34" t="s">
-        <v>305</v>
-      </c>
-      <c r="D53" s="34" t="s">
-        <v>323</v>
       </c>
       <c r="E53" s="34"/>
       <c r="F53" s="34"/>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="34" t="s">
+        <v>322</v>
+      </c>
+      <c r="B54" s="34" t="s">
+        <v>323</v>
+      </c>
+      <c r="C54" s="34" t="s">
+        <v>164</v>
+      </c>
+      <c r="D54" s="34" t="s">
         <v>324</v>
-      </c>
-      <c r="B54" s="34" t="s">
-        <v>325</v>
-      </c>
-      <c r="C54" s="34" t="s">
-        <v>166</v>
-      </c>
-      <c r="D54" s="34" t="s">
-        <v>326</v>
       </c>
       <c r="E54" s="34"/>
       <c r="F54" s="34"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="34" t="s">
+        <v>325</v>
+      </c>
+      <c r="B55" s="34" t="s">
+        <v>326</v>
+      </c>
+      <c r="C55" s="34" t="s">
+        <v>184</v>
+      </c>
+      <c r="D55" s="34" t="s">
         <v>327</v>
-      </c>
-      <c r="B55" s="34" t="s">
-        <v>328</v>
-      </c>
-      <c r="C55" s="34" t="s">
-        <v>186</v>
-      </c>
-      <c r="D55" s="34" t="s">
-        <v>329</v>
       </c>
       <c r="E55" s="34"/>
       <c r="F55" s="34"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="34" t="s">
+        <v>328</v>
+      </c>
+      <c r="B56" s="34" t="s">
+        <v>329</v>
+      </c>
+      <c r="C56" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="D56" s="34" t="s">
         <v>330</v>
-      </c>
-      <c r="B56" s="34" t="s">
-        <v>331</v>
-      </c>
-      <c r="C56" s="34" t="s">
-        <v>138</v>
-      </c>
-      <c r="D56" s="34" t="s">
-        <v>332</v>
       </c>
       <c r="E56" s="34"/>
       <c r="F56" s="34"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="34" t="s">
+        <v>331</v>
+      </c>
+      <c r="B57" s="34" t="s">
+        <v>332</v>
+      </c>
+      <c r="C57" s="34" t="s">
+        <v>172</v>
+      </c>
+      <c r="D57" s="34" t="s">
         <v>333</v>
-      </c>
-      <c r="B57" s="34" t="s">
-        <v>334</v>
-      </c>
-      <c r="C57" s="34" t="s">
-        <v>174</v>
-      </c>
-      <c r="D57" s="34" t="s">
-        <v>335</v>
       </c>
       <c r="E57" s="34"/>
       <c r="F57" s="34"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="34" t="s">
+        <v>334</v>
+      </c>
+      <c r="B58" s="34" t="s">
+        <v>335</v>
+      </c>
+      <c r="C58" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="D58" s="34" t="s">
         <v>336</v>
-      </c>
-      <c r="B58" s="34" t="s">
-        <v>337</v>
-      </c>
-      <c r="C58" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="D58" s="34" t="s">
-        <v>338</v>
       </c>
       <c r="E58" s="34"/>
       <c r="F58" s="34"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="34" t="s">
+        <v>337</v>
+      </c>
+      <c r="B59" s="34" t="s">
+        <v>338</v>
+      </c>
+      <c r="C59" s="34" t="s">
+        <v>191</v>
+      </c>
+      <c r="D59" s="34" t="s">
         <v>339</v>
-      </c>
-      <c r="B59" s="34" t="s">
-        <v>340</v>
-      </c>
-      <c r="C59" s="34" t="s">
-        <v>193</v>
-      </c>
-      <c r="D59" s="34" t="s">
-        <v>341</v>
       </c>
       <c r="E59" s="34"/>
       <c r="F59" s="34"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="34" t="s">
+        <v>340</v>
+      </c>
+      <c r="B60" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="C60" s="34" t="s">
         <v>342</v>
       </c>
-      <c r="B60" s="34" t="s">
+      <c r="D60" s="34" t="s">
         <v>343</v>
-      </c>
-      <c r="C60" s="34" t="s">
-        <v>344</v>
-      </c>
-      <c r="D60" s="34" t="s">
-        <v>345</v>
       </c>
       <c r="E60" s="34"/>
       <c r="F60" s="34"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="34" t="s">
+        <v>344</v>
+      </c>
+      <c r="B61" s="34" t="s">
+        <v>345</v>
+      </c>
+      <c r="C61" s="34" t="s">
+        <v>136</v>
+      </c>
+      <c r="D61" s="34" t="s">
         <v>346</v>
-      </c>
-      <c r="B61" s="34" t="s">
-        <v>347</v>
-      </c>
-      <c r="C61" s="34" t="s">
-        <v>138</v>
-      </c>
-      <c r="D61" s="34" t="s">
-        <v>348</v>
       </c>
       <c r="E61" s="34"/>
       <c r="F61" s="34"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="34" t="s">
+        <v>347</v>
+      </c>
+      <c r="B62" s="34" t="s">
+        <v>348</v>
+      </c>
+      <c r="C62" s="34" t="s">
         <v>349</v>
       </c>
-      <c r="B62" s="34" t="s">
+      <c r="D62" s="34" t="s">
         <v>350</v>
-      </c>
-      <c r="C62" s="34" t="s">
-        <v>351</v>
-      </c>
-      <c r="D62" s="34" t="s">
-        <v>352</v>
       </c>
       <c r="E62" s="34"/>
       <c r="F62" s="34"/>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="34" t="s">
+        <v>351</v>
+      </c>
+      <c r="B63" s="34" t="s">
+        <v>352</v>
+      </c>
+      <c r="C63" s="34" t="s">
         <v>353</v>
       </c>
-      <c r="B63" s="34" t="s">
+      <c r="D63" s="34" t="s">
         <v>354</v>
-      </c>
-      <c r="C63" s="34" t="s">
-        <v>355</v>
-      </c>
-      <c r="D63" s="34" t="s">
-        <v>356</v>
       </c>
       <c r="E63" s="34"/>
       <c r="F63" s="34"/>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="34" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="B64" s="34" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C64" s="34" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D64" s="34" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="E64" s="34"/>
       <c r="F64" s="34"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="34" t="s">
+        <v>394</v>
+      </c>
+      <c r="B65" s="34" t="s">
+        <v>395</v>
+      </c>
+      <c r="C65" s="34" t="s">
+        <v>278</v>
+      </c>
+      <c r="D65" s="34" t="s">
         <v>396</v>
-      </c>
-      <c r="B65" s="34" t="s">
-        <v>397</v>
-      </c>
-      <c r="C65" s="34" t="s">
-        <v>280</v>
-      </c>
-      <c r="D65" s="34" t="s">
-        <v>398</v>
       </c>
       <c r="E65" s="34"/>
       <c r="F65" s="34"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="34" t="s">
+        <v>397</v>
+      </c>
+      <c r="B66" s="34" t="s">
+        <v>370</v>
+      </c>
+      <c r="C66" s="34" t="s">
+        <v>398</v>
+      </c>
+      <c r="D66" s="34" t="s">
         <v>399</v>
-      </c>
-      <c r="B66" s="34" t="s">
-        <v>372</v>
-      </c>
-      <c r="C66" s="34" t="s">
-        <v>400</v>
-      </c>
-      <c r="D66" s="34" t="s">
-        <v>401</v>
       </c>
       <c r="E66" s="34"/>
       <c r="F66" s="34"/>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="34" t="s">
+        <v>400</v>
+      </c>
+      <c r="B67" s="34" t="s">
+        <v>401</v>
+      </c>
+      <c r="C67" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="D67" s="34" t="s">
         <v>402</v>
-      </c>
-      <c r="B67" s="34" t="s">
-        <v>403</v>
-      </c>
-      <c r="C67" s="34" t="s">
-        <v>222</v>
-      </c>
-      <c r="D67" s="34" t="s">
-        <v>404</v>
       </c>
       <c r="E67" s="34"/>
       <c r="F67" s="34"/>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="34" t="s">
+        <v>403</v>
+      </c>
+      <c r="B68" s="34" t="s">
+        <v>379</v>
+      </c>
+      <c r="C68" s="34" t="s">
+        <v>404</v>
+      </c>
+      <c r="D68" s="34" t="s">
         <v>405</v>
-      </c>
-      <c r="B68" s="34" t="s">
-        <v>381</v>
-      </c>
-      <c r="C68" s="34" t="s">
-        <v>406</v>
-      </c>
-      <c r="D68" s="34" t="s">
-        <v>407</v>
       </c>
       <c r="E68" s="34"/>
       <c r="F68" s="34"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="34" t="s">
+        <v>406</v>
+      </c>
+      <c r="B69" s="34" t="s">
+        <v>407</v>
+      </c>
+      <c r="C69" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="D69" s="34" t="s">
         <v>408</v>
-      </c>
-      <c r="B69" s="34" t="s">
-        <v>409</v>
-      </c>
-      <c r="C69" s="34" t="s">
-        <v>150</v>
-      </c>
-      <c r="D69" s="34" t="s">
-        <v>410</v>
       </c>
       <c r="E69" s="34"/>
       <c r="F69" s="34"/>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="34" t="s">
+        <v>409</v>
+      </c>
+      <c r="B70" s="34" t="s">
+        <v>410</v>
+      </c>
+      <c r="C70" s="34" t="s">
         <v>411</v>
       </c>
-      <c r="B70" s="34" t="s">
+      <c r="D70" s="34" t="s">
         <v>412</v>
-      </c>
-      <c r="C70" s="34" t="s">
-        <v>413</v>
-      </c>
-      <c r="D70" s="34" t="s">
-        <v>414</v>
       </c>
       <c r="E70" s="34"/>
       <c r="F70" s="34"/>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="34" t="s">
+        <v>413</v>
+      </c>
+      <c r="B71" s="34" t="s">
+        <v>414</v>
+      </c>
+      <c r="C71" s="34" t="s">
         <v>415</v>
       </c>
-      <c r="B71" s="34" t="s">
+      <c r="D71" s="34" t="s">
         <v>416</v>
-      </c>
-      <c r="C71" s="34" t="s">
-        <v>417</v>
-      </c>
-      <c r="D71" s="34" t="s">
-        <v>418</v>
       </c>
       <c r="E71" s="34"/>
       <c r="F71" s="34"/>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="34" t="s">
+        <v>417</v>
+      </c>
+      <c r="B72" s="34" t="s">
+        <v>418</v>
+      </c>
+      <c r="C72" s="34" t="s">
+        <v>285</v>
+      </c>
+      <c r="D72" s="34" t="s">
         <v>419</v>
-      </c>
-      <c r="B72" s="34" t="s">
-        <v>420</v>
-      </c>
-      <c r="C72" s="34" t="s">
-        <v>287</v>
-      </c>
-      <c r="D72" s="34" t="s">
-        <v>421</v>
       </c>
       <c r="E72" s="34"/>
       <c r="F72" s="34"/>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="34" t="s">
+        <v>420</v>
+      </c>
+      <c r="B73" s="34" t="s">
+        <v>387</v>
+      </c>
+      <c r="C73" s="34" t="s">
+        <v>421</v>
+      </c>
+      <c r="D73" s="34" t="s">
         <v>422</v>
-      </c>
-      <c r="B73" s="34" t="s">
-        <v>389</v>
-      </c>
-      <c r="C73" s="34" t="s">
-        <v>423</v>
-      </c>
-      <c r="D73" s="34" t="s">
-        <v>424</v>
       </c>
       <c r="E73" s="34"/>
       <c r="F73" s="34"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="34" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B74" s="34" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C74" s="34" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D74" s="34" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E74" s="34"/>
       <c r="F74" s="34"/>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="34" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B75" s="34" t="s">
+        <v>425</v>
+      </c>
+      <c r="C75" s="34" t="s">
+        <v>426</v>
+      </c>
+      <c r="D75" s="34" t="s">
         <v>427</v>
-      </c>
-      <c r="C75" s="34" t="s">
-        <v>428</v>
-      </c>
-      <c r="D75" s="34" t="s">
-        <v>429</v>
       </c>
       <c r="E75" s="34"/>
       <c r="F75" s="34"/>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="34" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="B76" s="34" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C76" s="34" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D76" s="34" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E76" s="34"/>
       <c r="F76" s="34"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="34" t="s">
+        <v>430</v>
+      </c>
+      <c r="B77" s="34" t="s">
+        <v>431</v>
+      </c>
+      <c r="C77" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="D77" s="34" t="s">
         <v>432</v>
-      </c>
-      <c r="B77" s="34" t="s">
-        <v>433</v>
-      </c>
-      <c r="C77" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="D77" s="34" t="s">
-        <v>434</v>
       </c>
       <c r="E77" s="34"/>
       <c r="F77" s="34"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="34" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B78" s="34" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C78" s="34" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D78" s="34" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E78" s="34"/>
       <c r="F78" s="34"/>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="34" t="s">
+        <v>435</v>
+      </c>
+      <c r="B79" s="34" t="s">
+        <v>436</v>
+      </c>
+      <c r="C79" s="34" t="s">
+        <v>184</v>
+      </c>
+      <c r="D79" s="34" t="s">
         <v>437</v>
-      </c>
-      <c r="B79" s="34" t="s">
-        <v>438</v>
-      </c>
-      <c r="C79" s="34" t="s">
-        <v>186</v>
-      </c>
-      <c r="D79" s="34" t="s">
-        <v>439</v>
       </c>
       <c r="E79" s="34"/>
       <c r="F79" s="34"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="34" t="s">
+        <v>438</v>
+      </c>
+      <c r="B80" s="34" t="s">
+        <v>367</v>
+      </c>
+      <c r="C80" s="34" t="s">
+        <v>439</v>
+      </c>
+      <c r="D80" s="34" t="s">
         <v>440</v>
-      </c>
-      <c r="B80" s="34" t="s">
-        <v>369</v>
-      </c>
-      <c r="C80" s="34" t="s">
-        <v>441</v>
-      </c>
-      <c r="D80" s="34" t="s">
-        <v>442</v>
       </c>
       <c r="E80" s="34"/>
       <c r="F80" s="34"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="34" t="s">
+        <v>441</v>
+      </c>
+      <c r="B81" s="34" t="s">
+        <v>442</v>
+      </c>
+      <c r="C81" s="34" t="s">
+        <v>285</v>
+      </c>
+      <c r="D81" s="34" t="s">
         <v>443</v>
-      </c>
-      <c r="B81" s="34" t="s">
-        <v>444</v>
-      </c>
-      <c r="C81" s="34" t="s">
-        <v>287</v>
-      </c>
-      <c r="D81" s="34" t="s">
-        <v>445</v>
       </c>
       <c r="E81" s="34"/>
       <c r="F81" s="34"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="34" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B82" s="34" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C82" s="34" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D82" s="34" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E82" s="34"/>
       <c r="F82" s="34"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="34" t="s">
+        <v>446</v>
+      </c>
+      <c r="B83" s="34" t="s">
+        <v>372</v>
+      </c>
+      <c r="C83" s="34" t="s">
+        <v>447</v>
+      </c>
+      <c r="D83" s="34" t="s">
         <v>448</v>
-      </c>
-      <c r="B83" s="34" t="s">
-        <v>374</v>
-      </c>
-      <c r="C83" s="34" t="s">
-        <v>449</v>
-      </c>
-      <c r="D83" s="34" t="s">
-        <v>450</v>
       </c>
       <c r="E83" s="34"/>
       <c r="F83" s="34"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="34" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="B84" s="34" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C84" s="34" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D84" s="34" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E84" s="34"/>
       <c r="F84" s="34"/>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="34" t="s">
+        <v>451</v>
+      </c>
+      <c r="B85" s="34" t="s">
+        <v>452</v>
+      </c>
+      <c r="C85" s="34" t="s">
+        <v>256</v>
+      </c>
+      <c r="D85" s="34" t="s">
         <v>453</v>
-      </c>
-      <c r="B85" s="34" t="s">
-        <v>454</v>
-      </c>
-      <c r="C85" s="34" t="s">
-        <v>258</v>
-      </c>
-      <c r="D85" s="34" t="s">
-        <v>455</v>
       </c>
       <c r="E85" s="34"/>
       <c r="F85" s="34"/>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="34" t="s">
+        <v>454</v>
+      </c>
+      <c r="B86" s="34" t="s">
+        <v>455</v>
+      </c>
+      <c r="C86" s="34" t="s">
+        <v>184</v>
+      </c>
+      <c r="D86" s="34" t="s">
         <v>456</v>
-      </c>
-      <c r="B86" s="34" t="s">
-        <v>457</v>
-      </c>
-      <c r="C86" s="34" t="s">
-        <v>186</v>
-      </c>
-      <c r="D86" s="34" t="s">
-        <v>458</v>
       </c>
       <c r="E86" s="34"/>
       <c r="F86" s="34"/>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="34" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="B87" s="34" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="C87" s="34" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D87" s="34" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="E87" s="34"/>
       <c r="F87" s="34"/>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="34" t="s">
+        <v>459</v>
+      </c>
+      <c r="B88" s="34" t="s">
+        <v>460</v>
+      </c>
+      <c r="C88" s="34" t="s">
+        <v>274</v>
+      </c>
+      <c r="D88" s="34" t="s">
         <v>461</v>
-      </c>
-      <c r="B88" s="34" t="s">
-        <v>462</v>
-      </c>
-      <c r="C88" s="34" t="s">
-        <v>276</v>
-      </c>
-      <c r="D88" s="34" t="s">
-        <v>463</v>
       </c>
       <c r="E88" s="34"/>
       <c r="F88" s="34"/>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="34" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="B89" s="34" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="C89" s="34" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="D89" s="34" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E89" s="34"/>
       <c r="F89" s="34"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="34" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B90" s="34" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C90" s="34" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D90" s="34" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E90" s="34"/>
       <c r="F90" s="34"/>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="34" t="s">
+        <v>466</v>
+      </c>
+      <c r="B91" s="34" t="s">
+        <v>366</v>
+      </c>
+      <c r="C91" s="34" t="s">
+        <v>467</v>
+      </c>
+      <c r="D91" s="34" t="s">
         <v>468</v>
-      </c>
-      <c r="B91" s="34" t="s">
-        <v>368</v>
-      </c>
-      <c r="C91" s="34" t="s">
-        <v>469</v>
-      </c>
-      <c r="D91" s="34" t="s">
-        <v>470</v>
       </c>
       <c r="E91" s="34"/>
       <c r="F91" s="34"/>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="34" t="s">
+        <v>469</v>
+      </c>
+      <c r="B92" s="34" t="s">
+        <v>470</v>
+      </c>
+      <c r="C92" s="34" t="s">
+        <v>184</v>
+      </c>
+      <c r="D92" s="34" t="s">
         <v>471</v>
-      </c>
-      <c r="B92" s="34" t="s">
-        <v>472</v>
-      </c>
-      <c r="C92" s="34" t="s">
-        <v>186</v>
-      </c>
-      <c r="D92" s="34" t="s">
-        <v>473</v>
       </c>
       <c r="E92" s="34"/>
       <c r="F92" s="34"/>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="34" t="s">
+        <v>472</v>
+      </c>
+      <c r="B93" s="34" t="s">
+        <v>473</v>
+      </c>
+      <c r="C93" s="34" t="s">
+        <v>310</v>
+      </c>
+      <c r="D93" s="34" t="s">
         <v>474</v>
-      </c>
-      <c r="B93" s="34" t="s">
-        <v>475</v>
-      </c>
-      <c r="C93" s="34" t="s">
-        <v>312</v>
-      </c>
-      <c r="D93" s="34" t="s">
-        <v>476</v>
       </c>
       <c r="E93" s="34"/>
       <c r="F93" s="34"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="34" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B94" s="34" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C94" s="34" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D94" s="34" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="E94" s="34"/>
       <c r="F94" s="34"/>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="34" t="s">
+        <v>477</v>
+      </c>
+      <c r="B95" s="34" t="s">
+        <v>478</v>
+      </c>
+      <c r="C95" s="34" t="s">
         <v>479</v>
       </c>
-      <c r="B95" s="34" t="s">
+      <c r="D95" s="34" t="s">
         <v>480</v>
-      </c>
-      <c r="C95" s="34" t="s">
-        <v>481</v>
-      </c>
-      <c r="D95" s="34" t="s">
-        <v>482</v>
       </c>
       <c r="E95" s="34"/>
       <c r="F95" s="34"/>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="34" t="s">
+        <v>481</v>
+      </c>
+      <c r="B96" s="34" t="s">
+        <v>482</v>
+      </c>
+      <c r="C96" s="34" t="s">
+        <v>289</v>
+      </c>
+      <c r="D96" s="34" t="s">
         <v>483</v>
-      </c>
-      <c r="B96" s="34" t="s">
-        <v>484</v>
-      </c>
-      <c r="C96" s="34" t="s">
-        <v>291</v>
-      </c>
-      <c r="D96" s="34" t="s">
-        <v>485</v>
       </c>
       <c r="E96" s="34"/>
       <c r="F96" s="34"/>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="34" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B97" s="34" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="C97" s="34" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D97" s="34" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E97" s="34"/>
       <c r="F97" s="34"/>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="34" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B98" s="34" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C98" s="34" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D98" s="34" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E98" s="34"/>
       <c r="F98" s="34"/>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="34" t="s">
+        <v>488</v>
+      </c>
+      <c r="B99" s="34" t="s">
+        <v>489</v>
+      </c>
+      <c r="C99" s="34" t="s">
+        <v>467</v>
+      </c>
+      <c r="D99" s="34" t="s">
         <v>490</v>
-      </c>
-      <c r="B99" s="34" t="s">
-        <v>491</v>
-      </c>
-      <c r="C99" s="34" t="s">
-        <v>469</v>
-      </c>
-      <c r="D99" s="34" t="s">
-        <v>492</v>
       </c>
       <c r="E99" s="34"/>
       <c r="F99" s="34"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="34" t="s">
+        <v>491</v>
+      </c>
+      <c r="B100" s="34" t="s">
+        <v>492</v>
+      </c>
+      <c r="C100" s="34" t="s">
+        <v>176</v>
+      </c>
+      <c r="D100" s="34" t="s">
         <v>493</v>
-      </c>
-      <c r="B100" s="34" t="s">
-        <v>494</v>
-      </c>
-      <c r="C100" s="34" t="s">
-        <v>178</v>
-      </c>
-      <c r="D100" s="34" t="s">
-        <v>495</v>
       </c>
       <c r="E100" s="34"/>
       <c r="F100" s="34"/>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="34" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B101" s="34" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C101" s="34" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D101" s="34" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="E101" s="34"/>
       <c r="F101" s="34"/>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="34" t="s">
+        <v>496</v>
+      </c>
+      <c r="B102" s="34" t="s">
+        <v>497</v>
+      </c>
+      <c r="C102" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="D102" s="34" t="s">
         <v>498</v>
-      </c>
-      <c r="B102" s="34" t="s">
-        <v>499</v>
-      </c>
-      <c r="C102" s="34" t="s">
-        <v>272</v>
-      </c>
-      <c r="D102" s="34" t="s">
-        <v>500</v>
       </c>
       <c r="E102" s="34"/>
       <c r="F102" s="34"/>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="34" t="s">
+        <v>499</v>
+      </c>
+      <c r="B103" s="34" t="s">
+        <v>500</v>
+      </c>
+      <c r="C103" s="34" t="s">
+        <v>310</v>
+      </c>
+      <c r="D103" s="34" t="s">
         <v>501</v>
-      </c>
-      <c r="B103" s="34" t="s">
-        <v>502</v>
-      </c>
-      <c r="C103" s="34" t="s">
-        <v>312</v>
-      </c>
-      <c r="D103" s="34" t="s">
-        <v>503</v>
       </c>
       <c r="E103" s="34"/>
       <c r="F103" s="34"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="34" t="s">
+        <v>502</v>
+      </c>
+      <c r="B104" s="34" t="s">
+        <v>503</v>
+      </c>
+      <c r="C104" s="34" t="s">
+        <v>411</v>
+      </c>
+      <c r="D104" s="34" t="s">
         <v>504</v>
-      </c>
-      <c r="B104" s="34" t="s">
-        <v>505</v>
-      </c>
-      <c r="C104" s="34" t="s">
-        <v>413</v>
-      </c>
-      <c r="D104" s="34" t="s">
-        <v>506</v>
       </c>
       <c r="E104" s="34"/>
       <c r="F104" s="34"/>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="34" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B105" s="34" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C105" s="34" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D105" s="34" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E105" s="34"/>
       <c r="F105" s="34"/>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="34" t="s">
+        <v>507</v>
+      </c>
+      <c r="B106" s="34" t="s">
+        <v>508</v>
+      </c>
+      <c r="C106" s="34" t="s">
+        <v>467</v>
+      </c>
+      <c r="D106" s="34" t="s">
         <v>509</v>
-      </c>
-      <c r="B106" s="34" t="s">
-        <v>510</v>
-      </c>
-      <c r="C106" s="34" t="s">
-        <v>469</v>
-      </c>
-      <c r="D106" s="34" t="s">
-        <v>511</v>
       </c>
       <c r="E106" s="34"/>
       <c r="F106" s="34"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="34" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="B107" s="34" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C107" s="34" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D107" s="34" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E107" s="34"/>
       <c r="F107" s="34"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="34" t="s">
+        <v>512</v>
+      </c>
+      <c r="B108" s="34" t="s">
+        <v>513</v>
+      </c>
+      <c r="C108" s="34" t="s">
+        <v>191</v>
+      </c>
+      <c r="D108" s="34" t="s">
         <v>514</v>
-      </c>
-      <c r="B108" s="34" t="s">
-        <v>515</v>
-      </c>
-      <c r="C108" s="34" t="s">
-        <v>193</v>
-      </c>
-      <c r="D108" s="34" t="s">
-        <v>516</v>
       </c>
       <c r="E108" s="34"/>
       <c r="F108" s="34"/>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="34" t="s">
+        <v>515</v>
+      </c>
+      <c r="B109" s="34" t="s">
+        <v>516</v>
+      </c>
+      <c r="C109" s="34" t="s">
+        <v>349</v>
+      </c>
+      <c r="D109" s="34" t="s">
         <v>517</v>
-      </c>
-      <c r="B109" s="34" t="s">
-        <v>518</v>
-      </c>
-      <c r="C109" s="34" t="s">
-        <v>351</v>
-      </c>
-      <c r="D109" s="34" t="s">
-        <v>519</v>
       </c>
       <c r="E109" s="34"/>
       <c r="F109" s="34"/>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="34" t="s">
+        <v>518</v>
+      </c>
+      <c r="B110" s="34" t="s">
+        <v>519</v>
+      </c>
+      <c r="C110" s="34" t="s">
+        <v>195</v>
+      </c>
+      <c r="D110" s="34" t="s">
         <v>520</v>
-      </c>
-      <c r="B110" s="34" t="s">
-        <v>521</v>
-      </c>
-      <c r="C110" s="34" t="s">
-        <v>197</v>
-      </c>
-      <c r="D110" s="34" t="s">
-        <v>522</v>
       </c>
       <c r="E110" s="34"/>
       <c r="F110" s="34"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="34" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="B111" s="34" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="C111" s="34" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D111" s="34" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="E111" s="34"/>
       <c r="F111" s="34"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="34" t="s">
+        <v>523</v>
+      </c>
+      <c r="B112" s="34" t="s">
+        <v>524</v>
+      </c>
+      <c r="C112" s="34" t="s">
+        <v>168</v>
+      </c>
+      <c r="D112" s="34" t="s">
         <v>525</v>
-      </c>
-      <c r="B112" s="34" t="s">
-        <v>526</v>
-      </c>
-      <c r="C112" s="34" t="s">
-        <v>170</v>
-      </c>
-      <c r="D112" s="34" t="s">
-        <v>527</v>
       </c>
       <c r="E112" s="34"/>
       <c r="F112" s="34"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="34" t="s">
+        <v>526</v>
+      </c>
+      <c r="B113" s="34" t="s">
+        <v>527</v>
+      </c>
+      <c r="C113" s="34" t="s">
+        <v>426</v>
+      </c>
+      <c r="D113" s="34" t="s">
         <v>528</v>
-      </c>
-      <c r="B113" s="34" t="s">
-        <v>529</v>
-      </c>
-      <c r="C113" s="34" t="s">
-        <v>428</v>
-      </c>
-      <c r="D113" s="34" t="s">
-        <v>530</v>
       </c>
       <c r="E113" s="34"/>
       <c r="F113" s="34"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="34" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="B114" s="34" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C114" s="34" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="D114" s="34" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E114" s="34"/>
       <c r="F114" s="34"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="34" t="s">
+        <v>531</v>
+      </c>
+      <c r="B115" s="34" t="s">
+        <v>388</v>
+      </c>
+      <c r="C115" s="34" t="s">
+        <v>532</v>
+      </c>
+      <c r="D115" s="34" t="s">
         <v>533</v>
-      </c>
-      <c r="B115" s="34" t="s">
-        <v>390</v>
-      </c>
-      <c r="C115" s="34" t="s">
-        <v>534</v>
-      </c>
-      <c r="D115" s="34" t="s">
-        <v>535</v>
       </c>
       <c r="E115" s="34"/>
       <c r="F115" s="34"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="34" t="s">
+        <v>534</v>
+      </c>
+      <c r="B116" s="34" t="s">
+        <v>535</v>
+      </c>
+      <c r="C116" s="34" t="s">
+        <v>353</v>
+      </c>
+      <c r="D116" s="34" t="s">
         <v>536</v>
-      </c>
-      <c r="B116" s="34" t="s">
-        <v>537</v>
-      </c>
-      <c r="C116" s="34" t="s">
-        <v>355</v>
-      </c>
-      <c r="D116" s="34" t="s">
-        <v>538</v>
       </c>
       <c r="E116" s="34"/>
       <c r="F116" s="34"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="34" t="s">
+        <v>537</v>
+      </c>
+      <c r="B117" s="34" t="s">
+        <v>538</v>
+      </c>
+      <c r="C117" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="D117" s="34" t="s">
         <v>539</v>
-      </c>
-      <c r="B117" s="34" t="s">
-        <v>540</v>
-      </c>
-      <c r="C117" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="D117" s="34" t="s">
-        <v>541</v>
       </c>
       <c r="E117" s="34"/>
       <c r="F117" s="34"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="34" t="s">
+        <v>540</v>
+      </c>
+      <c r="B118" s="34" t="s">
+        <v>541</v>
+      </c>
+      <c r="C118" s="34" t="s">
+        <v>164</v>
+      </c>
+      <c r="D118" s="34" t="s">
         <v>542</v>
-      </c>
-      <c r="B118" s="34" t="s">
-        <v>543</v>
-      </c>
-      <c r="C118" s="34" t="s">
-        <v>166</v>
-      </c>
-      <c r="D118" s="34" t="s">
-        <v>544</v>
       </c>
       <c r="E118" s="34"/>
       <c r="F118" s="34"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="34" t="s">
+        <v>543</v>
+      </c>
+      <c r="B119" s="34" t="s">
+        <v>544</v>
+      </c>
+      <c r="C119" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="D119" s="34" t="s">
         <v>545</v>
-      </c>
-      <c r="B119" s="34" t="s">
-        <v>546</v>
-      </c>
-      <c r="C119" s="34" t="s">
-        <v>150</v>
-      </c>
-      <c r="D119" s="34" t="s">
-        <v>547</v>
       </c>
       <c r="E119" s="34"/>
       <c r="F119" s="34"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="34" t="s">
+        <v>546</v>
+      </c>
+      <c r="B120" s="34" t="s">
+        <v>163</v>
+      </c>
+      <c r="C120" s="34" t="s">
+        <v>547</v>
+      </c>
+      <c r="D120" s="34" t="s">
         <v>548</v>
-      </c>
-      <c r="B120" s="34" t="s">
-        <v>165</v>
-      </c>
-      <c r="C120" s="34" t="s">
-        <v>549</v>
-      </c>
-      <c r="D120" s="34" t="s">
-        <v>550</v>
       </c>
       <c r="E120" s="34"/>
       <c r="F120" s="34"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="34" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B121" s="34" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C121" s="34" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="D121" s="34" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="E121" s="34"/>
       <c r="F121" s="34"/>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="34" t="s">
+        <v>551</v>
+      </c>
+      <c r="B122" s="34" t="s">
+        <v>552</v>
+      </c>
+      <c r="C122" s="34" t="s">
+        <v>447</v>
+      </c>
+      <c r="D122" s="34" t="s">
         <v>553</v>
-      </c>
-      <c r="B122" s="34" t="s">
-        <v>554</v>
-      </c>
-      <c r="C122" s="34" t="s">
-        <v>449</v>
-      </c>
-      <c r="D122" s="34" t="s">
-        <v>555</v>
       </c>
       <c r="E122" s="34"/>
       <c r="F122" s="34"/>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="34" t="s">
+        <v>554</v>
+      </c>
+      <c r="B123" s="34" t="s">
+        <v>555</v>
+      </c>
+      <c r="C123" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="D123" s="34" t="s">
         <v>556</v>
-      </c>
-      <c r="B123" s="34" t="s">
-        <v>557</v>
-      </c>
-      <c r="C123" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="D123" s="34" t="s">
-        <v>558</v>
       </c>
       <c r="E123" s="34"/>
       <c r="F123" s="34"/>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="34" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="B124" s="34" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C124" s="34" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D124" s="34" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="E124" s="34"/>
       <c r="F124" s="34"/>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="34" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="B125" s="34" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C125" s="34" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D125" s="34" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="E125" s="34"/>
       <c r="F125" s="34"/>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="34" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="B126" s="34" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C126" s="34" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D126" s="34" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="E126" s="34"/>
       <c r="F126" s="34"/>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="34" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B127" s="34" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C127" s="34" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D127" s="34" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="E127" s="34"/>
       <c r="F127" s="34"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="34" t="s">
+        <v>565</v>
+      </c>
+      <c r="B128" s="34" t="s">
+        <v>566</v>
+      </c>
+      <c r="C128" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="D128" s="34" t="s">
         <v>567</v>
-      </c>
-      <c r="B128" s="34" t="s">
-        <v>568</v>
-      </c>
-      <c r="C128" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="D128" s="34" t="s">
-        <v>569</v>
       </c>
       <c r="E128" s="34"/>
       <c r="F128" s="34"/>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="34" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="B129" s="34" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C129" s="34" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D129" s="34" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E129" s="34"/>
       <c r="F129" s="34"/>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="34" t="s">
+        <v>570</v>
+      </c>
+      <c r="B130" s="34" t="s">
+        <v>571</v>
+      </c>
+      <c r="C130" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="D130" s="34" t="s">
         <v>572</v>
-      </c>
-      <c r="B130" s="34" t="s">
-        <v>573</v>
-      </c>
-      <c r="C130" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="D130" s="34" t="s">
-        <v>574</v>
       </c>
       <c r="E130" s="34"/>
       <c r="F130" s="34"/>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="34" t="s">
+        <v>573</v>
+      </c>
+      <c r="B131" s="34" t="s">
+        <v>574</v>
+      </c>
+      <c r="C131" s="34" t="s">
         <v>575</v>
       </c>
-      <c r="B131" s="34" t="s">
+      <c r="D131" s="34" t="s">
         <v>576</v>
-      </c>
-      <c r="C131" s="34" t="s">
-        <v>577</v>
-      </c>
-      <c r="D131" s="34" t="s">
-        <v>578</v>
       </c>
       <c r="E131" s="34"/>
       <c r="F131" s="34"/>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="34" t="s">
+        <v>577</v>
+      </c>
+      <c r="B132" s="34" t="s">
+        <v>578</v>
+      </c>
+      <c r="C132" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="D132" s="34" t="s">
         <v>579</v>
-      </c>
-      <c r="B132" s="34" t="s">
-        <v>580</v>
-      </c>
-      <c r="C132" s="34" t="s">
-        <v>222</v>
-      </c>
-      <c r="D132" s="34" t="s">
-        <v>581</v>
       </c>
       <c r="E132" s="34"/>
       <c r="F132" s="34"/>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="34" t="s">
+        <v>580</v>
+      </c>
+      <c r="B133" s="34" t="s">
+        <v>581</v>
+      </c>
+      <c r="C133" s="34" t="s">
         <v>582</v>
       </c>
-      <c r="B133" s="34" t="s">
+      <c r="D133" s="34" t="s">
         <v>583</v>
-      </c>
-      <c r="C133" s="34" t="s">
-        <v>584</v>
-      </c>
-      <c r="D133" s="34" t="s">
-        <v>585</v>
       </c>
       <c r="E133" s="34"/>
       <c r="F133" s="34"/>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="34" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="B134" s="34" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C134" s="34" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D134" s="34" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E134" s="34"/>
       <c r="F134" s="34"/>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="34" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="B135" s="34" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C135" s="34" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D135" s="34" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E135" s="34"/>
       <c r="F135" s="34"/>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="34" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="B136" s="34" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C136" s="34" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D136" s="34" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E136" s="34"/>
       <c r="F136" s="34"/>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="34" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="B137" s="34" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="C137" s="34" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="D137" s="34" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E137" s="34"/>
       <c r="F137" s="34"/>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="34" t="s">
+        <v>592</v>
+      </c>
+      <c r="B138" s="34" t="s">
+        <v>593</v>
+      </c>
+      <c r="C138" s="34" t="s">
+        <v>575</v>
+      </c>
+      <c r="D138" s="34" t="s">
         <v>594</v>
-      </c>
-      <c r="B138" s="34" t="s">
-        <v>595</v>
-      </c>
-      <c r="C138" s="34" t="s">
-        <v>577</v>
-      </c>
-      <c r="D138" s="34" t="s">
-        <v>596</v>
       </c>
       <c r="E138" s="34"/>
       <c r="F138" s="34"/>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="34" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B139" s="34" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C139" s="34" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D139" s="34" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="E139" s="34"/>
       <c r="F139" s="34"/>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="34" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B140" s="34" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C140" s="34" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D140" s="34" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="E140" s="34"/>
       <c r="F140" s="34"/>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="34" t="s">
+        <v>599</v>
+      </c>
+      <c r="B141" s="34" t="s">
+        <v>600</v>
+      </c>
+      <c r="C141" s="34" t="s">
+        <v>224</v>
+      </c>
+      <c r="D141" s="34" t="s">
         <v>601</v>
-      </c>
-      <c r="B141" s="34" t="s">
-        <v>602</v>
-      </c>
-      <c r="C141" s="34" t="s">
-        <v>226</v>
-      </c>
-      <c r="D141" s="34" t="s">
-        <v>603</v>
       </c>
       <c r="E141" s="34"/>
       <c r="F141" s="34"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="34" t="s">
+        <v>602</v>
+      </c>
+      <c r="B142" s="34" t="s">
+        <v>603</v>
+      </c>
+      <c r="C142" s="34" t="s">
+        <v>349</v>
+      </c>
+      <c r="D142" s="34" t="s">
         <v>604</v>
-      </c>
-      <c r="B142" s="34" t="s">
-        <v>605</v>
-      </c>
-      <c r="C142" s="34" t="s">
-        <v>351</v>
-      </c>
-      <c r="D142" s="34" t="s">
-        <v>606</v>
       </c>
       <c r="E142" s="34"/>
       <c r="F142" s="34"/>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="34" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="B143" s="34" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C143" s="34" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D143" s="34" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E143" s="34"/>
       <c r="F143" s="34"/>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="34" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="B144" s="34" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C144" s="34" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D144" s="34" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="E144" s="34"/>
       <c r="F144" s="34"/>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="34" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="B145" s="34" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C145" s="34" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D145" s="34" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E145" s="34"/>
       <c r="F145" s="34"/>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="34" t="s">
+        <v>611</v>
+      </c>
+      <c r="B146" s="34" t="s">
+        <v>612</v>
+      </c>
+      <c r="C146" s="34" t="s">
+        <v>404</v>
+      </c>
+      <c r="D146" s="34" t="s">
         <v>613</v>
-      </c>
-      <c r="B146" s="34" t="s">
-        <v>614</v>
-      </c>
-      <c r="C146" s="34" t="s">
-        <v>406</v>
-      </c>
-      <c r="D146" s="34" t="s">
-        <v>615</v>
       </c>
       <c r="E146" s="34"/>
       <c r="F146" s="34"/>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="34" t="s">
+        <v>614</v>
+      </c>
+      <c r="B147" s="34" t="s">
+        <v>615</v>
+      </c>
+      <c r="C147" s="34" t="s">
+        <v>156</v>
+      </c>
+      <c r="D147" s="34" t="s">
         <v>616</v>
-      </c>
-      <c r="B147" s="34" t="s">
-        <v>617</v>
-      </c>
-      <c r="C147" s="34" t="s">
-        <v>158</v>
-      </c>
-      <c r="D147" s="34" t="s">
-        <v>618</v>
       </c>
       <c r="E147" s="34"/>
       <c r="F147" s="34"/>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="34" t="s">
+        <v>617</v>
+      </c>
+      <c r="B148" s="34" t="s">
+        <v>618</v>
+      </c>
+      <c r="C148" s="34" t="s">
+        <v>547</v>
+      </c>
+      <c r="D148" s="34" t="s">
         <v>619</v>
-      </c>
-      <c r="B148" s="34" t="s">
-        <v>620</v>
-      </c>
-      <c r="C148" s="34" t="s">
-        <v>549</v>
-      </c>
-      <c r="D148" s="34" t="s">
-        <v>621</v>
       </c>
       <c r="E148" s="34"/>
       <c r="F148" s="34"/>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="34" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="B149" s="34" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C149" s="34" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D149" s="34" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="E149" s="34"/>
       <c r="F149" s="34"/>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="34" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="B150" s="34" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C150" s="34" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D150" s="34" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="E150" s="34"/>
       <c r="F150" s="34"/>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="34" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="B151" s="34" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C151" s="34" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D151" s="34" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="E151" s="34"/>
       <c r="F151" s="34"/>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="34" t="s">
+        <v>626</v>
+      </c>
+      <c r="B152" s="34" t="s">
+        <v>627</v>
+      </c>
+      <c r="C152" s="34" t="s">
+        <v>310</v>
+      </c>
+      <c r="D152" s="34" t="s">
         <v>628</v>
-      </c>
-      <c r="B152" s="34" t="s">
-        <v>629</v>
-      </c>
-      <c r="C152" s="34" t="s">
-        <v>312</v>
-      </c>
-      <c r="D152" s="34" t="s">
-        <v>630</v>
       </c>
       <c r="E152" s="34"/>
       <c r="F152" s="34"/>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="34" t="s">
+        <v>629</v>
+      </c>
+      <c r="B153" s="34" t="s">
+        <v>630</v>
+      </c>
+      <c r="C153" s="34" t="s">
+        <v>310</v>
+      </c>
+      <c r="D153" s="34" t="s">
         <v>631</v>
-      </c>
-      <c r="B153" s="34" t="s">
-        <v>632</v>
-      </c>
-      <c r="C153" s="34" t="s">
-        <v>312</v>
-      </c>
-      <c r="D153" s="34" t="s">
-        <v>633</v>
       </c>
       <c r="E153" s="34"/>
       <c r="F153" s="34"/>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="34" t="s">
+        <v>632</v>
+      </c>
+      <c r="B154" s="34" t="s">
+        <v>633</v>
+      </c>
+      <c r="C154" s="34" t="s">
+        <v>270</v>
+      </c>
+      <c r="D154" s="34" t="s">
         <v>634</v>
-      </c>
-      <c r="B154" s="34" t="s">
-        <v>635</v>
-      </c>
-      <c r="C154" s="34" t="s">
-        <v>272</v>
-      </c>
-      <c r="D154" s="34" t="s">
-        <v>636</v>
       </c>
       <c r="E154" s="34"/>
       <c r="F154" s="34"/>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="34" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B155" s="34" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C155" s="34" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D155" s="34" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="E155" s="34"/>
       <c r="F155" s="34"/>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="34" t="s">
+        <v>637</v>
+      </c>
+      <c r="B156" s="34" t="s">
+        <v>638</v>
+      </c>
+      <c r="C156" s="34" t="s">
+        <v>479</v>
+      </c>
+      <c r="D156" s="34" t="s">
         <v>639</v>
-      </c>
-      <c r="B156" s="34" t="s">
-        <v>640</v>
-      </c>
-      <c r="C156" s="34" t="s">
-        <v>481</v>
-      </c>
-      <c r="D156" s="34" t="s">
-        <v>641</v>
       </c>
       <c r="E156" s="34"/>
       <c r="F156" s="34"/>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="34" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B157" s="34" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C157" s="34" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D157" s="34" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="E157" s="34"/>
       <c r="F157" s="34"/>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="34" t="s">
+        <v>642</v>
+      </c>
+      <c r="B158" s="34" t="s">
+        <v>643</v>
+      </c>
+      <c r="C158" s="34" t="s">
+        <v>479</v>
+      </c>
+      <c r="D158" s="34" t="s">
         <v>644</v>
-      </c>
-      <c r="B158" s="34" t="s">
-        <v>645</v>
-      </c>
-      <c r="C158" s="34" t="s">
-        <v>481</v>
-      </c>
-      <c r="D158" s="34" t="s">
-        <v>646</v>
       </c>
       <c r="E158" s="34"/>
       <c r="F158" s="34"/>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="34" t="s">
+        <v>645</v>
+      </c>
+      <c r="B159" s="34" t="s">
+        <v>646</v>
+      </c>
+      <c r="C159" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="D159" s="34" t="s">
         <v>647</v>
-      </c>
-      <c r="B159" s="34" t="s">
-        <v>648</v>
-      </c>
-      <c r="C159" s="34" t="s">
-        <v>150</v>
-      </c>
-      <c r="D159" s="34" t="s">
-        <v>649</v>
       </c>
       <c r="E159" s="34"/>
       <c r="F159" s="34"/>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="34" t="s">
+        <v>648</v>
+      </c>
+      <c r="B160" s="34" t="s">
+        <v>649</v>
+      </c>
+      <c r="C160" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="D160" s="34" t="s">
         <v>650</v>
-      </c>
-      <c r="B160" s="34" t="s">
-        <v>651</v>
-      </c>
-      <c r="C160" s="34" t="s">
-        <v>146</v>
-      </c>
-      <c r="D160" s="34" t="s">
-        <v>652</v>
       </c>
       <c r="E160" s="34"/>
       <c r="F160" s="34"/>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="34" t="s">
+        <v>651</v>
+      </c>
+      <c r="B161" s="34" t="s">
+        <v>652</v>
+      </c>
+      <c r="C161" s="34" t="s">
+        <v>220</v>
+      </c>
+      <c r="D161" s="34" t="s">
         <v>653</v>
-      </c>
-      <c r="B161" s="34" t="s">
-        <v>654</v>
-      </c>
-      <c r="C161" s="34" t="s">
-        <v>222</v>
-      </c>
-      <c r="D161" s="34" t="s">
-        <v>655</v>
       </c>
       <c r="E161" s="34"/>
       <c r="F161" s="34"/>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="34" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B162" s="34" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C162" s="34" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="D162" s="34" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="E162" s="34"/>
       <c r="F162" s="34"/>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="34" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B163" s="34" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C163" s="34" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D163" s="34" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="E163" s="34"/>
       <c r="F163" s="34"/>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="34" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B164" s="34" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C164" s="34" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D164" s="34" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="E164" s="34"/>
       <c r="F164" s="34"/>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="34" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B165" s="34" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C165" s="34" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="D165" s="34" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="E165" s="34"/>
       <c r="F165" s="34"/>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="34" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B166" s="34" t="s">
+        <v>662</v>
+      </c>
+      <c r="C166" s="34" t="s">
+        <v>755</v>
+      </c>
+      <c r="D166" s="34" t="s">
         <v>664</v>
-      </c>
-      <c r="C166" s="34" t="s">
-        <v>757</v>
-      </c>
-      <c r="D166" s="34" t="s">
-        <v>666</v>
       </c>
       <c r="F166" s="34"/>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="34" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="B167" s="34" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C167" s="34" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="D167" s="34" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="F167" s="34"/>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="34" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="B168" s="34" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C168" s="34" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="D168" s="34" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="F168" s="34"/>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="34" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="B169" s="34" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C169" s="34" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="D169" s="34" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="F169" s="34"/>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="34" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="B170" s="34" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C170" s="34" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="D170" s="34" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="F170" s="34"/>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="34" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="B171" s="34" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="C171" s="34" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="D171" s="34" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="F171" s="34"/>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="34" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B172" s="34" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="C172" s="34" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D172" s="34" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="F172" s="34"/>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="34" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="B173" s="34" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="C173" s="34" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="D173" s="34" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="F173" s="34"/>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="34" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="B174" s="37" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="C174" s="34" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="D174" s="34" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="F174" s="34"/>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="34" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B175" s="34" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="C175" s="34" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="D175" s="34" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="F175" s="34"/>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="34" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="B176" s="34" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C176" s="34" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D176" s="34" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="F176" s="34"/>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="34" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B177" s="34" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="C177" s="34" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="D177" s="34" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="F177" s="34"/>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="34" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B178" s="34" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C178" s="34" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D178" s="34" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="F178" s="34"/>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="34" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="B179" s="34" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C179" s="34" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="D179" s="34" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="F179" s="34"/>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="34" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="B180" s="37" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C180" s="34" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D180" s="34" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="F180" s="34"/>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="34" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B181" s="37" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="C181" s="34" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D181" s="34" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="F181" s="34"/>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="34" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B182" s="37" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C182" s="34" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="D182" s="34" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="F182" s="34"/>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="34" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B183" s="37" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C183" s="34" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D183" s="34" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="F183" s="34"/>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="34" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B184" s="37" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="C184" s="34" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="D184" s="34" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="F184" s="34"/>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="34" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B185" s="37" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="C185" s="34" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="D185" s="34" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="F185" s="34"/>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="34" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B186" s="37" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="C186" s="34" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="D186" s="34" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="F186" s="34"/>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="34" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B187" s="37" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C187" s="34" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="D187" s="34" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="F187" s="34"/>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="34" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B188" s="37" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C188" s="34" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="D188" s="34" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="F188" s="34"/>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="34" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B189" s="37" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C189" s="34" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="D189" s="34" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="F189" s="34"/>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="34" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B190" s="37" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="C190" s="34" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="D190" s="34" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="F190" s="34"/>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="34" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B191" s="37" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C191" s="34" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D191" s="34" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="F191" s="34"/>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="34" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="B192" s="37" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="C192" s="34" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="D192" s="34" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="F192" s="34"/>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="34" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="B193" s="37" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C193" s="34" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D193" s="34" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="F193" s="34"/>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="34" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="B194" s="34" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="C194" s="34" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D194" s="34" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="F194" s="34"/>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="34" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="B195" s="34" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="C195" s="34" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D195" s="34" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="F195" s="34"/>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="34" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="B196" s="37" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="C196" s="34" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D196" s="34" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="F196" s="34"/>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="34" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="B197" s="37" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C197" s="34" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D197" s="34" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="F197" s="34"/>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="34" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B198" s="37" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="C198" s="34" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D198" s="34" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="F198" s="34"/>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="34" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="B199" s="37" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C199" s="34" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D199" s="34" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="F199" s="34"/>
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="34" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="B200" s="37" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="C200" s="34" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D200" s="34" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="F200" s="34"/>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="34" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="B201" s="37" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C201" s="34" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D201" s="34" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="F201" s="34"/>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="34" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="B202" s="37" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C202" s="34" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D202" s="34" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="F202" s="34"/>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="34" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="B203" s="37" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="C203" s="34" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D203" s="34" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="F203" s="34"/>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="34" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="B204" s="37" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C204" s="34" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="D204" s="34" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="F204" s="34"/>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="34" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="B205" s="37" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C205" s="34" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="D205" s="34" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="F205" s="34"/>
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="34" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="B206" s="37" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="C206" s="34" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D206" s="34" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="F206" s="34"/>
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="34" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="B207" s="37" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C207" s="34" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="D207" s="34" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="F207" s="34"/>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="34" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="B208" s="37" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="C208" s="34" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="D208" s="34" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="F208" s="34"/>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="34" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="B209" s="37" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C209" s="34" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="D209" s="34" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="F209" s="34"/>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="34" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="B210" s="37" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="C210" s="34" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="D210" s="34" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="F210" s="34"/>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="34" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="B211" s="34" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="C211" s="34" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="D211" s="34" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="F211" s="34"/>
     </row>
@@ -7430,7 +7446,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C1" s="8" t="s">
         <v>1</v>
@@ -7446,13 +7462,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C2" s="4">
         <v>60</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -7462,13 +7478,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C3" s="4">
         <v>60</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -7476,13 +7492,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C4" s="4">
         <v>50</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -7490,13 +7506,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C5" s="4">
         <v>40</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -7504,13 +7520,13 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C6" s="4">
         <v>20</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -7518,13 +7534,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C7" s="4">
         <v>30</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E7" s="6"/>
     </row>
@@ -7533,13 +7549,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C8" s="4">
         <v>40</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E8" s="6"/>
     </row>
@@ -7548,13 +7564,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C9" s="4">
         <v>20</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -7562,13 +7578,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C10" s="4">
         <v>10</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -7576,13 +7592,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C11" s="4">
         <v>30</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -7590,13 +7606,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C12" s="4">
         <v>10</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -7604,13 +7620,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C13" s="4">
         <v>40</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E13" s="6"/>
     </row>
@@ -7619,13 +7635,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C14" s="4">
         <v>30</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -7633,13 +7649,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C15" s="4">
         <v>40</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -7647,13 +7663,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C16" s="4">
         <v>20</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E16" s="6"/>
     </row>
@@ -7662,13 +7678,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C17" s="4">
         <v>10</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -7676,13 +7692,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C18" s="4">
         <v>10</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -7690,13 +7706,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C19" s="4">
         <v>10</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -7704,13 +7720,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C20" s="4">
         <v>30</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -7718,13 +7734,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C21" s="4">
         <v>30</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -7732,13 +7748,13 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C22" s="4">
         <v>30</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -7746,13 +7762,13 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C23" s="4">
         <v>30</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/src/config/midas_config_values.xlsx
+++ b/src/config/midas_config_values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/james/Documents/code/midas-alt/src/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36BBED24-F22E-E440-98D6-A2F0550DFEA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE07FBB3-285B-5A46-AB0A-34C2BA241026}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="51200" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{C4C84A31-B2D7-9544-A674-D1C9532EF091}"/>
   </bookViews>

--- a/src/config/midas_config_values.xlsx
+++ b/src/config/midas_config_values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/james/Documents/code/midas-alt/src/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE78FA91-C5F8-3845-B782-703E8ECDC042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A26520C-FD58-5E49-8F5F-2067945475D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="80" yWindow="500" windowWidth="39880" windowHeight="28300" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="80" yWindow="500" windowWidth="39880" windowHeight="28300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="1" r:id="rId1"/>
